--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127054779</v>
+        <v>127054770</v>
       </c>
       <c r="B22" t="n">
-        <v>91621</v>
+        <v>92022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443684</v>
+        <v>443778</v>
       </c>
       <c r="R22" t="n">
-        <v>7009641</v>
+        <v>7009721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127054789</v>
+        <v>127054779</v>
       </c>
       <c r="B23" t="n">
-        <v>91343</v>
+        <v>91621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443770</v>
+        <v>443684</v>
       </c>
       <c r="R23" t="n">
-        <v>7009721</v>
+        <v>7009641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,6 +2803,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,32 +2834,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127054770</v>
+        <v>127054789</v>
       </c>
       <c r="B24" t="n">
-        <v>92022</v>
+        <v>91343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443778</v>
+        <v>443770</v>
       </c>
       <c r="R24" t="n">
         <v>7009721</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127054764</v>
+        <v>127054796</v>
       </c>
       <c r="B28" t="n">
-        <v>91325</v>
+        <v>91995</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444040</v>
+        <v>444064</v>
       </c>
       <c r="R28" t="n">
-        <v>7010094</v>
+        <v>7010051</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127054796</v>
+        <v>127054764</v>
       </c>
       <c r="B29" t="n">
-        <v>91995</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444064</v>
+        <v>444040</v>
       </c>
       <c r="R29" t="n">
-        <v>7010051</v>
+        <v>7010094</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5597,32 +5597,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171757</v>
+        <v>127171739</v>
       </c>
       <c r="B52" t="n">
-        <v>91779</v>
+        <v>92022</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443706</v>
+        <v>444045</v>
       </c>
       <c r="R52" t="n">
-        <v>7009637</v>
+        <v>7010113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127171778</v>
+        <v>127171757</v>
       </c>
       <c r="B53" t="n">
-        <v>79173</v>
+        <v>91779</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5705,21 +5705,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1249</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443849</v>
+        <v>443706</v>
       </c>
       <c r="R53" t="n">
-        <v>7010007</v>
+        <v>7009637</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127171748</v>
+        <v>127171778</v>
       </c>
       <c r="B54" t="n">
-        <v>75136</v>
+        <v>79173</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5802,21 +5802,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444052</v>
+        <v>443849</v>
       </c>
       <c r="R54" t="n">
-        <v>7010134</v>
+        <v>7010007</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5888,32 +5888,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127171797</v>
+        <v>127171748</v>
       </c>
       <c r="B55" t="n">
-        <v>91343</v>
+        <v>75136</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443694</v>
+        <v>444052</v>
       </c>
       <c r="R55" t="n">
-        <v>7009702</v>
+        <v>7010134</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5985,32 +5985,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127171739</v>
+        <v>127171797</v>
       </c>
       <c r="B56" t="n">
-        <v>92022</v>
+        <v>91343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444045</v>
+        <v>443694</v>
       </c>
       <c r="R56" t="n">
-        <v>7010113</v>
+        <v>7009702</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -9683,32 +9683,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127171801</v>
+        <v>127171751</v>
       </c>
       <c r="B94" t="n">
-        <v>88728</v>
+        <v>75136</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>6486</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443690</v>
+        <v>443751</v>
       </c>
       <c r="R94" t="n">
-        <v>7009636</v>
+        <v>7009735</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9780,32 +9780,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127171777</v>
+        <v>127171801</v>
       </c>
       <c r="B95" t="n">
-        <v>79173</v>
+        <v>88728</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1249</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444030</v>
+        <v>443690</v>
       </c>
       <c r="R95" t="n">
-        <v>7010188</v>
+        <v>7009636</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9877,10 +9877,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127171751</v>
+        <v>127171777</v>
       </c>
       <c r="B96" t="n">
-        <v>75136</v>
+        <v>79173</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9888,21 +9888,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9912,10 +9912,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443751</v>
+        <v>444030</v>
       </c>
       <c r="R96" t="n">
-        <v>7009735</v>
+        <v>7010188</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13768,10 +13768,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127299830</v>
+        <v>127299818</v>
       </c>
       <c r="B135" t="n">
-        <v>91995</v>
+        <v>75136</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13779,21 +13779,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>898</v>
+        <v>6486</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13803,10 +13803,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444057</v>
+        <v>444299</v>
       </c>
       <c r="R135" t="n">
-        <v>7010071</v>
+        <v>7010246</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13865,45 +13865,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127299818</v>
+        <v>127303899</v>
       </c>
       <c r="B136" t="n">
-        <v>75136</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444299</v>
+        <v>444289</v>
       </c>
       <c r="R136" t="n">
-        <v>7010246</v>
+        <v>7010247</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13933,9 +13933,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -13950,57 +13960,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127303899</v>
+        <v>127299830</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>91995</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444289</v>
+        <v>444057</v>
       </c>
       <c r="R137" t="n">
-        <v>7010247</v>
+        <v>7010071</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14030,19 +14040,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>20:30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14057,22 +14057,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127302634</v>
+        <v>127303913</v>
       </c>
       <c r="B138" t="n">
-        <v>91325</v>
+        <v>75060</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14080,34 +14080,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443749</v>
+        <v>443984</v>
       </c>
       <c r="R138" t="n">
-        <v>7010018</v>
+        <v>7010138</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14137,11 +14137,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -14150,26 +14160,41 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127303913</v>
+        <v>127302634</v>
       </c>
       <c r="B139" t="n">
-        <v>75060</v>
+        <v>91325</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14177,34 +14202,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443984</v>
+        <v>443749</v>
       </c>
       <c r="R139" t="n">
-        <v>7010138</v>
+        <v>7010018</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14234,21 +14259,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -14257,76 +14272,61 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127302660</v>
+        <v>127303916</v>
       </c>
       <c r="B140" t="n">
-        <v>91621</v>
+        <v>75136</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443679</v>
+        <v>443956</v>
       </c>
       <c r="R140" t="n">
-        <v>7009872</v>
+        <v>7010157</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14356,11 +14356,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -14369,61 +14379,76 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127302669</v>
+        <v>127303906</v>
       </c>
       <c r="B141" t="n">
-        <v>91339</v>
+        <v>79100</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443852</v>
+        <v>444000</v>
       </c>
       <c r="R141" t="n">
-        <v>7009880</v>
+        <v>7010124</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14453,11 +14478,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -14466,61 +14501,76 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127303916</v>
+        <v>127302669</v>
       </c>
       <c r="B142" t="n">
-        <v>75136</v>
+        <v>91339</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443956</v>
+        <v>443852</v>
       </c>
       <c r="R142" t="n">
-        <v>7010157</v>
+        <v>7009880</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14550,21 +14600,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -14573,76 +14613,61 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127303906</v>
+        <v>127302660</v>
       </c>
       <c r="B143" t="n">
-        <v>79100</v>
+        <v>91621</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6450</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444000</v>
+        <v>443679</v>
       </c>
       <c r="R143" t="n">
-        <v>7010124</v>
+        <v>7009872</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14672,21 +14697,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
@@ -14695,31 +14710,16 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -18787,10 +18787,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127302659</v>
+        <v>127299815</v>
       </c>
       <c r="B184" t="n">
-        <v>91621</v>
+        <v>91325</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18798,34 +18798,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443722</v>
+        <v>444084</v>
       </c>
       <c r="R184" t="n">
-        <v>7010007</v>
+        <v>7010049</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18872,19 +18872,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127302653</v>
+        <v>127302659</v>
       </c>
       <c r="B185" t="n">
         <v>91621</v>
@@ -18919,10 +18919,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443979</v>
+        <v>443722</v>
       </c>
       <c r="R185" t="n">
-        <v>7010133</v>
+        <v>7010007</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18981,7 +18981,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127302654</v>
+        <v>127302653</v>
       </c>
       <c r="B186" t="n">
         <v>91621</v>
@@ -19016,10 +19016,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443964</v>
+        <v>443979</v>
       </c>
       <c r="R186" t="n">
-        <v>7010137</v>
+        <v>7010133</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127303909</v>
+        <v>127302654</v>
       </c>
       <c r="B187" t="n">
         <v>91621</v>
@@ -19109,14 +19109,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443991</v>
+        <v>443964</v>
       </c>
       <c r="R187" t="n">
-        <v>7010145</v>
+        <v>7010137</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19146,21 +19146,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -19169,41 +19159,26 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127299815</v>
+        <v>127303909</v>
       </c>
       <c r="B188" t="n">
-        <v>91325</v>
+        <v>91621</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19211,34 +19186,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>444084</v>
+        <v>443991</v>
       </c>
       <c r="R188" t="n">
-        <v>7010049</v>
+        <v>7010145</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19268,11 +19243,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
@@ -19281,26 +19266,41 @@
       </c>
       <c r="AG188" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127299829</v>
+        <v>127302636</v>
       </c>
       <c r="B189" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19308,34 +19308,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>444259</v>
+        <v>443640</v>
       </c>
       <c r="R189" t="n">
-        <v>7010202</v>
+        <v>7010000</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19382,19 +19382,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127302636</v>
+        <v>127302627</v>
       </c>
       <c r="B190" t="n">
         <v>91325</v>
@@ -19429,10 +19429,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443640</v>
+        <v>444031</v>
       </c>
       <c r="R190" t="n">
-        <v>7010000</v>
+        <v>7010049</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19491,7 +19491,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127302627</v>
+        <v>127302640</v>
       </c>
       <c r="B191" t="n">
         <v>91325</v>
@@ -19526,10 +19526,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>444031</v>
+        <v>443738</v>
       </c>
       <c r="R191" t="n">
-        <v>7010049</v>
+        <v>7009862</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19588,10 +19588,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127302640</v>
+        <v>127302655</v>
       </c>
       <c r="B192" t="n">
-        <v>91325</v>
+        <v>91621</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19599,21 +19599,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19623,10 +19623,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443738</v>
+        <v>443907</v>
       </c>
       <c r="R192" t="n">
-        <v>7009862</v>
+        <v>7010185</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19685,10 +19685,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127302655</v>
+        <v>127299829</v>
       </c>
       <c r="B193" t="n">
-        <v>91621</v>
+        <v>79014</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19696,34 +19696,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443907</v>
+        <v>444259</v>
       </c>
       <c r="R193" t="n">
-        <v>7010185</v>
+        <v>7010202</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19770,12 +19770,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -20526,10 +20526,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127299817</v>
+        <v>127303927</v>
       </c>
       <c r="B201" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20537,34 +20537,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>444242</v>
+        <v>443629</v>
       </c>
       <c r="R201" t="n">
-        <v>7010316</v>
+        <v>7009887</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20594,11 +20594,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
@@ -20607,26 +20617,41 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127303927</v>
+        <v>127299817</v>
       </c>
       <c r="B202" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20634,34 +20659,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>443629</v>
+        <v>444242</v>
       </c>
       <c r="R202" t="n">
-        <v>7009887</v>
+        <v>7010316</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20691,21 +20716,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -20714,31 +20729,16 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -4217,32 +4217,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127063412</v>
+        <v>127063416</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>91780</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4252,10 +4252,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444500</v>
+        <v>444276</v>
       </c>
       <c r="R38" t="n">
-        <v>7010378</v>
+        <v>7010235</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,17 +4290,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bohål i gran 1,6m upp</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4319,7 +4315,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127063416</v>
+        <v>127063417</v>
       </c>
       <c r="B39" t="n">
         <v>91780</v>
@@ -4354,10 +4350,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444276</v>
+        <v>444369</v>
       </c>
       <c r="R39" t="n">
-        <v>7010235</v>
+        <v>7010228</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4417,32 +4413,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127063417</v>
+        <v>127063412</v>
       </c>
       <c r="B40" t="n">
-        <v>91780</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4452,10 +4448,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444369</v>
+        <v>444500</v>
       </c>
       <c r="R40" t="n">
-        <v>7010228</v>
+        <v>7010378</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,13 +4486,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bohål i gran 1,6m upp</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127171772</v>
+        <v>127171789</v>
       </c>
       <c r="B46" t="n">
-        <v>91622</v>
+        <v>91340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443665</v>
+        <v>443942</v>
       </c>
       <c r="R46" t="n">
-        <v>7009633</v>
+        <v>7010153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127171789</v>
+        <v>127171794</v>
       </c>
       <c r="B47" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5123,21 +5123,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443942</v>
+        <v>443868</v>
       </c>
       <c r="R47" t="n">
-        <v>7010153</v>
+        <v>7009783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127171794</v>
+        <v>127171795</v>
       </c>
       <c r="B48" t="n">
         <v>91344</v>
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443868</v>
+        <v>443763</v>
       </c>
       <c r="R48" t="n">
-        <v>7009783</v>
+        <v>7009828</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5306,10 +5306,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127171795</v>
+        <v>127171733</v>
       </c>
       <c r="B49" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5317,21 +5317,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443763</v>
+        <v>443799</v>
       </c>
       <c r="R49" t="n">
-        <v>7009828</v>
+        <v>7009908</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5403,32 +5403,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127171733</v>
+        <v>127171750</v>
       </c>
       <c r="B50" t="n">
-        <v>91326</v>
+        <v>75136</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443799</v>
+        <v>443811</v>
       </c>
       <c r="R50" t="n">
-        <v>7009908</v>
+        <v>7009946</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5500,32 +5500,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171750</v>
+        <v>127171772</v>
       </c>
       <c r="B51" t="n">
-        <v>75136</v>
+        <v>91622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443811</v>
+        <v>443665</v>
       </c>
       <c r="R51" t="n">
-        <v>7009946</v>
+        <v>7009633</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5597,32 +5597,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171739</v>
+        <v>127171748</v>
       </c>
       <c r="B52" t="n">
-        <v>92023</v>
+        <v>75136</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6486</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444045</v>
+        <v>444052</v>
       </c>
       <c r="R52" t="n">
-        <v>7010113</v>
+        <v>7010134</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5694,32 +5694,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127171778</v>
+        <v>127171739</v>
       </c>
       <c r="B53" t="n">
-        <v>79173</v>
+        <v>92023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443849</v>
+        <v>444045</v>
       </c>
       <c r="R53" t="n">
-        <v>7010007</v>
+        <v>7010113</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127171757</v>
+        <v>127171778</v>
       </c>
       <c r="B54" t="n">
-        <v>91780</v>
+        <v>79173</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5802,21 +5802,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1249</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443706</v>
+        <v>443849</v>
       </c>
       <c r="R54" t="n">
-        <v>7009637</v>
+        <v>7010007</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5888,32 +5888,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127171797</v>
+        <v>127171757</v>
       </c>
       <c r="B55" t="n">
-        <v>91344</v>
+        <v>91780</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443694</v>
+        <v>443706</v>
       </c>
       <c r="R55" t="n">
-        <v>7009702</v>
+        <v>7009637</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5985,32 +5985,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127171748</v>
+        <v>127171797</v>
       </c>
       <c r="B56" t="n">
-        <v>75136</v>
+        <v>91344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444052</v>
+        <v>443694</v>
       </c>
       <c r="R56" t="n">
-        <v>7010134</v>
+        <v>7009702</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6276,57 +6276,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127171746</v>
+        <v>127171747</v>
       </c>
       <c r="B59" t="n">
-        <v>57654</v>
+        <v>75136</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6486</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443702</v>
+        <v>443962</v>
       </c>
       <c r="R59" t="n">
-        <v>7009658</v>
+        <v>7009915</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6385,32 +6373,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127171774</v>
+        <v>127171763</v>
       </c>
       <c r="B60" t="n">
-        <v>79173</v>
+        <v>91622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6420,10 +6408,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443612</v>
+        <v>444018</v>
       </c>
       <c r="R60" t="n">
-        <v>7009871</v>
+        <v>7010190</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6482,32 +6470,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171740</v>
+        <v>127171762</v>
       </c>
       <c r="B61" t="n">
-        <v>92023</v>
+        <v>91622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6517,10 +6505,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444029</v>
+        <v>443999</v>
       </c>
       <c r="R61" t="n">
-        <v>7010202</v>
+        <v>7010217</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6579,32 +6567,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171747</v>
+        <v>127171760</v>
       </c>
       <c r="B62" t="n">
-        <v>75136</v>
+        <v>91622</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6614,10 +6602,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443962</v>
+        <v>443882</v>
       </c>
       <c r="R62" t="n">
-        <v>7009915</v>
+        <v>7009800</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6676,10 +6664,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127171763</v>
+        <v>127171746</v>
       </c>
       <c r="B63" t="n">
-        <v>91622</v>
+        <v>57654</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6687,34 +6675,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444018</v>
+        <v>443702</v>
       </c>
       <c r="R63" t="n">
-        <v>7010190</v>
+        <v>7009658</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6773,32 +6773,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171762</v>
+        <v>127171774</v>
       </c>
       <c r="B64" t="n">
-        <v>91622</v>
+        <v>79173</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443999</v>
+        <v>443612</v>
       </c>
       <c r="R64" t="n">
-        <v>7010217</v>
+        <v>7009871</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6870,32 +6870,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127171760</v>
+        <v>127171740</v>
       </c>
       <c r="B65" t="n">
-        <v>91622</v>
+        <v>92023</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443882</v>
+        <v>444029</v>
       </c>
       <c r="R65" t="n">
-        <v>7009800</v>
+        <v>7010202</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127171730</v>
+        <v>127171725</v>
       </c>
       <c r="B74" t="n">
-        <v>91326</v>
+        <v>75138</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443904</v>
+        <v>443925</v>
       </c>
       <c r="R74" t="n">
-        <v>7010041</v>
+        <v>7010042</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127171725</v>
+        <v>127171798</v>
       </c>
       <c r="B75" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443925</v>
+        <v>443680</v>
       </c>
       <c r="R75" t="n">
-        <v>7010042</v>
+        <v>7009642</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7937,10 +7937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127171798</v>
+        <v>127171730</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7948,21 +7948,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7972,10 +7972,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443680</v>
+        <v>443904</v>
       </c>
       <c r="R76" t="n">
-        <v>7009642</v>
+        <v>7010041</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10750,32 +10750,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127171802</v>
+        <v>127171731</v>
       </c>
       <c r="B105" t="n">
-        <v>80152</v>
+        <v>91326</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10785,10 +10785,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443853</v>
+        <v>443827</v>
       </c>
       <c r="R105" t="n">
-        <v>7009799</v>
+        <v>7009979</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10847,32 +10847,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127171731</v>
+        <v>127171802</v>
       </c>
       <c r="B106" t="n">
-        <v>91326</v>
+        <v>80152</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10882,10 +10882,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443827</v>
+        <v>443853</v>
       </c>
       <c r="R106" t="n">
-        <v>7009979</v>
+        <v>7009799</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11138,32 +11138,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127171764</v>
+        <v>127171726</v>
       </c>
       <c r="B109" t="n">
-        <v>91622</v>
+        <v>91291</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11173,10 +11173,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443826</v>
+        <v>443752</v>
       </c>
       <c r="R109" t="n">
-        <v>7009951</v>
+        <v>7009813</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11235,10 +11235,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127171726</v>
+        <v>127171741</v>
       </c>
       <c r="B110" t="n">
-        <v>91291</v>
+        <v>92023</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11246,21 +11246,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443752</v>
+        <v>443691</v>
       </c>
       <c r="R110" t="n">
-        <v>7009813</v>
+        <v>7009636</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11332,32 +11332,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127171741</v>
+        <v>127171752</v>
       </c>
       <c r="B111" t="n">
-        <v>92023</v>
+        <v>75136</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3298</v>
+        <v>6486</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11367,10 +11367,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443691</v>
+        <v>443685</v>
       </c>
       <c r="R111" t="n">
-        <v>7009636</v>
+        <v>7009691</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11429,32 +11429,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127171752</v>
+        <v>127171781</v>
       </c>
       <c r="B112" t="n">
-        <v>75136</v>
+        <v>80117</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6486</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11464,10 +11464,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443685</v>
+        <v>443861</v>
       </c>
       <c r="R112" t="n">
-        <v>7009691</v>
+        <v>7009776</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127171781</v>
+        <v>127171764</v>
       </c>
       <c r="B113" t="n">
-        <v>80117</v>
+        <v>91622</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11537,21 +11537,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443861</v>
+        <v>443826</v>
       </c>
       <c r="R113" t="n">
-        <v>7009776</v>
+        <v>7009951</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11817,45 +11817,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127302649</v>
+        <v>127303918</v>
       </c>
       <c r="B116" t="n">
-        <v>91622</v>
+        <v>97470</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>222741</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444329</v>
+        <v>443944</v>
       </c>
       <c r="R116" t="n">
-        <v>7010232</v>
+        <v>7010169</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11885,9 +11885,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11902,22 +11912,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127302675</v>
+        <v>127302649</v>
       </c>
       <c r="B117" t="n">
-        <v>91344</v>
+        <v>91622</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11925,21 +11935,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11949,10 +11959,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443823</v>
+        <v>444329</v>
       </c>
       <c r="R117" t="n">
-        <v>7010119</v>
+        <v>7010232</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12011,45 +12021,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127303918</v>
+        <v>127302642</v>
       </c>
       <c r="B118" t="n">
-        <v>97470</v>
+        <v>57657</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443944</v>
+        <v>444096</v>
       </c>
       <c r="R118" t="n">
-        <v>7010169</v>
+        <v>7010088</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12079,19 +12097,14 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>18:28</t>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12106,22 +12119,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127302642</v>
+        <v>127302632</v>
       </c>
       <c r="B119" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12129,42 +12142,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444096</v>
+        <v>443773</v>
       </c>
       <c r="R119" t="n">
-        <v>7010088</v>
+        <v>7010102</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12197,11 +12202,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12228,10 +12228,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127302632</v>
+        <v>127302675</v>
       </c>
       <c r="B120" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12239,21 +12239,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443773</v>
+        <v>443823</v>
       </c>
       <c r="R120" t="n">
-        <v>7010102</v>
+        <v>7010119</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12325,10 +12325,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127299825</v>
+        <v>127302635</v>
       </c>
       <c r="B121" t="n">
-        <v>91340</v>
+        <v>91326</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12336,34 +12336,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444013</v>
+        <v>443722</v>
       </c>
       <c r="R121" t="n">
-        <v>7010089</v>
+        <v>7010008</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12410,19 +12410,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127303919</v>
+        <v>127299825</v>
       </c>
       <c r="B122" t="n">
         <v>91340</v>
@@ -12453,14 +12453,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443944</v>
+        <v>444013</v>
       </c>
       <c r="R122" t="n">
-        <v>7010169</v>
+        <v>7010089</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,21 +12490,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -12513,41 +12503,26 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127302635</v>
+        <v>127303919</v>
       </c>
       <c r="B123" t="n">
-        <v>91326</v>
+        <v>91340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12555,34 +12530,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443722</v>
+        <v>443944</v>
       </c>
       <c r="R123" t="n">
-        <v>7010008</v>
+        <v>7010169</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12612,11 +12587,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -12625,26 +12610,41 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127302641</v>
+        <v>127303924</v>
       </c>
       <c r="B124" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12652,34 +12652,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444203</v>
+        <v>443651</v>
       </c>
       <c r="R124" t="n">
-        <v>7010082</v>
+        <v>7010015</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12709,14 +12709,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12727,26 +12732,41 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127299820</v>
+        <v>127302641</v>
       </c>
       <c r="B125" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12754,34 +12774,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444007</v>
+        <v>444203</v>
       </c>
       <c r="R125" t="n">
-        <v>7010102</v>
+        <v>7010082</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12818,7 +12838,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>14 fruktkroppar</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12833,22 +12853,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127303924</v>
+        <v>127302625</v>
       </c>
       <c r="B126" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12856,34 +12876,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443651</v>
+        <v>444262</v>
       </c>
       <c r="R126" t="n">
-        <v>7010015</v>
+        <v>7010300</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12913,21 +12933,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -12936,41 +12946,26 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127302625</v>
+        <v>127299820</v>
       </c>
       <c r="B127" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12978,34 +12973,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444262</v>
+        <v>444007</v>
       </c>
       <c r="R127" t="n">
-        <v>7010300</v>
+        <v>7010102</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13040,6 +13035,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>14 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13052,12 +13052,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -15736,10 +15736,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127303898</v>
+        <v>127302650</v>
       </c>
       <c r="B154" t="n">
-        <v>80117</v>
+        <v>91622</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15747,34 +15747,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>444047</v>
+        <v>444093</v>
       </c>
       <c r="R154" t="n">
-        <v>7009927</v>
+        <v>7010086</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15804,19 +15804,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>21:26</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>21:26</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15831,57 +15821,57 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127303907</v>
+        <v>127302639</v>
       </c>
       <c r="B155" t="n">
-        <v>98776</v>
+        <v>91326</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>444006</v>
+        <v>443697</v>
       </c>
       <c r="R155" t="n">
-        <v>7010126</v>
+        <v>7009873</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15911,19 +15901,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -15938,22 +15918,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127302650</v>
+        <v>127303898</v>
       </c>
       <c r="B156" t="n">
-        <v>91622</v>
+        <v>80117</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15961,34 +15941,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>444093</v>
+        <v>444047</v>
       </c>
       <c r="R156" t="n">
-        <v>7010086</v>
+        <v>7009927</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16018,9 +15998,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16035,57 +16025,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127302639</v>
+        <v>127303907</v>
       </c>
       <c r="B157" t="n">
-        <v>91326</v>
+        <v>98776</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443697</v>
+        <v>444006</v>
       </c>
       <c r="R157" t="n">
-        <v>7009873</v>
+        <v>7010126</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16115,9 +16105,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16132,22 +16132,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127302648</v>
+        <v>127302643</v>
       </c>
       <c r="B158" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16155,34 +16155,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>444005</v>
+        <v>443735</v>
       </c>
       <c r="R158" t="n">
-        <v>7009910</v>
+        <v>7009851</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16215,6 +16223,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16338,10 +16351,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127302643</v>
+        <v>127302648</v>
       </c>
       <c r="B160" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16349,42 +16362,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443735</v>
+        <v>444005</v>
       </c>
       <c r="R160" t="n">
-        <v>7009851</v>
+        <v>7009910</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16417,11 +16422,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16448,10 +16448,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127303930</v>
+        <v>127299813</v>
       </c>
       <c r="B161" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16459,34 +16459,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443689</v>
+        <v>444303</v>
       </c>
       <c r="R161" t="n">
-        <v>7009719</v>
+        <v>7010251</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16516,21 +16516,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -16539,38 +16529,23 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127299813</v>
+        <v>127302638</v>
       </c>
       <c r="B162" t="n">
         <v>91326</v>
@@ -16601,14 +16576,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>444303</v>
+        <v>443679</v>
       </c>
       <c r="R162" t="n">
-        <v>7010251</v>
+        <v>7009870</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16655,44 +16630,44 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127302638</v>
+        <v>127302644</v>
       </c>
       <c r="B163" t="n">
-        <v>91326</v>
+        <v>91780</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16702,10 +16677,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>443679</v>
+        <v>443970</v>
       </c>
       <c r="R163" t="n">
-        <v>7009870</v>
+        <v>7009897</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16746,6 +16721,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16764,45 +16740,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127302644</v>
+        <v>127303930</v>
       </c>
       <c r="B164" t="n">
-        <v>91780</v>
+        <v>91622</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>443970</v>
+        <v>443689</v>
       </c>
       <c r="R164" t="n">
-        <v>7009897</v>
+        <v>7009719</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16832,30 +16808,54 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -17494,10 +17494,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127299827</v>
+        <v>127302630</v>
       </c>
       <c r="B171" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17505,34 +17505,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>444241</v>
+        <v>443979</v>
       </c>
       <c r="R171" t="n">
-        <v>7010317</v>
+        <v>7010134</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17579,22 +17579,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127302630</v>
+        <v>127303914</v>
       </c>
       <c r="B172" t="n">
-        <v>91326</v>
+        <v>75060</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17602,31 +17602,31 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>443979</v>
+        <v>443985</v>
       </c>
       <c r="R172" t="n">
         <v>7010134</v>
@@ -17659,11 +17659,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
@@ -17672,61 +17682,76 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127303914</v>
+        <v>127302645</v>
       </c>
       <c r="B173" t="n">
-        <v>75060</v>
+        <v>91780</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1460</v>
+        <v>1209</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443985</v>
+        <v>443997</v>
       </c>
       <c r="R173" t="n">
-        <v>7010134</v>
+        <v>7010102</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17756,99 +17781,75 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302645</v>
+        <v>127299827</v>
       </c>
       <c r="B174" t="n">
-        <v>91780</v>
+        <v>91344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443997</v>
+        <v>444241</v>
       </c>
       <c r="R174" t="n">
-        <v>7010102</v>
+        <v>7010317</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17889,19 +17890,18 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -18787,7 +18787,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127302654</v>
+        <v>127303909</v>
       </c>
       <c r="B184" t="n">
         <v>91622</v>
@@ -18818,14 +18818,14 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443964</v>
+        <v>443991</v>
       </c>
       <c r="R184" t="n">
-        <v>7010137</v>
+        <v>7010145</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18855,11 +18855,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -18868,26 +18878,41 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127303909</v>
+        <v>127299815</v>
       </c>
       <c r="B185" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18895,34 +18920,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443991</v>
+        <v>444084</v>
       </c>
       <c r="R185" t="n">
-        <v>7010145</v>
+        <v>7010049</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18952,21 +18977,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -18975,41 +18990,26 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127299815</v>
+        <v>127302659</v>
       </c>
       <c r="B186" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19017,34 +19017,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>444084</v>
+        <v>443722</v>
       </c>
       <c r="R186" t="n">
-        <v>7010049</v>
+        <v>7010007</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19091,19 +19091,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127302659</v>
+        <v>127302653</v>
       </c>
       <c r="B187" t="n">
         <v>91622</v>
@@ -19138,10 +19138,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443722</v>
+        <v>443979</v>
       </c>
       <c r="R187" t="n">
-        <v>7010007</v>
+        <v>7010133</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19200,7 +19200,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127302653</v>
+        <v>127302654</v>
       </c>
       <c r="B188" t="n">
         <v>91622</v>
@@ -19235,10 +19235,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>443979</v>
+        <v>443964</v>
       </c>
       <c r="R188" t="n">
-        <v>7010133</v>
+        <v>7010137</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19782,10 +19782,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127303922</v>
+        <v>127303925</v>
       </c>
       <c r="B194" t="n">
-        <v>91686</v>
+        <v>79173</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19793,21 +19793,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2063</v>
+        <v>1249</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19817,10 +19817,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>443745</v>
+        <v>443627</v>
       </c>
       <c r="R194" t="n">
-        <v>7010077</v>
+        <v>7009957</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19874,9 +19874,19 @@
       <c r="AG194" t="b">
         <v>0</v>
       </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>På/intill död granticka på grov granlåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>
@@ -19894,32 +19904,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127303925</v>
+        <v>127303928</v>
       </c>
       <c r="B195" t="n">
-        <v>79173</v>
+        <v>91326</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19929,10 +19939,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443627</v>
+        <v>443698</v>
       </c>
       <c r="R195" t="n">
-        <v>7009957</v>
+        <v>7009874</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19964,7 +19974,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -19974,7 +19984,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20016,32 +20026,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127303928</v>
+        <v>127303922</v>
       </c>
       <c r="B196" t="n">
-        <v>91326</v>
+        <v>91686</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20051,10 +20061,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443698</v>
+        <v>443745</v>
       </c>
       <c r="R196" t="n">
-        <v>7009874</v>
+        <v>7010077</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20086,7 +20096,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20096,7 +20106,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20108,19 +20118,9 @@
       <c r="AG196" t="b">
         <v>0</v>
       </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>På/intill död granticka på grov granlåga.</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr"/>
@@ -22213,32 +22213,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127311039</v>
+        <v>127311052</v>
       </c>
       <c r="B218" t="n">
-        <v>79173</v>
+        <v>79014</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22248,10 +22248,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>443626</v>
+        <v>443874</v>
       </c>
       <c r="R218" t="n">
-        <v>7009924</v>
+        <v>7009953</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22310,10 +22310,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127311052</v>
+        <v>127311042</v>
       </c>
       <c r="B219" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22321,21 +22321,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22345,10 +22345,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>443874</v>
+        <v>443919</v>
       </c>
       <c r="R219" t="n">
-        <v>7009953</v>
+        <v>7010183</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22407,32 +22407,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127311042</v>
+        <v>127311039</v>
       </c>
       <c r="B220" t="n">
-        <v>80117</v>
+        <v>79173</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22442,10 +22442,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>443919</v>
+        <v>443626</v>
       </c>
       <c r="R220" t="n">
-        <v>7010183</v>
+        <v>7009924</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24541,10 +24541,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127310988</v>
+        <v>127311025</v>
       </c>
       <c r="B242" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24552,21 +24552,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24576,10 +24576,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>443937</v>
+        <v>443634</v>
       </c>
       <c r="R242" t="n">
-        <v>7010167</v>
+        <v>7009878</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24638,10 +24638,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127311050</v>
+        <v>127310988</v>
       </c>
       <c r="B243" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24649,21 +24649,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24673,10 +24673,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>443756</v>
+        <v>443937</v>
       </c>
       <c r="R243" t="n">
-        <v>7010085</v>
+        <v>7010167</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24735,7 +24735,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127311051</v>
+        <v>127311050</v>
       </c>
       <c r="B244" t="n">
         <v>91344</v>
@@ -24770,10 +24770,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>443729</v>
+        <v>443756</v>
       </c>
       <c r="R244" t="n">
-        <v>7009862</v>
+        <v>7010085</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24832,10 +24832,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127311025</v>
+        <v>127311051</v>
       </c>
       <c r="B245" t="n">
-        <v>91622</v>
+        <v>91344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -24843,21 +24843,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -24867,10 +24867,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>443634</v>
+        <v>443729</v>
       </c>
       <c r="R245" t="n">
-        <v>7009878</v>
+        <v>7009862</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25220,10 +25220,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127311023</v>
+        <v>127310991</v>
       </c>
       <c r="B249" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25231,21 +25231,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25255,10 +25255,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>444039</v>
+        <v>443609</v>
       </c>
       <c r="R249" t="n">
-        <v>7010073</v>
+        <v>7009974</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25317,10 +25317,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127310991</v>
+        <v>127311023</v>
       </c>
       <c r="B250" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25328,21 +25328,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25352,10 +25352,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>443609</v>
+        <v>444039</v>
       </c>
       <c r="R250" t="n">
-        <v>7009974</v>
+        <v>7010073</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25705,10 +25705,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127311038</v>
+        <v>127311008</v>
       </c>
       <c r="B254" t="n">
-        <v>79173</v>
+        <v>75136</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -25716,21 +25716,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -25740,10 +25740,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>444108</v>
+        <v>443750</v>
       </c>
       <c r="R254" t="n">
-        <v>7010013</v>
+        <v>7010074</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25802,10 +25802,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127311008</v>
+        <v>127311038</v>
       </c>
       <c r="B255" t="n">
-        <v>75136</v>
+        <v>79173</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -25813,21 +25813,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -25837,10 +25837,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>443750</v>
+        <v>444108</v>
       </c>
       <c r="R255" t="n">
-        <v>7010074</v>
+        <v>7010013</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127054779</v>
+        <v>127054789</v>
       </c>
       <c r="B22" t="n">
-        <v>91622</v>
+        <v>91344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443684</v>
+        <v>443770</v>
       </c>
       <c r="R22" t="n">
-        <v>7009641</v>
+        <v>7009721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,32 +2732,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127054770</v>
+        <v>127054779</v>
       </c>
       <c r="B23" t="n">
-        <v>92023</v>
+        <v>91622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443778</v>
+        <v>443684</v>
       </c>
       <c r="R23" t="n">
-        <v>7009721</v>
+        <v>7009641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,6 +2803,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,32 +2834,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127054789</v>
+        <v>127054770</v>
       </c>
       <c r="B24" t="n">
-        <v>91344</v>
+        <v>92023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443770</v>
+        <v>443778</v>
       </c>
       <c r="R24" t="n">
         <v>7009721</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127054796</v>
+        <v>127054764</v>
       </c>
       <c r="B28" t="n">
-        <v>91996</v>
+        <v>91326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444064</v>
+        <v>444040</v>
       </c>
       <c r="R28" t="n">
-        <v>7010051</v>
+        <v>7010094</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127054764</v>
+        <v>127054796</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>91996</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444040</v>
+        <v>444064</v>
       </c>
       <c r="R29" t="n">
-        <v>7010094</v>
+        <v>7010051</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127054784</v>
+        <v>127054768</v>
       </c>
       <c r="B31" t="n">
-        <v>91340</v>
+        <v>92023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443951</v>
+        <v>443988</v>
       </c>
       <c r="R31" t="n">
-        <v>7010189</v>
+        <v>7010226</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127054768</v>
+        <v>127054784</v>
       </c>
       <c r="B32" t="n">
-        <v>92023</v>
+        <v>91340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443988</v>
+        <v>443951</v>
       </c>
       <c r="R32" t="n">
-        <v>7010226</v>
+        <v>7010189</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5266,10 +5266,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127171759</v>
+        <v>127171792</v>
       </c>
       <c r="B49" t="n">
-        <v>91622</v>
+        <v>91340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5277,21 +5277,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443657</v>
+        <v>443662</v>
       </c>
       <c r="R49" t="n">
-        <v>7009838</v>
+        <v>7009632</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5363,10 +5363,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127171792</v>
+        <v>127171759</v>
       </c>
       <c r="B50" t="n">
-        <v>91340</v>
+        <v>91622</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5374,21 +5374,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443662</v>
+        <v>443657</v>
       </c>
       <c r="R50" t="n">
-        <v>7009632</v>
+        <v>7009838</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6151,10 +6151,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127171767</v>
+        <v>127171727</v>
       </c>
       <c r="B58" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443706</v>
+        <v>443530</v>
       </c>
       <c r="R58" t="n">
-        <v>7009709</v>
+        <v>7009894</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6248,7 +6248,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127171771</v>
+        <v>127171767</v>
       </c>
       <c r="B59" t="n">
         <v>91622</v>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443696</v>
+        <v>443706</v>
       </c>
       <c r="R59" t="n">
-        <v>7009640</v>
+        <v>7009709</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6345,10 +6345,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127171727</v>
+        <v>127171771</v>
       </c>
       <c r="B60" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6356,21 +6356,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443530</v>
+        <v>443696</v>
       </c>
       <c r="R60" t="n">
-        <v>7009894</v>
+        <v>7009640</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -11947,10 +11947,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127302625</v>
+        <v>127302641</v>
       </c>
       <c r="B117" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11958,21 +11958,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444262</v>
+        <v>444203</v>
       </c>
       <c r="R117" t="n">
-        <v>7010300</v>
+        <v>7010082</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12018,6 +12018,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12044,10 +12049,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127302641</v>
+        <v>127299820</v>
       </c>
       <c r="B118" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12055,34 +12060,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444203</v>
+        <v>444007</v>
       </c>
       <c r="R118" t="n">
-        <v>7010082</v>
+        <v>7010102</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12119,7 +12124,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>14 fruktkroppar</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12134,22 +12139,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127299820</v>
+        <v>127302625</v>
       </c>
       <c r="B119" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12157,34 +12162,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444007</v>
+        <v>444262</v>
       </c>
       <c r="R119" t="n">
-        <v>7010102</v>
+        <v>7010300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12219,11 +12224,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>14 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12236,22 +12236,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127302676</v>
+        <v>127302657</v>
       </c>
       <c r="B120" t="n">
-        <v>91344</v>
+        <v>91622</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12259,21 +12259,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443737</v>
+        <v>443766</v>
       </c>
       <c r="R120" t="n">
-        <v>7009850</v>
+        <v>7010076</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12345,7 +12345,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127302657</v>
+        <v>127302661</v>
       </c>
       <c r="B121" t="n">
         <v>91622</v>
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443766</v>
+        <v>443698</v>
       </c>
       <c r="R121" t="n">
-        <v>7010076</v>
+        <v>7009876</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12442,10 +12442,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127302661</v>
+        <v>127302637</v>
       </c>
       <c r="B122" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12453,21 +12453,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12477,10 +12477,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443698</v>
+        <v>443618</v>
       </c>
       <c r="R122" t="n">
-        <v>7009876</v>
+        <v>7009972</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127302637</v>
+        <v>127302676</v>
       </c>
       <c r="B123" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12550,21 +12550,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443618</v>
+        <v>443737</v>
       </c>
       <c r="R123" t="n">
-        <v>7009972</v>
+        <v>7009850</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13910,45 +13910,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127303920</v>
+        <v>127299816</v>
       </c>
       <c r="B136" t="n">
-        <v>100532</v>
+        <v>91326</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443902</v>
+        <v>444022</v>
       </c>
       <c r="R136" t="n">
-        <v>7010174</v>
+        <v>7010055</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13978,24 +13978,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14010,12 +13995,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14119,10 +14104,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127299816</v>
+        <v>127302668</v>
       </c>
       <c r="B138" t="n">
-        <v>91326</v>
+        <v>91340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,34 +14115,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444022</v>
+        <v>443816</v>
       </c>
       <c r="R138" t="n">
-        <v>7010055</v>
+        <v>7009788</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14204,22 +14189,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302666</v>
+        <v>127302670</v>
       </c>
       <c r="B139" t="n">
-        <v>91322</v>
+        <v>91340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14227,21 +14212,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14236,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443769</v>
+        <v>444114</v>
       </c>
       <c r="R139" t="n">
-        <v>7010089</v>
+        <v>7010064</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14313,45 +14298,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127302668</v>
+        <v>127303920</v>
       </c>
       <c r="B140" t="n">
-        <v>91340</v>
+        <v>100532</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1204</v>
+        <v>222771</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443816</v>
+        <v>443902</v>
       </c>
       <c r="R140" t="n">
-        <v>7009788</v>
+        <v>7010174</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14381,9 +14366,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14398,22 +14398,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127302670</v>
+        <v>127302666</v>
       </c>
       <c r="B141" t="n">
-        <v>91340</v>
+        <v>91322</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,21 +14421,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444114</v>
+        <v>443769</v>
       </c>
       <c r="R141" t="n">
-        <v>7010064</v>
+        <v>7010089</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15632,10 +15632,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127299813</v>
+        <v>127303930</v>
       </c>
       <c r="B153" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15643,34 +15643,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>444303</v>
+        <v>443689</v>
       </c>
       <c r="R153" t="n">
-        <v>7010251</v>
+        <v>7009719</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15700,11 +15700,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -15713,61 +15723,76 @@
       </c>
       <c r="AG153" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127303930</v>
+        <v>127302644</v>
       </c>
       <c r="B154" t="n">
-        <v>91622</v>
+        <v>91780</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443689</v>
+        <v>443970</v>
       </c>
       <c r="R154" t="n">
-        <v>7009719</v>
+        <v>7009897</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15797,61 +15822,37 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127302638</v>
+        <v>127299813</v>
       </c>
       <c r="B155" t="n">
         <v>91326</v>
@@ -15882,14 +15883,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443679</v>
+        <v>444303</v>
       </c>
       <c r="R155" t="n">
-        <v>7009870</v>
+        <v>7010251</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15936,44 +15937,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127302644</v>
+        <v>127302638</v>
       </c>
       <c r="B156" t="n">
-        <v>91780</v>
+        <v>91326</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15983,10 +15984,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443970</v>
+        <v>443679</v>
       </c>
       <c r="R156" t="n">
-        <v>7009897</v>
+        <v>7009870</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16027,7 +16028,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -16678,32 +16678,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127302630</v>
+        <v>127302645</v>
       </c>
       <c r="B163" t="n">
-        <v>91326</v>
+        <v>91780</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>443979</v>
+        <v>443997</v>
       </c>
       <c r="R163" t="n">
-        <v>7010134</v>
+        <v>7010102</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16757,6 +16757,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16872,10 +16873,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127303914</v>
+        <v>127302630</v>
       </c>
       <c r="B165" t="n">
-        <v>75060</v>
+        <v>91326</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16883,31 +16884,31 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>443985</v>
+        <v>443979</v>
       </c>
       <c r="R165" t="n">
         <v>7010134</v>
@@ -16940,21 +16941,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -16963,76 +16954,61 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127302645</v>
+        <v>127303914</v>
       </c>
       <c r="B166" t="n">
-        <v>91780</v>
+        <v>75060</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1209</v>
+        <v>1460</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>443997</v>
+        <v>443985</v>
       </c>
       <c r="R166" t="n">
-        <v>7010102</v>
+        <v>7010134</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17062,30 +17038,54 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127302627</v>
+        <v>127299829</v>
       </c>
       <c r="B182" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18589,34 +18589,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>444031</v>
+        <v>444259</v>
       </c>
       <c r="R182" t="n">
-        <v>7010049</v>
+        <v>7010202</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18663,22 +18663,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127299829</v>
+        <v>127302636</v>
       </c>
       <c r="B183" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18686,34 +18686,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>444259</v>
+        <v>443640</v>
       </c>
       <c r="R183" t="n">
-        <v>7010202</v>
+        <v>7010000</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18760,19 +18760,19 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127302636</v>
+        <v>127302627</v>
       </c>
       <c r="B184" t="n">
         <v>91326</v>
@@ -18807,10 +18807,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443640</v>
+        <v>444031</v>
       </c>
       <c r="R184" t="n">
-        <v>7010000</v>
+        <v>7010049</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19419,10 +19419,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127302672</v>
+        <v>127299817</v>
       </c>
       <c r="B190" t="n">
-        <v>91340</v>
+        <v>91326</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19430,34 +19430,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443978</v>
+        <v>444242</v>
       </c>
       <c r="R190" t="n">
-        <v>7010133</v>
+        <v>7010316</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19504,22 +19504,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127303927</v>
+        <v>127302672</v>
       </c>
       <c r="B191" t="n">
-        <v>79014</v>
+        <v>91340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19527,34 +19527,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443629</v>
+        <v>443978</v>
       </c>
       <c r="R191" t="n">
-        <v>7009887</v>
+        <v>7010133</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19584,21 +19584,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
@@ -19607,41 +19597,26 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127299817</v>
+        <v>127303927</v>
       </c>
       <c r="B192" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19649,34 +19624,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>444242</v>
+        <v>443629</v>
       </c>
       <c r="R192" t="n">
-        <v>7010316</v>
+        <v>7009887</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19706,11 +19681,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
@@ -19719,16 +19704,31 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
@@ -19929,45 +19929,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127311003</v>
+        <v>127311483</v>
       </c>
       <c r="B195" t="n">
-        <v>57499</v>
+        <v>92028</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>102621</v>
+        <v>67</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443820</v>
+        <v>443711</v>
       </c>
       <c r="R195" t="n">
-        <v>7009812</v>
+        <v>7010048</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20026,45 +20026,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127311483</v>
+        <v>127311026</v>
       </c>
       <c r="B196" t="n">
-        <v>92028</v>
+        <v>91622</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>67</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Haratjärnen, Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443711</v>
+        <v>443721</v>
       </c>
       <c r="R196" t="n">
-        <v>7010048</v>
+        <v>7009852</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20123,7 +20123,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127311026</v>
+        <v>127311016</v>
       </c>
       <c r="B197" t="n">
         <v>91622</v>
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443721</v>
+        <v>443914</v>
       </c>
       <c r="R197" t="n">
-        <v>7009852</v>
+        <v>7009959</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20220,7 +20220,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127311016</v>
+        <v>127311021</v>
       </c>
       <c r="B198" t="n">
         <v>91622</v>
@@ -20255,10 +20255,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>443914</v>
+        <v>444283</v>
       </c>
       <c r="R198" t="n">
-        <v>7009959</v>
+        <v>7010242</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20317,32 +20317,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127311021</v>
+        <v>127311006</v>
       </c>
       <c r="B199" t="n">
-        <v>91622</v>
+        <v>75136</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>444283</v>
+        <v>444031</v>
       </c>
       <c r="R199" t="n">
-        <v>7010242</v>
+        <v>7010078</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20414,32 +20414,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127311006</v>
+        <v>127311003</v>
       </c>
       <c r="B200" t="n">
-        <v>75136</v>
+        <v>57499</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6486</v>
+        <v>102621</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20449,10 +20449,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>444031</v>
+        <v>443820</v>
       </c>
       <c r="R200" t="n">
-        <v>7010078</v>
+        <v>7009812</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21093,10 +21093,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127310987</v>
+        <v>127310997</v>
       </c>
       <c r="B207" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21104,34 +21104,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443973</v>
+        <v>443735</v>
       </c>
       <c r="R207" t="n">
-        <v>7010146</v>
+        <v>7009858</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21164,6 +21172,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21190,10 +21203,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127310997</v>
+        <v>127310987</v>
       </c>
       <c r="B208" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21201,42 +21214,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>443735</v>
+        <v>443973</v>
       </c>
       <c r="R208" t="n">
-        <v>7009858</v>
+        <v>7010146</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21269,11 +21274,6 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22755,10 +22755,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127311030</v>
+        <v>127311059</v>
       </c>
       <c r="B224" t="n">
-        <v>75060</v>
+        <v>88729</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22766,21 +22766,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1460</v>
+        <v>510</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22790,10 +22790,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>444131</v>
+        <v>444272</v>
       </c>
       <c r="R224" t="n">
-        <v>7010038</v>
+        <v>7010237</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22852,10 +22852,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127311034</v>
+        <v>127311022</v>
       </c>
       <c r="B225" t="n">
-        <v>75060</v>
+        <v>91622</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22863,21 +22863,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>444026</v>
+        <v>444108</v>
       </c>
       <c r="R225" t="n">
-        <v>7010076</v>
+        <v>7010040</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22949,10 +22949,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127311041</v>
+        <v>127310995</v>
       </c>
       <c r="B226" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22960,21 +22960,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>444094</v>
+        <v>443689</v>
       </c>
       <c r="R226" t="n">
-        <v>7010004</v>
+        <v>7009728</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23046,10 +23046,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127311059</v>
+        <v>127310990</v>
       </c>
       <c r="B227" t="n">
-        <v>88729</v>
+        <v>91326</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23057,21 +23057,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23081,10 +23081,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>444272</v>
+        <v>443745</v>
       </c>
       <c r="R227" t="n">
-        <v>7010237</v>
+        <v>7010081</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23143,10 +23143,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127311022</v>
+        <v>127310986</v>
       </c>
       <c r="B228" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23154,21 +23154,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23178,10 +23178,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>444108</v>
+        <v>444046</v>
       </c>
       <c r="R228" t="n">
-        <v>7010040</v>
+        <v>7010063</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23240,10 +23240,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127310995</v>
+        <v>127311030</v>
       </c>
       <c r="B229" t="n">
-        <v>91326</v>
+        <v>75060</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23251,21 +23251,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>443689</v>
+        <v>444131</v>
       </c>
       <c r="R229" t="n">
-        <v>7009728</v>
+        <v>7010038</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127310990</v>
+        <v>127311034</v>
       </c>
       <c r="B230" t="n">
-        <v>91326</v>
+        <v>75060</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23348,21 +23348,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23372,10 +23372,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>443745</v>
+        <v>444026</v>
       </c>
       <c r="R230" t="n">
-        <v>7010081</v>
+        <v>7010076</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23434,10 +23434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127310986</v>
+        <v>127311041</v>
       </c>
       <c r="B231" t="n">
-        <v>91326</v>
+        <v>80117</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23445,21 +23445,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444046</v>
+        <v>444094</v>
       </c>
       <c r="R231" t="n">
-        <v>7010063</v>
+        <v>7010004</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23531,10 +23531,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127311027</v>
+        <v>127311025</v>
       </c>
       <c r="B232" t="n">
-        <v>75060</v>
+        <v>91622</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23542,21 +23542,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23566,10 +23566,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>444316</v>
+        <v>443634</v>
       </c>
       <c r="R232" t="n">
-        <v>7010269</v>
+        <v>7009878</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23628,10 +23628,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127311050</v>
+        <v>127311024</v>
       </c>
       <c r="B233" t="n">
-        <v>91344</v>
+        <v>91622</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23639,21 +23639,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23663,10 +23663,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>443756</v>
+        <v>443987</v>
       </c>
       <c r="R233" t="n">
-        <v>7010085</v>
+        <v>7010155</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23725,10 +23725,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127311051</v>
+        <v>127311027</v>
       </c>
       <c r="B234" t="n">
-        <v>91344</v>
+        <v>75060</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23736,21 +23736,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5432</v>
+        <v>1460</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23760,10 +23760,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443729</v>
+        <v>444316</v>
       </c>
       <c r="R234" t="n">
-        <v>7009862</v>
+        <v>7010269</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23822,10 +23822,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127311024</v>
+        <v>127311050</v>
       </c>
       <c r="B235" t="n">
-        <v>91622</v>
+        <v>91344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23833,21 +23833,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23857,10 +23857,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443987</v>
+        <v>443756</v>
       </c>
       <c r="R235" t="n">
-        <v>7010155</v>
+        <v>7010085</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23919,10 +23919,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127311025</v>
+        <v>127311051</v>
       </c>
       <c r="B236" t="n">
-        <v>91622</v>
+        <v>91344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23930,21 +23930,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23954,10 +23954,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>443634</v>
+        <v>443729</v>
       </c>
       <c r="R236" t="n">
-        <v>7009878</v>
+        <v>7009862</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127054780</v>
+        <v>127054791</v>
       </c>
       <c r="B4" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443665</v>
+        <v>444024</v>
       </c>
       <c r="R4" t="n">
-        <v>7009647</v>
+        <v>7009956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127054791</v>
+        <v>127054772</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444024</v>
+        <v>443748</v>
       </c>
       <c r="R5" t="n">
-        <v>7009956</v>
+        <v>7009749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127054772</v>
+        <v>127054780</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>91626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443748</v>
+        <v>443665</v>
       </c>
       <c r="R6" t="n">
-        <v>7009749</v>
+        <v>7009647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127054762</v>
+        <v>127054790</v>
       </c>
       <c r="B10" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443835</v>
+        <v>443700</v>
       </c>
       <c r="R10" t="n">
-        <v>7010003</v>
+        <v>7009788</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1553,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127054790</v>
+        <v>127054762</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443700</v>
+        <v>443835</v>
       </c>
       <c r="R11" t="n">
-        <v>7009788</v>
+        <v>7010003</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1624,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127054793</v>
+        <v>127054781</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>91699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443739</v>
+        <v>443695</v>
       </c>
       <c r="R16" t="n">
-        <v>7009743</v>
+        <v>7009658</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2114,11 +2114,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127054781</v>
+        <v>127054783</v>
       </c>
       <c r="B17" t="n">
-        <v>91699</v>
+        <v>91344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443695</v>
+        <v>444045</v>
       </c>
       <c r="R17" t="n">
-        <v>7009658</v>
+        <v>7010128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127054778</v>
+        <v>127054793</v>
       </c>
       <c r="B18" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443693</v>
+        <v>443739</v>
       </c>
       <c r="R18" t="n">
-        <v>7009697</v>
+        <v>7009743</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2312,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127054783</v>
+        <v>127054778</v>
       </c>
       <c r="B19" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444045</v>
+        <v>443693</v>
       </c>
       <c r="R19" t="n">
-        <v>7010128</v>
+        <v>7009697</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127054770</v>
+        <v>127054779</v>
       </c>
       <c r="B22" t="n">
-        <v>92027</v>
+        <v>91626</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443778</v>
+        <v>443684</v>
       </c>
       <c r="R22" t="n">
-        <v>7009721</v>
+        <v>7009641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2706,6 +2706,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,32 +2737,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127054789</v>
+        <v>127054770</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>92027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,7 +2772,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443770</v>
+        <v>443778</v>
       </c>
       <c r="R23" t="n">
         <v>7009721</v>
@@ -2829,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127054779</v>
+        <v>127054789</v>
       </c>
       <c r="B24" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443684</v>
+        <v>443770</v>
       </c>
       <c r="R24" t="n">
-        <v>7009641</v>
+        <v>7009721</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2900,11 +2905,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127054764</v>
+        <v>127054796</v>
       </c>
       <c r="B28" t="n">
-        <v>91330</v>
+        <v>92000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444040</v>
+        <v>444064</v>
       </c>
       <c r="R28" t="n">
-        <v>7010094</v>
+        <v>7010051</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127054796</v>
+        <v>127054764</v>
       </c>
       <c r="B29" t="n">
-        <v>92000</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444064</v>
+        <v>444040</v>
       </c>
       <c r="R29" t="n">
-        <v>7010051</v>
+        <v>7010094</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127171733</v>
+        <v>127171772</v>
       </c>
       <c r="B38" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4210,21 +4210,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443799</v>
+        <v>443665</v>
       </c>
       <c r="R38" t="n">
-        <v>7009908</v>
+        <v>7009633</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127171772</v>
+        <v>127171733</v>
       </c>
       <c r="B39" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443665</v>
+        <v>443799</v>
       </c>
       <c r="R39" t="n">
-        <v>7009633</v>
+        <v>7009908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127171789</v>
+        <v>127171750</v>
       </c>
       <c r="B42" t="n">
-        <v>91344</v>
+        <v>75140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443942</v>
+        <v>443811</v>
       </c>
       <c r="R42" t="n">
-        <v>7010153</v>
+        <v>7009946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127171750</v>
+        <v>127171789</v>
       </c>
       <c r="B43" t="n">
-        <v>75140</v>
+        <v>91344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443811</v>
+        <v>443942</v>
       </c>
       <c r="R43" t="n">
-        <v>7009946</v>
+        <v>7010153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127171757</v>
+        <v>127171739</v>
       </c>
       <c r="B44" t="n">
-        <v>91784</v>
+        <v>92027</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443706</v>
+        <v>444045</v>
       </c>
       <c r="R44" t="n">
-        <v>7009637</v>
+        <v>7010113</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127171797</v>
+        <v>127171778</v>
       </c>
       <c r="B45" t="n">
-        <v>91348</v>
+        <v>79177</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443694</v>
+        <v>443849</v>
       </c>
       <c r="R45" t="n">
-        <v>7009702</v>
+        <v>7010007</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4975,32 +4975,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127171739</v>
+        <v>127171757</v>
       </c>
       <c r="B46" t="n">
-        <v>92027</v>
+        <v>91784</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444045</v>
+        <v>443706</v>
       </c>
       <c r="R46" t="n">
-        <v>7010113</v>
+        <v>7009637</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127171778</v>
+        <v>127171748</v>
       </c>
       <c r="B47" t="n">
-        <v>79177</v>
+        <v>75140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443849</v>
+        <v>444052</v>
       </c>
       <c r="R47" t="n">
-        <v>7010007</v>
+        <v>7010134</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,32 +5169,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127171748</v>
+        <v>127171797</v>
       </c>
       <c r="B48" t="n">
-        <v>75140</v>
+        <v>91348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444052</v>
+        <v>443694</v>
       </c>
       <c r="R48" t="n">
-        <v>7010134</v>
+        <v>7009702</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5266,10 +5266,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127171792</v>
+        <v>127171759</v>
       </c>
       <c r="B49" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5277,21 +5277,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443662</v>
+        <v>443657</v>
       </c>
       <c r="R49" t="n">
-        <v>7009632</v>
+        <v>7009838</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5363,10 +5363,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127171759</v>
+        <v>127171792</v>
       </c>
       <c r="B50" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5374,21 +5374,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443657</v>
+        <v>443662</v>
       </c>
       <c r="R50" t="n">
-        <v>7009838</v>
+        <v>7009632</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5848,45 +5848,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127171774</v>
+        <v>127171746</v>
       </c>
       <c r="B55" t="n">
-        <v>79177</v>
+        <v>57658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1249</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443612</v>
+        <v>443702</v>
       </c>
       <c r="R55" t="n">
-        <v>7009871</v>
+        <v>7009658</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5945,10 +5957,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127171747</v>
+        <v>127171774</v>
       </c>
       <c r="B56" t="n">
-        <v>75140</v>
+        <v>79177</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5956,21 +5968,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5980,10 +5992,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443962</v>
+        <v>443612</v>
       </c>
       <c r="R56" t="n">
-        <v>7009915</v>
+        <v>7009871</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6042,57 +6054,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127171746</v>
+        <v>127171747</v>
       </c>
       <c r="B57" t="n">
-        <v>57658</v>
+        <v>75140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6486</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443702</v>
+        <v>443962</v>
       </c>
       <c r="R57" t="n">
-        <v>7009658</v>
+        <v>7009915</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6248,10 +6248,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127171727</v>
+        <v>127171771</v>
       </c>
       <c r="B59" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6259,21 +6259,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443530</v>
+        <v>443696</v>
       </c>
       <c r="R59" t="n">
-        <v>7009894</v>
+        <v>7009640</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6345,10 +6345,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127171771</v>
+        <v>127171799</v>
       </c>
       <c r="B60" t="n">
-        <v>91626</v>
+        <v>82859</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6356,21 +6356,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443696</v>
+        <v>444014</v>
       </c>
       <c r="R60" t="n">
-        <v>7009640</v>
+        <v>7010157</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6442,10 +6442,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171799</v>
+        <v>127171727</v>
       </c>
       <c r="B61" t="n">
-        <v>82859</v>
+        <v>91330</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6453,21 +6453,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444014</v>
+        <v>443530</v>
       </c>
       <c r="R61" t="n">
-        <v>7010157</v>
+        <v>7009894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6539,32 +6539,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171791</v>
+        <v>127171775</v>
       </c>
       <c r="B62" t="n">
-        <v>91344</v>
+        <v>79177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443740</v>
+        <v>443959</v>
       </c>
       <c r="R62" t="n">
-        <v>7009800</v>
+        <v>7009897</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6636,10 +6636,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127171775</v>
+        <v>127171749</v>
       </c>
       <c r="B63" t="n">
-        <v>79177</v>
+        <v>75140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6647,21 +6647,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443959</v>
+        <v>443940</v>
       </c>
       <c r="R63" t="n">
-        <v>7009897</v>
+        <v>7010148</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6830,32 +6830,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127171749</v>
+        <v>127171791</v>
       </c>
       <c r="B65" t="n">
-        <v>75140</v>
+        <v>91344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443940</v>
+        <v>443740</v>
       </c>
       <c r="R65" t="n">
-        <v>7010148</v>
+        <v>7009800</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127171732</v>
+        <v>127171755</v>
       </c>
       <c r="B72" t="n">
-        <v>91330</v>
+        <v>80122</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7520,21 +7520,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443830</v>
+        <v>443873</v>
       </c>
       <c r="R72" t="n">
-        <v>7010003</v>
+        <v>7009800</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7606,10 +7606,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127171766</v>
+        <v>127171790</v>
       </c>
       <c r="B73" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7617,21 +7617,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443739</v>
+        <v>443779</v>
       </c>
       <c r="R73" t="n">
-        <v>7009690</v>
+        <v>7009833</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7703,10 +7703,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127171765</v>
+        <v>127171735</v>
       </c>
       <c r="B74" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7714,21 +7714,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443801</v>
+        <v>443742</v>
       </c>
       <c r="R74" t="n">
-        <v>7009898</v>
+        <v>7009693</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7800,10 +7800,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127171755</v>
+        <v>127171732</v>
       </c>
       <c r="B75" t="n">
-        <v>80122</v>
+        <v>91330</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7811,21 +7811,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7835,10 +7835,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443873</v>
+        <v>443830</v>
       </c>
       <c r="R75" t="n">
-        <v>7009800</v>
+        <v>7010003</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7897,32 +7897,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127171790</v>
+        <v>127171753</v>
       </c>
       <c r="B76" t="n">
-        <v>91344</v>
+        <v>75140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443779</v>
+        <v>443701</v>
       </c>
       <c r="R76" t="n">
-        <v>7009833</v>
+        <v>7009672</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7994,10 +7994,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127171735</v>
+        <v>127171782</v>
       </c>
       <c r="B77" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443742</v>
+        <v>443853</v>
       </c>
       <c r="R77" t="n">
-        <v>7009693</v>
+        <v>7009796</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8091,32 +8091,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127171753</v>
+        <v>127171766</v>
       </c>
       <c r="B78" t="n">
-        <v>75140</v>
+        <v>91626</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8126,10 +8126,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443701</v>
+        <v>443739</v>
       </c>
       <c r="R78" t="n">
-        <v>7009672</v>
+        <v>7009690</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8188,10 +8188,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127171782</v>
+        <v>127171765</v>
       </c>
       <c r="B79" t="n">
-        <v>80121</v>
+        <v>91626</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8199,21 +8199,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443853</v>
+        <v>443801</v>
       </c>
       <c r="R79" t="n">
-        <v>7009796</v>
+        <v>7009898</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8479,10 +8479,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127171793</v>
+        <v>127171761</v>
       </c>
       <c r="B82" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8490,21 +8490,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443669</v>
+        <v>444054</v>
       </c>
       <c r="R82" t="n">
-        <v>7009641</v>
+        <v>7010086</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8576,32 +8576,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127171738</v>
+        <v>127171776</v>
       </c>
       <c r="B83" t="n">
-        <v>92027</v>
+        <v>79177</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8611,10 +8611,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444071</v>
+        <v>444054</v>
       </c>
       <c r="R83" t="n">
-        <v>7010048</v>
+        <v>7010026</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8673,32 +8673,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127171776</v>
+        <v>127171738</v>
       </c>
       <c r="B84" t="n">
-        <v>79177</v>
+        <v>92027</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444054</v>
+        <v>444071</v>
       </c>
       <c r="R84" t="n">
-        <v>7010026</v>
+        <v>7010048</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127171761</v>
+        <v>127171793</v>
       </c>
       <c r="B85" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8781,21 +8781,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444054</v>
+        <v>443669</v>
       </c>
       <c r="R85" t="n">
-        <v>7010086</v>
+        <v>7009641</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9255,32 +9255,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127171768</v>
+        <v>127171779</v>
       </c>
       <c r="B90" t="n">
-        <v>91626</v>
+        <v>79177</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>1249</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443694</v>
+        <v>443829</v>
       </c>
       <c r="R90" t="n">
-        <v>7009672</v>
+        <v>7010003</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9352,32 +9352,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127171779</v>
+        <v>127171768</v>
       </c>
       <c r="B91" t="n">
-        <v>79177</v>
+        <v>91626</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443829</v>
+        <v>443694</v>
       </c>
       <c r="R91" t="n">
-        <v>7010003</v>
+        <v>7009672</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9449,10 +9449,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127171783</v>
+        <v>127171788</v>
       </c>
       <c r="B92" t="n">
-        <v>80121</v>
+        <v>91344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9460,21 +9460,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9484,10 +9484,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443909</v>
+        <v>443538</v>
       </c>
       <c r="R92" t="n">
-        <v>7009801</v>
+        <v>7009933</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9546,10 +9546,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127171788</v>
+        <v>127171783</v>
       </c>
       <c r="B93" t="n">
-        <v>91344</v>
+        <v>80121</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9557,21 +9557,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9581,10 +9581,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443538</v>
+        <v>443909</v>
       </c>
       <c r="R93" t="n">
-        <v>7009933</v>
+        <v>7009801</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9643,10 +9643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127171780</v>
+        <v>127171729</v>
       </c>
       <c r="B94" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9654,21 +9654,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443594</v>
+        <v>444018</v>
       </c>
       <c r="R94" t="n">
-        <v>7009896</v>
+        <v>7010176</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127171729</v>
+        <v>127171780</v>
       </c>
       <c r="B95" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9751,21 +9751,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444018</v>
+        <v>443594</v>
       </c>
       <c r="R95" t="n">
-        <v>7010176</v>
+        <v>7009896</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9934,32 +9934,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127171731</v>
+        <v>127171802</v>
       </c>
       <c r="B97" t="n">
-        <v>91330</v>
+        <v>80156</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443827</v>
+        <v>443853</v>
       </c>
       <c r="R97" t="n">
-        <v>7009979</v>
+        <v>7009799</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10031,32 +10031,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127171802</v>
+        <v>127171731</v>
       </c>
       <c r="B98" t="n">
-        <v>80156</v>
+        <v>91330</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443853</v>
+        <v>443827</v>
       </c>
       <c r="R98" t="n">
-        <v>7009799</v>
+        <v>7009979</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10128,32 +10128,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127171745</v>
+        <v>127171773</v>
       </c>
       <c r="B99" t="n">
-        <v>80150</v>
+        <v>91699</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443708</v>
+        <v>443696</v>
       </c>
       <c r="R99" t="n">
-        <v>7009649</v>
+        <v>7009647</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10225,32 +10225,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127171773</v>
+        <v>127171745</v>
       </c>
       <c r="B100" t="n">
-        <v>91699</v>
+        <v>80150</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1506</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443696</v>
+        <v>443708</v>
       </c>
       <c r="R100" t="n">
-        <v>7009647</v>
+        <v>7009649</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10322,32 +10322,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127171726</v>
+        <v>127171764</v>
       </c>
       <c r="B101" t="n">
-        <v>91295</v>
+        <v>91626</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443752</v>
+        <v>443826</v>
       </c>
       <c r="R101" t="n">
-        <v>7009813</v>
+        <v>7009951</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10516,32 +10516,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127171764</v>
+        <v>127171726</v>
       </c>
       <c r="B103" t="n">
-        <v>91626</v>
+        <v>91295</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10551,10 +10551,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443826</v>
+        <v>443752</v>
       </c>
       <c r="R103" t="n">
-        <v>7009951</v>
+        <v>7009813</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11001,45 +11001,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127302675</v>
+        <v>127303918</v>
       </c>
       <c r="B108" t="n">
-        <v>91348</v>
+        <v>97474</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>222741</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443823</v>
+        <v>443944</v>
       </c>
       <c r="R108" t="n">
-        <v>7010119</v>
+        <v>7010169</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11069,9 +11069,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11086,12 +11096,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11195,10 +11205,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127302649</v>
+        <v>127302642</v>
       </c>
       <c r="B110" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11206,34 +11216,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444329</v>
+        <v>444096</v>
       </c>
       <c r="R110" t="n">
-        <v>7010232</v>
+        <v>7010088</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11266,6 +11284,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11292,10 +11315,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127302642</v>
+        <v>127302675</v>
       </c>
       <c r="B111" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11303,42 +11326,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444096</v>
+        <v>443823</v>
       </c>
       <c r="R111" t="n">
-        <v>7010088</v>
+        <v>7010119</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11371,11 +11386,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11402,45 +11412,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127303918</v>
+        <v>127302649</v>
       </c>
       <c r="B112" t="n">
-        <v>97474</v>
+        <v>91626</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222741</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443944</v>
+        <v>444329</v>
       </c>
       <c r="R112" t="n">
-        <v>7010169</v>
+        <v>7010232</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11470,19 +11480,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>18:28</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11497,12 +11497,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12024,10 +12024,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127303924</v>
+        <v>127302641</v>
       </c>
       <c r="B118" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12035,34 +12035,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443651</v>
+        <v>444203</v>
       </c>
       <c r="R118" t="n">
-        <v>7010015</v>
+        <v>7010082</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12092,19 +12092,14 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12115,41 +12110,26 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127302641</v>
+        <v>127303924</v>
       </c>
       <c r="B119" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12157,34 +12137,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444203</v>
+        <v>443651</v>
       </c>
       <c r="R119" t="n">
-        <v>7010082</v>
+        <v>7010015</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12214,14 +12194,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12232,26 +12217,41 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127302657</v>
+        <v>127302637</v>
       </c>
       <c r="B120" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12259,21 +12259,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443766</v>
+        <v>443618</v>
       </c>
       <c r="R120" t="n">
-        <v>7010076</v>
+        <v>7009972</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12345,10 +12345,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127302637</v>
+        <v>127302676</v>
       </c>
       <c r="B121" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12356,21 +12356,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443618</v>
+        <v>443737</v>
       </c>
       <c r="R121" t="n">
-        <v>7009972</v>
+        <v>7009850</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127302661</v>
+        <v>127302657</v>
       </c>
       <c r="B122" t="n">
         <v>91626</v>
@@ -12477,10 +12477,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443698</v>
+        <v>443766</v>
       </c>
       <c r="R122" t="n">
-        <v>7009876</v>
+        <v>7010076</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127302676</v>
+        <v>127302661</v>
       </c>
       <c r="B123" t="n">
-        <v>91348</v>
+        <v>91626</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12550,21 +12550,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443737</v>
+        <v>443698</v>
       </c>
       <c r="R123" t="n">
-        <v>7009850</v>
+        <v>7009876</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12636,10 +12636,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127302629</v>
+        <v>127299819</v>
       </c>
       <c r="B124" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12647,34 +12647,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443988</v>
+        <v>444269</v>
       </c>
       <c r="R124" t="n">
-        <v>7010097</v>
+        <v>7010299</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12721,57 +12721,57 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127303905</v>
+        <v>127299818</v>
       </c>
       <c r="B125" t="n">
-        <v>75064</v>
+        <v>75140</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1460</v>
+        <v>6486</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444019</v>
+        <v>444299</v>
       </c>
       <c r="R125" t="n">
-        <v>7010089</v>
+        <v>7010246</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12801,21 +12801,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -12824,76 +12814,61 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127303899</v>
+        <v>127299830</v>
       </c>
       <c r="B126" t="n">
-        <v>79018</v>
+        <v>92000</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444289</v>
+        <v>444057</v>
       </c>
       <c r="R126" t="n">
-        <v>7010247</v>
+        <v>7010071</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12923,19 +12898,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>20:30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -12950,57 +12915,57 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127299830</v>
+        <v>127302629</v>
       </c>
       <c r="B127" t="n">
-        <v>92000</v>
+        <v>91330</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444057</v>
+        <v>443988</v>
       </c>
       <c r="R127" t="n">
-        <v>7010071</v>
+        <v>7010097</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13047,22 +13012,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127299819</v>
+        <v>127303905</v>
       </c>
       <c r="B128" t="n">
-        <v>91626</v>
+        <v>75064</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13070,34 +13035,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>658</v>
+        <v>1460</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444269</v>
+        <v>444019</v>
       </c>
       <c r="R128" t="n">
-        <v>7010299</v>
+        <v>7010089</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13127,11 +13092,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13140,61 +13115,76 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127299818</v>
+        <v>127303899</v>
       </c>
       <c r="B129" t="n">
-        <v>75140</v>
+        <v>79018</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444299</v>
+        <v>444289</v>
       </c>
       <c r="R129" t="n">
-        <v>7010246</v>
+        <v>7010247</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13224,9 +13214,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13241,22 +13241,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127303913</v>
+        <v>127302634</v>
       </c>
       <c r="B130" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13264,34 +13264,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443984</v>
+        <v>443749</v>
       </c>
       <c r="R130" t="n">
-        <v>7010138</v>
+        <v>7010018</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13321,21 +13321,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -13344,41 +13334,26 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127302634</v>
+        <v>127303913</v>
       </c>
       <c r="B131" t="n">
-        <v>91330</v>
+        <v>75064</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13386,34 +13361,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443749</v>
+        <v>443984</v>
       </c>
       <c r="R131" t="n">
-        <v>7010018</v>
+        <v>7010138</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13443,11 +13418,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -13456,61 +13441,76 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127303906</v>
+        <v>127302669</v>
       </c>
       <c r="B132" t="n">
-        <v>79104</v>
+        <v>91344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6450</v>
+        <v>1204</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444000</v>
+        <v>443852</v>
       </c>
       <c r="R132" t="n">
-        <v>7010124</v>
+        <v>7009880</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13540,21 +13540,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -13563,76 +13553,61 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127302669</v>
+        <v>127303916</v>
       </c>
       <c r="B133" t="n">
-        <v>91344</v>
+        <v>75140</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443852</v>
+        <v>443956</v>
       </c>
       <c r="R133" t="n">
-        <v>7009880</v>
+        <v>7010157</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13662,11 +13637,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -13675,61 +13660,76 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127302660</v>
+        <v>127303906</v>
       </c>
       <c r="B134" t="n">
-        <v>91626</v>
+        <v>79104</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>658</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443679</v>
+        <v>444000</v>
       </c>
       <c r="R134" t="n">
-        <v>7009872</v>
+        <v>7010124</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13759,11 +13759,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -13772,61 +13782,76 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127303916</v>
+        <v>127302660</v>
       </c>
       <c r="B135" t="n">
-        <v>75140</v>
+        <v>91626</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>443956</v>
+        <v>443679</v>
       </c>
       <c r="R135" t="n">
-        <v>7010157</v>
+        <v>7009872</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13856,21 +13881,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -13879,31 +13894,16 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14007,10 +14007,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127302666</v>
+        <v>127302668</v>
       </c>
       <c r="B137" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14018,21 +14018,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14042,10 +14042,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443769</v>
+        <v>443816</v>
       </c>
       <c r="R137" t="n">
-        <v>7010089</v>
+        <v>7009788</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14104,7 +14104,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127302668</v>
+        <v>127302670</v>
       </c>
       <c r="B138" t="n">
         <v>91344</v>
@@ -14139,10 +14139,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443816</v>
+        <v>444114</v>
       </c>
       <c r="R138" t="n">
-        <v>7009788</v>
+        <v>7010064</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14201,10 +14201,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302670</v>
+        <v>127302666</v>
       </c>
       <c r="B139" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14212,21 +14212,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14236,10 +14236,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444114</v>
+        <v>443769</v>
       </c>
       <c r="R139" t="n">
-        <v>7010064</v>
+        <v>7010089</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14507,10 +14507,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127302646</v>
+        <v>127302671</v>
       </c>
       <c r="B142" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14518,21 +14518,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443843</v>
+        <v>443664</v>
       </c>
       <c r="R142" t="n">
-        <v>7009837</v>
+        <v>7009683</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14604,10 +14604,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127302671</v>
+        <v>127302646</v>
       </c>
       <c r="B143" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14615,21 +14615,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>443664</v>
+        <v>443843</v>
       </c>
       <c r="R143" t="n">
-        <v>7009683</v>
+        <v>7009837</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15328,10 +15328,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127302648</v>
+        <v>127299824</v>
       </c>
       <c r="B150" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15339,34 +15339,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>444005</v>
+        <v>444076</v>
       </c>
       <c r="R150" t="n">
-        <v>7009910</v>
+        <v>7010048</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15413,22 +15413,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127299824</v>
+        <v>127302643</v>
       </c>
       <c r="B151" t="n">
-        <v>91344</v>
+        <v>57661</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15436,34 +15436,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>444076</v>
+        <v>443735</v>
       </c>
       <c r="R151" t="n">
-        <v>7010048</v>
+        <v>7009851</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15498,6 +15506,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -15510,22 +15523,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127302643</v>
+        <v>127302648</v>
       </c>
       <c r="B152" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15533,42 +15546,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443735</v>
+        <v>444005</v>
       </c>
       <c r="R152" t="n">
-        <v>7009851</v>
+        <v>7009910</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15601,11 +15606,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127299813</v>
+        <v>127303930</v>
       </c>
       <c r="B153" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15643,34 +15643,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>444303</v>
+        <v>443689</v>
       </c>
       <c r="R153" t="n">
-        <v>7010251</v>
+        <v>7009719</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15700,11 +15700,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -15713,16 +15723,31 @@
       </c>
       <c r="AG153" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -15826,10 +15851,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127303930</v>
+        <v>127299813</v>
       </c>
       <c r="B155" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15837,34 +15862,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443689</v>
+        <v>444303</v>
       </c>
       <c r="R155" t="n">
-        <v>7009719</v>
+        <v>7010251</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15894,21 +15919,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -15917,31 +15932,16 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -16046,7 +16046,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127302652</v>
+        <v>127299821</v>
       </c>
       <c r="B157" t="n">
         <v>91626</v>
@@ -16077,14 +16077,14 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443999</v>
+        <v>444255</v>
       </c>
       <c r="R157" t="n">
-        <v>7010076</v>
+        <v>7010318</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16131,19 +16131,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127303932</v>
+        <v>127299814</v>
       </c>
       <c r="B158" t="n">
         <v>91330</v>
@@ -16174,14 +16174,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443689</v>
+        <v>444084</v>
       </c>
       <c r="R158" t="n">
-        <v>7009719</v>
+        <v>7010048</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16211,21 +16211,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16234,76 +16224,61 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127302664</v>
+        <v>127303932</v>
       </c>
       <c r="B159" t="n">
-        <v>79177</v>
+        <v>91330</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443777</v>
+        <v>443689</v>
       </c>
       <c r="R159" t="n">
-        <v>7010051</v>
+        <v>7009719</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16333,11 +16308,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -16346,16 +16331,31 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16484,45 +16484,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127299821</v>
+        <v>127302664</v>
       </c>
       <c r="B161" t="n">
-        <v>91626</v>
+        <v>79177</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>658</v>
+        <v>1249</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>444255</v>
+        <v>443777</v>
       </c>
       <c r="R161" t="n">
-        <v>7010318</v>
+        <v>7010051</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16569,22 +16569,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127299814</v>
+        <v>127302652</v>
       </c>
       <c r="B162" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16592,34 +16592,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>444084</v>
+        <v>443999</v>
       </c>
       <c r="R162" t="n">
-        <v>7010048</v>
+        <v>7010076</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16666,22 +16666,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127299827</v>
+        <v>127302630</v>
       </c>
       <c r="B163" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16689,34 +16689,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>444241</v>
+        <v>443979</v>
       </c>
       <c r="R163" t="n">
-        <v>7010317</v>
+        <v>7010134</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16763,44 +16763,44 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127302630</v>
+        <v>127302645</v>
       </c>
       <c r="B164" t="n">
-        <v>91330</v>
+        <v>91784</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16810,10 +16810,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>443979</v>
+        <v>443997</v>
       </c>
       <c r="R164" t="n">
-        <v>7010134</v>
+        <v>7010102</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16854,6 +16854,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -16994,45 +16995,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127302645</v>
+        <v>127299827</v>
       </c>
       <c r="B166" t="n">
-        <v>91784</v>
+        <v>91348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>443997</v>
+        <v>444241</v>
       </c>
       <c r="R166" t="n">
-        <v>7010102</v>
+        <v>7010317</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17073,19 +17074,18 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -17282,10 +17282,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127302628</v>
+        <v>127302678</v>
       </c>
       <c r="B169" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17293,21 +17293,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17317,10 +17317,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443999</v>
+        <v>443705</v>
       </c>
       <c r="R169" t="n">
-        <v>7010076</v>
+        <v>7009844</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17379,45 +17379,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127302678</v>
+        <v>127303912</v>
       </c>
       <c r="B170" t="n">
-        <v>91348</v>
+        <v>75140</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>443705</v>
+        <v>443984</v>
       </c>
       <c r="R170" t="n">
-        <v>7009844</v>
+        <v>7010138</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17447,9 +17447,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17464,57 +17474,57 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127303912</v>
+        <v>127302628</v>
       </c>
       <c r="B171" t="n">
-        <v>75140</v>
+        <v>91330</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6486</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>443984</v>
+        <v>443999</v>
       </c>
       <c r="R171" t="n">
-        <v>7010138</v>
+        <v>7010076</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17544,19 +17554,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>19:01</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>19:01</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17571,22 +17571,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127299822</v>
+        <v>127302651</v>
       </c>
       <c r="B172" t="n">
-        <v>80121</v>
+        <v>91626</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17594,34 +17594,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>444113</v>
+        <v>444007</v>
       </c>
       <c r="R172" t="n">
-        <v>7010093</v>
+        <v>7010058</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17668,22 +17668,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127302673</v>
+        <v>127299822</v>
       </c>
       <c r="B173" t="n">
-        <v>91344</v>
+        <v>80121</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17691,34 +17691,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443884</v>
+        <v>444113</v>
       </c>
       <c r="R173" t="n">
-        <v>7010169</v>
+        <v>7010093</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17765,22 +17765,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302633</v>
+        <v>127302673</v>
       </c>
       <c r="B174" t="n">
-        <v>91330</v>
+        <v>91344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443747</v>
+        <v>443884</v>
       </c>
       <c r="R174" t="n">
-        <v>7010019</v>
+        <v>7010169</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17874,10 +17874,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127302651</v>
+        <v>127302633</v>
       </c>
       <c r="B175" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17885,21 +17885,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17909,10 +17909,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>444007</v>
+        <v>443747</v>
       </c>
       <c r="R175" t="n">
-        <v>7010058</v>
+        <v>7010019</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17971,10 +17971,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127299815</v>
+        <v>127302659</v>
       </c>
       <c r="B176" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17982,34 +17982,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>444084</v>
+        <v>443722</v>
       </c>
       <c r="R176" t="n">
-        <v>7010049</v>
+        <v>7010007</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18056,19 +18056,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127302659</v>
+        <v>127302653</v>
       </c>
       <c r="B177" t="n">
         <v>91626</v>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443722</v>
+        <v>443979</v>
       </c>
       <c r="R177" t="n">
-        <v>7010007</v>
+        <v>7010133</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127302653</v>
+        <v>127302654</v>
       </c>
       <c r="B178" t="n">
         <v>91626</v>
@@ -18200,10 +18200,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>443979</v>
+        <v>443964</v>
       </c>
       <c r="R178" t="n">
-        <v>7010133</v>
+        <v>7010137</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18262,7 +18262,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127302654</v>
+        <v>127303909</v>
       </c>
       <c r="B179" t="n">
         <v>91626</v>
@@ -18293,14 +18293,14 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443964</v>
+        <v>443991</v>
       </c>
       <c r="R179" t="n">
-        <v>7010137</v>
+        <v>7010145</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18330,11 +18330,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -18343,26 +18353,41 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127303909</v>
+        <v>127299815</v>
       </c>
       <c r="B180" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18370,34 +18395,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443991</v>
+        <v>444084</v>
       </c>
       <c r="R180" t="n">
-        <v>7010145</v>
+        <v>7010049</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18427,21 +18452,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
@@ -18450,31 +18465,16 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -19078,45 +19078,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127303925</v>
+        <v>127302624</v>
       </c>
       <c r="B187" t="n">
-        <v>79177</v>
+        <v>91330</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443627</v>
+        <v>444005</v>
       </c>
       <c r="R187" t="n">
-        <v>7009957</v>
+        <v>7009910</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19146,21 +19146,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -19169,38 +19159,23 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127302624</v>
+        <v>127303928</v>
       </c>
       <c r="B188" t="n">
         <v>91330</v>
@@ -19231,14 +19206,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>444005</v>
+        <v>443698</v>
       </c>
       <c r="R188" t="n">
-        <v>7009910</v>
+        <v>7009874</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19268,11 +19243,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
@@ -19281,48 +19266,63 @@
       </c>
       <c r="AG188" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127303928</v>
+        <v>127303925</v>
       </c>
       <c r="B189" t="n">
-        <v>91330</v>
+        <v>79177</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19332,10 +19332,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>443698</v>
+        <v>443627</v>
       </c>
       <c r="R189" t="n">
-        <v>7009874</v>
+        <v>7009957</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19367,7 +19367,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19613,10 +19613,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127302672</v>
+        <v>127302647</v>
       </c>
       <c r="B192" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19624,21 +19624,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19648,10 +19648,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443978</v>
+        <v>443989</v>
       </c>
       <c r="R192" t="n">
-        <v>7010133</v>
+        <v>7009901</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19710,10 +19710,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127302647</v>
+        <v>127302672</v>
       </c>
       <c r="B193" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19721,21 +19721,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19745,10 +19745,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443989</v>
+        <v>443978</v>
       </c>
       <c r="R193" t="n">
-        <v>7009901</v>
+        <v>7010133</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19929,45 +19929,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127311026</v>
+        <v>127311483</v>
       </c>
       <c r="B195" t="n">
-        <v>91626</v>
+        <v>92032</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443721</v>
+        <v>443711</v>
       </c>
       <c r="R195" t="n">
-        <v>7009852</v>
+        <v>7010048</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20026,7 +20026,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127311016</v>
+        <v>127311026</v>
       </c>
       <c r="B196" t="n">
         <v>91626</v>
@@ -20061,10 +20061,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443914</v>
+        <v>443721</v>
       </c>
       <c r="R196" t="n">
-        <v>7009959</v>
+        <v>7009852</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20123,7 +20123,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127311021</v>
+        <v>127311016</v>
       </c>
       <c r="B197" t="n">
         <v>91626</v>
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>444283</v>
+        <v>443914</v>
       </c>
       <c r="R197" t="n">
-        <v>7010242</v>
+        <v>7009959</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20220,45 +20220,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127311483</v>
+        <v>127311021</v>
       </c>
       <c r="B198" t="n">
-        <v>92032</v>
+        <v>91626</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>67</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Haratjärnen, Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>443711</v>
+        <v>444283</v>
       </c>
       <c r="R198" t="n">
-        <v>7010048</v>
+        <v>7010242</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20317,32 +20317,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127311006</v>
+        <v>127311003</v>
       </c>
       <c r="B199" t="n">
-        <v>75140</v>
+        <v>57503</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6486</v>
+        <v>102621</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>444031</v>
+        <v>443820</v>
       </c>
       <c r="R199" t="n">
-        <v>7010078</v>
+        <v>7009812</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20414,32 +20414,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127311003</v>
+        <v>127311006</v>
       </c>
       <c r="B200" t="n">
-        <v>57503</v>
+        <v>75140</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>102621</v>
+        <v>6486</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20449,10 +20449,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>443820</v>
+        <v>444031</v>
       </c>
       <c r="R200" t="n">
-        <v>7009812</v>
+        <v>7010078</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127311031</v>
+        <v>127311020</v>
       </c>
       <c r="B202" t="n">
-        <v>75064</v>
+        <v>91626</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20619,21 +20619,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>444124</v>
+        <v>444252</v>
       </c>
       <c r="R202" t="n">
-        <v>7010021</v>
+        <v>7010325</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20705,10 +20705,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127311020</v>
+        <v>127311031</v>
       </c>
       <c r="B203" t="n">
-        <v>91626</v>
+        <v>75064</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20716,21 +20716,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>658</v>
+        <v>1460</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>444252</v>
+        <v>444124</v>
       </c>
       <c r="R203" t="n">
-        <v>7010325</v>
+        <v>7010021</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20996,10 +20996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127311018</v>
+        <v>127310987</v>
       </c>
       <c r="B206" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21007,21 +21007,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21031,10 +21031,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>444250</v>
+        <v>443973</v>
       </c>
       <c r="R206" t="n">
-        <v>7010307</v>
+        <v>7010146</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21093,10 +21093,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127310987</v>
+        <v>127310997</v>
       </c>
       <c r="B207" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21104,34 +21104,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443973</v>
+        <v>443735</v>
       </c>
       <c r="R207" t="n">
-        <v>7010146</v>
+        <v>7009858</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21164,6 +21172,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21190,10 +21203,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127310997</v>
+        <v>127311018</v>
       </c>
       <c r="B208" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21201,42 +21214,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>443735</v>
+        <v>444250</v>
       </c>
       <c r="R208" t="n">
-        <v>7009858</v>
+        <v>7010307</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21269,11 +21274,6 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21397,32 +21397,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127311039</v>
+        <v>127311052</v>
       </c>
       <c r="B210" t="n">
-        <v>79177</v>
+        <v>79018</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21432,10 +21432,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443626</v>
+        <v>443874</v>
       </c>
       <c r="R210" t="n">
-        <v>7009924</v>
+        <v>7009953</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21494,10 +21494,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127311052</v>
+        <v>127311042</v>
       </c>
       <c r="B211" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21505,21 +21505,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21529,10 +21529,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>443874</v>
+        <v>443919</v>
       </c>
       <c r="R211" t="n">
-        <v>7009953</v>
+        <v>7010183</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21591,32 +21591,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127311042</v>
+        <v>127311039</v>
       </c>
       <c r="B212" t="n">
-        <v>80121</v>
+        <v>79177</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21626,10 +21626,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>443919</v>
+        <v>443626</v>
       </c>
       <c r="R212" t="n">
-        <v>7010183</v>
+        <v>7009924</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21688,32 +21688,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310989</v>
+        <v>127311037</v>
       </c>
       <c r="B213" t="n">
-        <v>91330</v>
+        <v>79177</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21723,10 +21723,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>443910</v>
+        <v>443844</v>
       </c>
       <c r="R213" t="n">
-        <v>7010191</v>
+        <v>7009886</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21785,10 +21785,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127311037</v>
+        <v>127311036</v>
       </c>
       <c r="B214" t="n">
-        <v>79177</v>
+        <v>91699</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21796,21 +21796,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1249</v>
+        <v>1506</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21820,10 +21820,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>443844</v>
+        <v>443694</v>
       </c>
       <c r="R214" t="n">
-        <v>7009886</v>
+        <v>7009882</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21882,32 +21882,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127311036</v>
+        <v>127311033</v>
       </c>
       <c r="B215" t="n">
-        <v>91699</v>
+        <v>75064</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1506</v>
+        <v>1460</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21917,10 +21917,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>443694</v>
+        <v>444055</v>
       </c>
       <c r="R215" t="n">
-        <v>7009882</v>
+        <v>7010052</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21979,10 +21979,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127311033</v>
+        <v>127310989</v>
       </c>
       <c r="B216" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21990,21 +21990,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22014,10 +22014,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>444055</v>
+        <v>443910</v>
       </c>
       <c r="R216" t="n">
-        <v>7010052</v>
+        <v>7010191</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22949,10 +22949,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127311030</v>
+        <v>127310986</v>
       </c>
       <c r="B226" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22960,21 +22960,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>444131</v>
+        <v>444046</v>
       </c>
       <c r="R226" t="n">
-        <v>7010038</v>
+        <v>7010063</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23046,10 +23046,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127311034</v>
+        <v>127311059</v>
       </c>
       <c r="B227" t="n">
-        <v>75064</v>
+        <v>88733</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23057,21 +23057,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1460</v>
+        <v>510</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23081,10 +23081,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>444026</v>
+        <v>444272</v>
       </c>
       <c r="R227" t="n">
-        <v>7010076</v>
+        <v>7010237</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23143,10 +23143,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127310986</v>
+        <v>127311022</v>
       </c>
       <c r="B228" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23154,21 +23154,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23178,10 +23178,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>444046</v>
+        <v>444108</v>
       </c>
       <c r="R228" t="n">
-        <v>7010063</v>
+        <v>7010040</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23240,10 +23240,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127311022</v>
+        <v>127311041</v>
       </c>
       <c r="B229" t="n">
-        <v>91626</v>
+        <v>80121</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23251,21 +23251,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>444108</v>
+        <v>444094</v>
       </c>
       <c r="R229" t="n">
-        <v>7010040</v>
+        <v>7010004</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127311059</v>
+        <v>127311030</v>
       </c>
       <c r="B230" t="n">
-        <v>88733</v>
+        <v>75064</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23348,21 +23348,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>510</v>
+        <v>1460</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23372,10 +23372,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>444272</v>
+        <v>444131</v>
       </c>
       <c r="R230" t="n">
-        <v>7010237</v>
+        <v>7010038</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23434,10 +23434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127311041</v>
+        <v>127311034</v>
       </c>
       <c r="B231" t="n">
-        <v>80121</v>
+        <v>75064</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23445,21 +23445,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444094</v>
+        <v>444026</v>
       </c>
       <c r="R231" t="n">
-        <v>7010004</v>
+        <v>7010076</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23628,10 +23628,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127311024</v>
+        <v>127311051</v>
       </c>
       <c r="B233" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23639,21 +23639,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23663,10 +23663,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>443987</v>
+        <v>443729</v>
       </c>
       <c r="R233" t="n">
-        <v>7010155</v>
+        <v>7009862</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23725,10 +23725,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127310988</v>
+        <v>127311050</v>
       </c>
       <c r="B234" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23736,21 +23736,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23760,10 +23760,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443937</v>
+        <v>443756</v>
       </c>
       <c r="R234" t="n">
-        <v>7010167</v>
+        <v>7010085</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23822,7 +23822,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127311025</v>
+        <v>127311024</v>
       </c>
       <c r="B235" t="n">
         <v>91626</v>
@@ -23857,10 +23857,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443634</v>
+        <v>443987</v>
       </c>
       <c r="R235" t="n">
-        <v>7009878</v>
+        <v>7010155</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23919,10 +23919,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127311050</v>
+        <v>127311025</v>
       </c>
       <c r="B236" t="n">
-        <v>91348</v>
+        <v>91626</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23930,21 +23930,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23954,10 +23954,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>443756</v>
+        <v>443634</v>
       </c>
       <c r="R236" t="n">
-        <v>7010085</v>
+        <v>7009878</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24016,10 +24016,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127311051</v>
+        <v>127310988</v>
       </c>
       <c r="B237" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24027,21 +24027,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24051,10 +24051,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>443729</v>
+        <v>443937</v>
       </c>
       <c r="R237" t="n">
-        <v>7009862</v>
+        <v>7010167</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24113,32 +24113,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127310994</v>
+        <v>127311004</v>
       </c>
       <c r="B238" t="n">
-        <v>91330</v>
+        <v>75140</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24148,10 +24148,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>443734</v>
+        <v>444086</v>
       </c>
       <c r="R238" t="n">
-        <v>7009841</v>
+        <v>7010102</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24210,10 +24210,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127311029</v>
+        <v>127310994</v>
       </c>
       <c r="B239" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24221,21 +24221,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24245,10 +24245,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>444127</v>
+        <v>443734</v>
       </c>
       <c r="R239" t="n">
-        <v>7010058</v>
+        <v>7009841</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24307,32 +24307,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127311004</v>
+        <v>127311029</v>
       </c>
       <c r="B240" t="n">
-        <v>75140</v>
+        <v>75064</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6486</v>
+        <v>1460</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24342,10 +24342,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>444086</v>
+        <v>444127</v>
       </c>
       <c r="R240" t="n">
-        <v>7010102</v>
+        <v>7010058</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24404,10 +24404,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127311023</v>
+        <v>127310991</v>
       </c>
       <c r="B241" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24415,21 +24415,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24439,10 +24439,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>444039</v>
+        <v>443609</v>
       </c>
       <c r="R241" t="n">
-        <v>7010073</v>
+        <v>7009974</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24501,10 +24501,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127310991</v>
+        <v>127311048</v>
       </c>
       <c r="B242" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24512,21 +24512,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24536,10 +24536,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>443609</v>
+        <v>444000</v>
       </c>
       <c r="R242" t="n">
-        <v>7009974</v>
+        <v>7009885</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24598,10 +24598,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127311053</v>
+        <v>127311023</v>
       </c>
       <c r="B243" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24609,21 +24609,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24633,10 +24633,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>443960</v>
+        <v>444039</v>
       </c>
       <c r="R243" t="n">
-        <v>7010126</v>
+        <v>7010073</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24695,10 +24695,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127311048</v>
+        <v>127311053</v>
       </c>
       <c r="B244" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24706,21 +24706,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -24730,10 +24730,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>444000</v>
+        <v>443960</v>
       </c>
       <c r="R244" t="n">
-        <v>7009885</v>
+        <v>7010126</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24889,10 +24889,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127311038</v>
+        <v>127311008</v>
       </c>
       <c r="B246" t="n">
-        <v>79177</v>
+        <v>75140</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -24900,21 +24900,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -24924,10 +24924,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>444108</v>
+        <v>443750</v>
       </c>
       <c r="R246" t="n">
-        <v>7010013</v>
+        <v>7010074</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -24986,10 +24986,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127311008</v>
+        <v>127311038</v>
       </c>
       <c r="B247" t="n">
-        <v>75140</v>
+        <v>79177</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24997,21 +24997,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25021,10 +25021,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>443750</v>
+        <v>444108</v>
       </c>
       <c r="R247" t="n">
-        <v>7010074</v>
+        <v>7010013</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25083,32 +25083,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127311013</v>
+        <v>127311044</v>
       </c>
       <c r="B248" t="n">
-        <v>91784</v>
+        <v>91326</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25118,10 +25118,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>443905</v>
+        <v>444128</v>
       </c>
       <c r="R248" t="n">
-        <v>7010167</v>
+        <v>7010081</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25180,32 +25180,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127311044</v>
+        <v>127311061</v>
       </c>
       <c r="B249" t="n">
-        <v>91326</v>
+        <v>92000</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1108</v>
+        <v>898</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>444128</v>
+        <v>444006</v>
       </c>
       <c r="R249" t="n">
-        <v>7010081</v>
+        <v>7010113</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25277,10 +25277,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127311061</v>
+        <v>127311013</v>
       </c>
       <c r="B250" t="n">
-        <v>92000</v>
+        <v>91784</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25288,21 +25288,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25312,10 +25312,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>444006</v>
+        <v>443905</v>
       </c>
       <c r="R250" t="n">
-        <v>7010113</v>
+        <v>7010167</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25471,10 +25471,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127311009</v>
+        <v>127310992</v>
       </c>
       <c r="B252" t="n">
-        <v>80122</v>
+        <v>91330</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25482,21 +25482,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25506,10 +25506,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>444133</v>
+        <v>443635</v>
       </c>
       <c r="R252" t="n">
-        <v>7010104</v>
+        <v>7009927</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25568,7 +25568,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127311010</v>
+        <v>127311009</v>
       </c>
       <c r="B253" t="n">
         <v>80122</v>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>443921</v>
+        <v>444133</v>
       </c>
       <c r="R253" t="n">
-        <v>7010190</v>
+        <v>7010104</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25665,32 +25665,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127311014</v>
+        <v>127311010</v>
       </c>
       <c r="B254" t="n">
-        <v>91784</v>
+        <v>80122</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -25700,10 +25700,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>443719</v>
+        <v>443921</v>
       </c>
       <c r="R254" t="n">
-        <v>7009858</v>
+        <v>7010190</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25762,32 +25762,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127310992</v>
+        <v>127311014</v>
       </c>
       <c r="B255" t="n">
-        <v>91330</v>
+        <v>91784</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -25797,10 +25797,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>443635</v>
+        <v>443719</v>
       </c>
       <c r="R255" t="n">
-        <v>7009927</v>
+        <v>7009858</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26247,32 +26247,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127311001</v>
+        <v>127311043</v>
       </c>
       <c r="B260" t="n">
-        <v>92032</v>
+        <v>80121</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26282,10 +26282,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>443716</v>
+        <v>443639</v>
       </c>
       <c r="R260" t="n">
-        <v>7010053</v>
+        <v>7010011</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26344,32 +26344,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127311043</v>
+        <v>127311001</v>
       </c>
       <c r="B261" t="n">
-        <v>80121</v>
+        <v>92032</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26379,10 +26379,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>443639</v>
+        <v>443716</v>
       </c>
       <c r="R261" t="n">
-        <v>7010011</v>
+        <v>7010053</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26441,7 +26441,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127063410</v>
+        <v>127063414</v>
       </c>
       <c r="B262" t="n">
         <v>57661</v>
@@ -26476,10 +26476,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>444171</v>
+        <v>444463</v>
       </c>
       <c r="R262" t="n">
-        <v>7010149</v>
+        <v>7010311</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -26543,7 +26543,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127063414</v>
+        <v>127063410</v>
       </c>
       <c r="B263" t="n">
         <v>57661</v>
@@ -26578,10 +26578,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>444463</v>
+        <v>444171</v>
       </c>
       <c r="R263" t="n">
-        <v>7010311</v>
+        <v>7010149</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26618,7 +26618,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD263" t="b">

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127171733</v>
+        <v>127171789</v>
       </c>
       <c r="B39" t="n">
-        <v>91330</v>
+        <v>91344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443799</v>
+        <v>443942</v>
       </c>
       <c r="R39" t="n">
-        <v>7009908</v>
+        <v>7010153</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127171795</v>
+        <v>127171733</v>
       </c>
       <c r="B40" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443763</v>
+        <v>443799</v>
       </c>
       <c r="R40" t="n">
-        <v>7009828</v>
+        <v>7009908</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127171794</v>
+        <v>127171795</v>
       </c>
       <c r="B41" t="n">
         <v>91348</v>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443868</v>
+        <v>443763</v>
       </c>
       <c r="R41" t="n">
-        <v>7009783</v>
+        <v>7009828</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127171750</v>
+        <v>127171794</v>
       </c>
       <c r="B42" t="n">
-        <v>75140</v>
+        <v>91348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443811</v>
+        <v>443868</v>
       </c>
       <c r="R42" t="n">
-        <v>7009946</v>
+        <v>7009783</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127171789</v>
+        <v>127171750</v>
       </c>
       <c r="B43" t="n">
-        <v>91344</v>
+        <v>75140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443942</v>
+        <v>443811</v>
       </c>
       <c r="R43" t="n">
-        <v>7010153</v>
+        <v>7009946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -7315,32 +7315,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127171769</v>
+        <v>127171744</v>
       </c>
       <c r="B70" t="n">
-        <v>91626</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443709</v>
+        <v>443782</v>
       </c>
       <c r="R70" t="n">
-        <v>7009666</v>
+        <v>7009804</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,32 +7412,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127171744</v>
+        <v>127171769</v>
       </c>
       <c r="B71" t="n">
-        <v>80150</v>
+        <v>91626</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443782</v>
+        <v>443709</v>
       </c>
       <c r="R71" t="n">
-        <v>7009804</v>
+        <v>7009666</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127171755</v>
+        <v>127171766</v>
       </c>
       <c r="B72" t="n">
-        <v>80122</v>
+        <v>91626</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7520,21 +7520,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443873</v>
+        <v>443739</v>
       </c>
       <c r="R72" t="n">
-        <v>7009800</v>
+        <v>7009690</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7606,10 +7606,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127171790</v>
+        <v>127171755</v>
       </c>
       <c r="B73" t="n">
-        <v>91344</v>
+        <v>80122</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7617,21 +7617,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443779</v>
+        <v>443873</v>
       </c>
       <c r="R73" t="n">
-        <v>7009833</v>
+        <v>7009800</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7703,10 +7703,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127171735</v>
+        <v>127171790</v>
       </c>
       <c r="B74" t="n">
-        <v>91330</v>
+        <v>91344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7714,21 +7714,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443742</v>
+        <v>443779</v>
       </c>
       <c r="R74" t="n">
-        <v>7009693</v>
+        <v>7009833</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7800,7 +7800,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127171732</v>
+        <v>127171735</v>
       </c>
       <c r="B75" t="n">
         <v>91330</v>
@@ -7835,10 +7835,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443830</v>
+        <v>443742</v>
       </c>
       <c r="R75" t="n">
-        <v>7010003</v>
+        <v>7009693</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7897,32 +7897,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127171753</v>
+        <v>127171732</v>
       </c>
       <c r="B76" t="n">
-        <v>75140</v>
+        <v>91330</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6486</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443701</v>
+        <v>443830</v>
       </c>
       <c r="R76" t="n">
-        <v>7009672</v>
+        <v>7010003</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8091,7 +8091,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127171766</v>
+        <v>127171765</v>
       </c>
       <c r="B78" t="n">
         <v>91626</v>
@@ -8126,10 +8126,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443739</v>
+        <v>443801</v>
       </c>
       <c r="R78" t="n">
-        <v>7009690</v>
+        <v>7009898</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8188,32 +8188,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127171765</v>
+        <v>127171753</v>
       </c>
       <c r="B79" t="n">
-        <v>91626</v>
+        <v>75140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443801</v>
+        <v>443701</v>
       </c>
       <c r="R79" t="n">
-        <v>7009898</v>
+        <v>7009672</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9643,7 +9643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127171729</v>
+        <v>127171728</v>
       </c>
       <c r="B94" t="n">
         <v>91330</v>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444018</v>
+        <v>443634</v>
       </c>
       <c r="R94" t="n">
-        <v>7010176</v>
+        <v>7009855</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127171780</v>
+        <v>127171729</v>
       </c>
       <c r="B95" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9751,21 +9751,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443594</v>
+        <v>444018</v>
       </c>
       <c r="R95" t="n">
-        <v>7009896</v>
+        <v>7010176</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9837,10 +9837,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127171728</v>
+        <v>127171780</v>
       </c>
       <c r="B96" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9848,21 +9848,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443634</v>
+        <v>443594</v>
       </c>
       <c r="R96" t="n">
-        <v>7009855</v>
+        <v>7009896</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127299820</v>
+        <v>127302625</v>
       </c>
       <c r="B116" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,34 +11836,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444007</v>
+        <v>444262</v>
       </c>
       <c r="R116" t="n">
-        <v>7010102</v>
+        <v>7010300</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11898,11 +11898,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>14 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11915,22 +11910,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127302625</v>
+        <v>127302641</v>
       </c>
       <c r="B117" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11938,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11962,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444262</v>
+        <v>444203</v>
       </c>
       <c r="R117" t="n">
-        <v>7010300</v>
+        <v>7010082</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11998,6 +11993,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12024,10 +12024,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127302641</v>
+        <v>127299820</v>
       </c>
       <c r="B118" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12035,34 +12035,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444203</v>
+        <v>444007</v>
       </c>
       <c r="R118" t="n">
-        <v>7010082</v>
+        <v>7010102</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12099,7 +12099,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>14 fruktkroppar</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12114,12 +12114,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12636,32 +12636,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127299819</v>
+        <v>127299830</v>
       </c>
       <c r="B124" t="n">
-        <v>91626</v>
+        <v>92000</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12671,10 +12671,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444269</v>
+        <v>444057</v>
       </c>
       <c r="R124" t="n">
-        <v>7010299</v>
+        <v>7010071</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12733,32 +12733,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127299818</v>
+        <v>127299819</v>
       </c>
       <c r="B125" t="n">
-        <v>75140</v>
+        <v>91626</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444299</v>
+        <v>444269</v>
       </c>
       <c r="R125" t="n">
-        <v>7010246</v>
+        <v>7010299</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12830,10 +12830,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127299830</v>
+        <v>127299818</v>
       </c>
       <c r="B126" t="n">
-        <v>92000</v>
+        <v>75140</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12841,21 +12841,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>898</v>
+        <v>6486</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12865,10 +12865,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444057</v>
+        <v>444299</v>
       </c>
       <c r="R126" t="n">
-        <v>7010071</v>
+        <v>7010246</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12927,10 +12927,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127302629</v>
+        <v>127303899</v>
       </c>
       <c r="B127" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12938,34 +12938,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443988</v>
+        <v>444289</v>
       </c>
       <c r="R127" t="n">
-        <v>7010097</v>
+        <v>7010247</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,9 +12995,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13012,22 +13022,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127303905</v>
+        <v>127302629</v>
       </c>
       <c r="B128" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13035,34 +13045,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444019</v>
+        <v>443988</v>
       </c>
       <c r="R128" t="n">
-        <v>7010089</v>
+        <v>7010097</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13092,21 +13102,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13115,41 +13115,26 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127303899</v>
+        <v>127303905</v>
       </c>
       <c r="B129" t="n">
-        <v>79018</v>
+        <v>75064</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13157,21 +13142,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13181,10 +13166,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444289</v>
+        <v>444019</v>
       </c>
       <c r="R129" t="n">
-        <v>7010247</v>
+        <v>7010089</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13216,7 +13201,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13226,7 +13211,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13237,6 +13222,21 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -13910,10 +13910,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127299816</v>
+        <v>127302668</v>
       </c>
       <c r="B136" t="n">
-        <v>91330</v>
+        <v>91344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13921,34 +13921,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444022</v>
+        <v>443816</v>
       </c>
       <c r="R136" t="n">
-        <v>7010055</v>
+        <v>7009788</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13995,19 +13995,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127302668</v>
+        <v>127302670</v>
       </c>
       <c r="B137" t="n">
         <v>91344</v>
@@ -14042,10 +14042,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443816</v>
+        <v>444114</v>
       </c>
       <c r="R137" t="n">
-        <v>7009788</v>
+        <v>7010064</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14104,10 +14104,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127302670</v>
+        <v>127302666</v>
       </c>
       <c r="B138" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14115,21 +14115,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14139,10 +14139,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444114</v>
+        <v>443769</v>
       </c>
       <c r="R138" t="n">
-        <v>7010064</v>
+        <v>7010089</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14201,10 +14201,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302666</v>
+        <v>127302658</v>
       </c>
       <c r="B139" t="n">
-        <v>91326</v>
+        <v>91626</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14212,21 +14212,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14236,10 +14236,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443769</v>
+        <v>443777</v>
       </c>
       <c r="R139" t="n">
-        <v>7010089</v>
+        <v>7010050</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14298,45 +14298,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127302658</v>
+        <v>127303920</v>
       </c>
       <c r="B140" t="n">
-        <v>91626</v>
+        <v>100536</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443777</v>
+        <v>443902</v>
       </c>
       <c r="R140" t="n">
-        <v>7010050</v>
+        <v>7010174</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14366,9 +14366,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14383,57 +14398,57 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127303920</v>
+        <v>127299816</v>
       </c>
       <c r="B141" t="n">
-        <v>100536</v>
+        <v>91330</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443902</v>
+        <v>444022</v>
       </c>
       <c r="R141" t="n">
-        <v>7010174</v>
+        <v>7010055</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14463,24 +14478,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14495,12 +14495,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15328,10 +15328,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127299824</v>
+        <v>127302643</v>
       </c>
       <c r="B150" t="n">
-        <v>91344</v>
+        <v>57661</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15339,34 +15339,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>444076</v>
+        <v>443735</v>
       </c>
       <c r="R150" t="n">
-        <v>7010048</v>
+        <v>7009851</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15401,6 +15409,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -15413,22 +15426,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127302643</v>
+        <v>127302648</v>
       </c>
       <c r="B151" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15436,42 +15449,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443735</v>
+        <v>444005</v>
       </c>
       <c r="R151" t="n">
-        <v>7009851</v>
+        <v>7009910</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15504,11 +15509,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15535,10 +15535,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127302648</v>
+        <v>127299824</v>
       </c>
       <c r="B152" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15546,34 +15546,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>444005</v>
+        <v>444076</v>
       </c>
       <c r="R152" t="n">
-        <v>7009910</v>
+        <v>7010048</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15620,12 +15620,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16046,45 +16046,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127299821</v>
+        <v>127302664</v>
       </c>
       <c r="B157" t="n">
-        <v>91626</v>
+        <v>79177</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>1249</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>444255</v>
+        <v>443777</v>
       </c>
       <c r="R157" t="n">
-        <v>7010318</v>
+        <v>7010051</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16131,12 +16131,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16240,10 +16240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127303932</v>
+        <v>127303915</v>
       </c>
       <c r="B159" t="n">
-        <v>91330</v>
+        <v>79099</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16251,21 +16251,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16275,10 +16275,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443689</v>
+        <v>443965</v>
       </c>
       <c r="R159" t="n">
-        <v>7009719</v>
+        <v>7010163</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16362,10 +16362,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127303915</v>
+        <v>127302652</v>
       </c>
       <c r="B160" t="n">
-        <v>79099</v>
+        <v>91626</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16373,34 +16373,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>283</v>
+        <v>658</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443965</v>
+        <v>443999</v>
       </c>
       <c r="R160" t="n">
-        <v>7010163</v>
+        <v>7010076</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16430,21 +16430,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -16453,76 +16443,61 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127302664</v>
+        <v>127299821</v>
       </c>
       <c r="B161" t="n">
-        <v>79177</v>
+        <v>91626</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443777</v>
+        <v>444255</v>
       </c>
       <c r="R161" t="n">
-        <v>7010051</v>
+        <v>7010318</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16569,22 +16544,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127302652</v>
+        <v>127303932</v>
       </c>
       <c r="B162" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16592,34 +16567,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443999</v>
+        <v>443689</v>
       </c>
       <c r="R162" t="n">
-        <v>7010076</v>
+        <v>7009719</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16649,11 +16624,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
@@ -16662,16 +16647,31 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17583,10 +17583,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127302651</v>
+        <v>127299822</v>
       </c>
       <c r="B172" t="n">
-        <v>91626</v>
+        <v>80121</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17594,34 +17594,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>444007</v>
+        <v>444113</v>
       </c>
       <c r="R172" t="n">
-        <v>7010058</v>
+        <v>7010093</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17668,22 +17668,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127299822</v>
+        <v>127302673</v>
       </c>
       <c r="B173" t="n">
-        <v>80121</v>
+        <v>91344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17691,34 +17691,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>444113</v>
+        <v>443884</v>
       </c>
       <c r="R173" t="n">
-        <v>7010093</v>
+        <v>7010169</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17765,22 +17765,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302673</v>
+        <v>127302633</v>
       </c>
       <c r="B174" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443884</v>
+        <v>443747</v>
       </c>
       <c r="R174" t="n">
-        <v>7010169</v>
+        <v>7010019</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17874,10 +17874,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127302633</v>
+        <v>127302651</v>
       </c>
       <c r="B175" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17885,21 +17885,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17909,10 +17909,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443747</v>
+        <v>444007</v>
       </c>
       <c r="R175" t="n">
-        <v>7010019</v>
+        <v>7010058</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17971,10 +17971,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127302659</v>
+        <v>127299815</v>
       </c>
       <c r="B176" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17982,34 +17982,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>443722</v>
+        <v>444084</v>
       </c>
       <c r="R176" t="n">
-        <v>7010007</v>
+        <v>7010049</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18056,19 +18056,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127302653</v>
+        <v>127302659</v>
       </c>
       <c r="B177" t="n">
         <v>91626</v>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443979</v>
+        <v>443722</v>
       </c>
       <c r="R177" t="n">
-        <v>7010133</v>
+        <v>7010007</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127302654</v>
+        <v>127302653</v>
       </c>
       <c r="B178" t="n">
         <v>91626</v>
@@ -18200,10 +18200,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>443964</v>
+        <v>443979</v>
       </c>
       <c r="R178" t="n">
-        <v>7010137</v>
+        <v>7010133</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18262,7 +18262,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127303909</v>
+        <v>127302654</v>
       </c>
       <c r="B179" t="n">
         <v>91626</v>
@@ -18293,14 +18293,14 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443991</v>
+        <v>443964</v>
       </c>
       <c r="R179" t="n">
-        <v>7010145</v>
+        <v>7010137</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18330,21 +18330,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -18353,41 +18343,26 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127299815</v>
+        <v>127303909</v>
       </c>
       <c r="B180" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18395,34 +18370,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>444084</v>
+        <v>443991</v>
       </c>
       <c r="R180" t="n">
-        <v>7010049</v>
+        <v>7010145</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18452,11 +18427,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
@@ -18465,16 +18450,31 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -19516,10 +19516,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127302663</v>
+        <v>127302672</v>
       </c>
       <c r="B191" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19527,21 +19527,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19551,10 +19551,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443671</v>
+        <v>443978</v>
       </c>
       <c r="R191" t="n">
-        <v>7009726</v>
+        <v>7010133</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19613,7 +19613,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127302647</v>
+        <v>127302663</v>
       </c>
       <c r="B192" t="n">
         <v>91626</v>
@@ -19648,10 +19648,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443989</v>
+        <v>443671</v>
       </c>
       <c r="R192" t="n">
-        <v>7009901</v>
+        <v>7009726</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19710,10 +19710,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127302672</v>
+        <v>127302647</v>
       </c>
       <c r="B193" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19721,21 +19721,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19745,10 +19745,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443978</v>
+        <v>443989</v>
       </c>
       <c r="R193" t="n">
-        <v>7010133</v>
+        <v>7009901</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20317,32 +20317,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127311003</v>
+        <v>127311006</v>
       </c>
       <c r="B199" t="n">
-        <v>57503</v>
+        <v>75140</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>102621</v>
+        <v>6486</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>443820</v>
+        <v>444031</v>
       </c>
       <c r="R199" t="n">
-        <v>7009812</v>
+        <v>7010078</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20414,32 +20414,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127311006</v>
+        <v>127311003</v>
       </c>
       <c r="B200" t="n">
-        <v>75140</v>
+        <v>57503</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6486</v>
+        <v>102621</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20449,10 +20449,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>444031</v>
+        <v>443820</v>
       </c>
       <c r="R200" t="n">
-        <v>7010078</v>
+        <v>7009812</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20511,10 +20511,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127310993</v>
+        <v>127311020</v>
       </c>
       <c r="B201" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20522,21 +20522,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>443730</v>
+        <v>444252</v>
       </c>
       <c r="R201" t="n">
-        <v>7009851</v>
+        <v>7010325</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127311020</v>
+        <v>127310993</v>
       </c>
       <c r="B202" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20619,21 +20619,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>444252</v>
+        <v>443730</v>
       </c>
       <c r="R202" t="n">
-        <v>7010325</v>
+        <v>7009851</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21397,32 +21397,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127311052</v>
+        <v>127311039</v>
       </c>
       <c r="B210" t="n">
-        <v>79018</v>
+        <v>79177</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21432,10 +21432,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443874</v>
+        <v>443626</v>
       </c>
       <c r="R210" t="n">
-        <v>7009953</v>
+        <v>7009924</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21494,10 +21494,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127311042</v>
+        <v>127311052</v>
       </c>
       <c r="B211" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21505,21 +21505,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21529,10 +21529,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>443919</v>
+        <v>443874</v>
       </c>
       <c r="R211" t="n">
-        <v>7010183</v>
+        <v>7009953</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21591,32 +21591,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127311039</v>
+        <v>127311042</v>
       </c>
       <c r="B212" t="n">
-        <v>79177</v>
+        <v>80121</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21626,10 +21626,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>443626</v>
+        <v>443919</v>
       </c>
       <c r="R212" t="n">
-        <v>7009924</v>
+        <v>7010183</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23046,10 +23046,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127311059</v>
+        <v>127311030</v>
       </c>
       <c r="B227" t="n">
-        <v>88733</v>
+        <v>75064</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23057,21 +23057,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>510</v>
+        <v>1460</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23081,10 +23081,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>444272</v>
+        <v>444131</v>
       </c>
       <c r="R227" t="n">
-        <v>7010237</v>
+        <v>7010038</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23143,10 +23143,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127311022</v>
+        <v>127311034</v>
       </c>
       <c r="B228" t="n">
-        <v>91626</v>
+        <v>75064</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23154,21 +23154,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>658</v>
+        <v>1460</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23178,10 +23178,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>444108</v>
+        <v>444026</v>
       </c>
       <c r="R228" t="n">
-        <v>7010040</v>
+        <v>7010076</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23240,10 +23240,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127311041</v>
+        <v>127311059</v>
       </c>
       <c r="B229" t="n">
-        <v>80121</v>
+        <v>88733</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23251,21 +23251,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>444094</v>
+        <v>444272</v>
       </c>
       <c r="R229" t="n">
-        <v>7010004</v>
+        <v>7010237</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127311030</v>
+        <v>127311022</v>
       </c>
       <c r="B230" t="n">
-        <v>75064</v>
+        <v>91626</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23348,21 +23348,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23372,10 +23372,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>444131</v>
+        <v>444108</v>
       </c>
       <c r="R230" t="n">
-        <v>7010038</v>
+        <v>7010040</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23434,10 +23434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127311034</v>
+        <v>127311041</v>
       </c>
       <c r="B231" t="n">
-        <v>75064</v>
+        <v>80121</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23445,21 +23445,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444026</v>
+        <v>444094</v>
       </c>
       <c r="R231" t="n">
-        <v>7010076</v>
+        <v>7010004</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24113,32 +24113,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127311004</v>
+        <v>127311029</v>
       </c>
       <c r="B238" t="n">
-        <v>75140</v>
+        <v>75064</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6486</v>
+        <v>1460</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24148,10 +24148,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>444086</v>
+        <v>444127</v>
       </c>
       <c r="R238" t="n">
-        <v>7010102</v>
+        <v>7010058</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24210,32 +24210,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127310994</v>
+        <v>127311004</v>
       </c>
       <c r="B239" t="n">
-        <v>91330</v>
+        <v>75140</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24245,10 +24245,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>443734</v>
+        <v>444086</v>
       </c>
       <c r="R239" t="n">
-        <v>7009841</v>
+        <v>7010102</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24307,10 +24307,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127311029</v>
+        <v>127310994</v>
       </c>
       <c r="B240" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24318,21 +24318,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24342,10 +24342,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>444127</v>
+        <v>443734</v>
       </c>
       <c r="R240" t="n">
-        <v>7010058</v>
+        <v>7009841</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24404,10 +24404,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127310991</v>
+        <v>127311053</v>
       </c>
       <c r="B241" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24415,21 +24415,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24439,10 +24439,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>443609</v>
+        <v>443960</v>
       </c>
       <c r="R241" t="n">
-        <v>7009974</v>
+        <v>7010126</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24501,32 +24501,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127311048</v>
+        <v>127311007</v>
       </c>
       <c r="B242" t="n">
-        <v>91348</v>
+        <v>75140</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24536,10 +24536,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>444000</v>
+        <v>443893</v>
       </c>
       <c r="R242" t="n">
-        <v>7009885</v>
+        <v>7010175</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24598,10 +24598,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127311023</v>
+        <v>127310991</v>
       </c>
       <c r="B243" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24609,21 +24609,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24633,10 +24633,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>444039</v>
+        <v>443609</v>
       </c>
       <c r="R243" t="n">
-        <v>7010073</v>
+        <v>7009974</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24695,10 +24695,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127311053</v>
+        <v>127311048</v>
       </c>
       <c r="B244" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24706,21 +24706,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -24730,10 +24730,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>443960</v>
+        <v>444000</v>
       </c>
       <c r="R244" t="n">
-        <v>7010126</v>
+        <v>7009885</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24792,32 +24792,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127311007</v>
+        <v>127311023</v>
       </c>
       <c r="B245" t="n">
-        <v>75140</v>
+        <v>91626</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -24827,10 +24827,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>443893</v>
+        <v>444039</v>
       </c>
       <c r="R245" t="n">
-        <v>7010175</v>
+        <v>7010073</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -24889,10 +24889,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127311008</v>
+        <v>127311038</v>
       </c>
       <c r="B246" t="n">
-        <v>75140</v>
+        <v>79177</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -24900,21 +24900,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -24924,10 +24924,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>443750</v>
+        <v>444108</v>
       </c>
       <c r="R246" t="n">
-        <v>7010074</v>
+        <v>7010013</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -24986,10 +24986,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127311038</v>
+        <v>127311008</v>
       </c>
       <c r="B247" t="n">
-        <v>79177</v>
+        <v>75140</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24997,21 +24997,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25021,10 +25021,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>444108</v>
+        <v>443750</v>
       </c>
       <c r="R247" t="n">
-        <v>7010013</v>
+        <v>7010074</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25083,32 +25083,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127311044</v>
+        <v>127311013</v>
       </c>
       <c r="B248" t="n">
-        <v>91326</v>
+        <v>91784</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25118,10 +25118,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>444128</v>
+        <v>443905</v>
       </c>
       <c r="R248" t="n">
-        <v>7010081</v>
+        <v>7010167</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25180,32 +25180,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127311061</v>
+        <v>127311044</v>
       </c>
       <c r="B249" t="n">
-        <v>92000</v>
+        <v>91326</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>898</v>
+        <v>1108</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>444006</v>
+        <v>444128</v>
       </c>
       <c r="R249" t="n">
-        <v>7010113</v>
+        <v>7010081</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25277,10 +25277,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127311013</v>
+        <v>127311061</v>
       </c>
       <c r="B250" t="n">
-        <v>91784</v>
+        <v>92000</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25288,21 +25288,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25312,10 +25312,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>443905</v>
+        <v>444006</v>
       </c>
       <c r="R250" t="n">
-        <v>7010167</v>
+        <v>7010113</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127171789</v>
+        <v>127171733</v>
       </c>
       <c r="B39" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443942</v>
+        <v>443799</v>
       </c>
       <c r="R39" t="n">
-        <v>7010153</v>
+        <v>7009908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127171733</v>
+        <v>127171795</v>
       </c>
       <c r="B40" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443799</v>
+        <v>443763</v>
       </c>
       <c r="R40" t="n">
-        <v>7009908</v>
+        <v>7009828</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127171795</v>
+        <v>127171794</v>
       </c>
       <c r="B41" t="n">
         <v>91348</v>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443763</v>
+        <v>443868</v>
       </c>
       <c r="R41" t="n">
-        <v>7009828</v>
+        <v>7009783</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127171794</v>
+        <v>127171750</v>
       </c>
       <c r="B42" t="n">
-        <v>91348</v>
+        <v>75140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443868</v>
+        <v>443811</v>
       </c>
       <c r="R42" t="n">
-        <v>7009783</v>
+        <v>7009946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127171750</v>
+        <v>127171789</v>
       </c>
       <c r="B43" t="n">
-        <v>75140</v>
+        <v>91344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443811</v>
+        <v>443942</v>
       </c>
       <c r="R43" t="n">
-        <v>7009946</v>
+        <v>7010153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5266,10 +5266,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127171759</v>
+        <v>127171792</v>
       </c>
       <c r="B49" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5277,21 +5277,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443657</v>
+        <v>443662</v>
       </c>
       <c r="R49" t="n">
-        <v>7009838</v>
+        <v>7009632</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5363,10 +5363,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127171792</v>
+        <v>127171759</v>
       </c>
       <c r="B50" t="n">
-        <v>91344</v>
+        <v>91626</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5374,21 +5374,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443662</v>
+        <v>443657</v>
       </c>
       <c r="R50" t="n">
-        <v>7009632</v>
+        <v>7009838</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127171730</v>
+        <v>127171798</v>
       </c>
       <c r="B66" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443904</v>
+        <v>443680</v>
       </c>
       <c r="R66" t="n">
-        <v>7010041</v>
+        <v>7009642</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7024,10 +7024,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127171798</v>
+        <v>127171725</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443680</v>
+        <v>443925</v>
       </c>
       <c r="R67" t="n">
-        <v>7009642</v>
+        <v>7010042</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127171725</v>
+        <v>127171730</v>
       </c>
       <c r="B68" t="n">
-        <v>75142</v>
+        <v>91330</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443925</v>
+        <v>443904</v>
       </c>
       <c r="R68" t="n">
-        <v>7010042</v>
+        <v>7010041</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9643,7 +9643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127171728</v>
+        <v>127171729</v>
       </c>
       <c r="B94" t="n">
         <v>91330</v>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443634</v>
+        <v>444018</v>
       </c>
       <c r="R94" t="n">
-        <v>7009855</v>
+        <v>7010176</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127171729</v>
+        <v>127171780</v>
       </c>
       <c r="B95" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9751,21 +9751,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444018</v>
+        <v>443594</v>
       </c>
       <c r="R95" t="n">
-        <v>7010176</v>
+        <v>7009896</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9837,10 +9837,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127171780</v>
+        <v>127171728</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9848,21 +9848,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443594</v>
+        <v>443634</v>
       </c>
       <c r="R96" t="n">
-        <v>7009896</v>
+        <v>7009855</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12636,32 +12636,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127299830</v>
+        <v>127299819</v>
       </c>
       <c r="B124" t="n">
-        <v>92000</v>
+        <v>91626</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12671,10 +12671,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444057</v>
+        <v>444269</v>
       </c>
       <c r="R124" t="n">
-        <v>7010071</v>
+        <v>7010299</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12733,32 +12733,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127299819</v>
+        <v>127299818</v>
       </c>
       <c r="B125" t="n">
-        <v>91626</v>
+        <v>75140</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444269</v>
+        <v>444299</v>
       </c>
       <c r="R125" t="n">
-        <v>7010299</v>
+        <v>7010246</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12830,10 +12830,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127299818</v>
+        <v>127299830</v>
       </c>
       <c r="B126" t="n">
-        <v>75140</v>
+        <v>92000</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12841,21 +12841,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6486</v>
+        <v>898</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12865,10 +12865,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444299</v>
+        <v>444057</v>
       </c>
       <c r="R126" t="n">
-        <v>7010246</v>
+        <v>7010071</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12927,10 +12927,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127303899</v>
+        <v>127302629</v>
       </c>
       <c r="B127" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12938,34 +12938,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444289</v>
+        <v>443988</v>
       </c>
       <c r="R127" t="n">
-        <v>7010247</v>
+        <v>7010097</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,19 +12995,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>20:30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13022,22 +13012,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127302629</v>
+        <v>127303905</v>
       </c>
       <c r="B128" t="n">
-        <v>91330</v>
+        <v>75064</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13045,34 +13035,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443988</v>
+        <v>444019</v>
       </c>
       <c r="R128" t="n">
-        <v>7010097</v>
+        <v>7010089</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13102,11 +13092,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13115,26 +13115,41 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127303905</v>
+        <v>127303899</v>
       </c>
       <c r="B129" t="n">
-        <v>75064</v>
+        <v>79018</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13142,21 +13157,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13166,10 +13181,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444019</v>
+        <v>444289</v>
       </c>
       <c r="R129" t="n">
-        <v>7010089</v>
+        <v>7010247</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13201,7 +13216,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13211,7 +13226,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13222,21 +13237,6 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -13253,10 +13253,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127302634</v>
+        <v>127303913</v>
       </c>
       <c r="B130" t="n">
-        <v>91330</v>
+        <v>75064</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13264,34 +13264,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443749</v>
+        <v>443984</v>
       </c>
       <c r="R130" t="n">
-        <v>7010018</v>
+        <v>7010138</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13321,11 +13321,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -13334,26 +13344,41 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127303913</v>
+        <v>127302634</v>
       </c>
       <c r="B131" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13361,34 +13386,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443984</v>
+        <v>443749</v>
       </c>
       <c r="R131" t="n">
-        <v>7010138</v>
+        <v>7010018</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13418,21 +13443,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -13441,76 +13456,61 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127302669</v>
+        <v>127303916</v>
       </c>
       <c r="B132" t="n">
-        <v>91344</v>
+        <v>75140</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443852</v>
+        <v>443956</v>
       </c>
       <c r="R132" t="n">
-        <v>7009880</v>
+        <v>7010157</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13540,11 +13540,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -13553,48 +13563,63 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127303916</v>
+        <v>127303906</v>
       </c>
       <c r="B133" t="n">
-        <v>75140</v>
+        <v>79104</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6486</v>
+        <v>6450</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13604,10 +13629,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443956</v>
+        <v>444000</v>
       </c>
       <c r="R133" t="n">
-        <v>7010157</v>
+        <v>7010124</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13639,7 +13664,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13649,7 +13674,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13691,45 +13716,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127303906</v>
+        <v>127302669</v>
       </c>
       <c r="B134" t="n">
-        <v>79104</v>
+        <v>91344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6450</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444000</v>
+        <v>443852</v>
       </c>
       <c r="R134" t="n">
-        <v>7010124</v>
+        <v>7009880</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13759,21 +13784,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -13782,31 +13797,16 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -16046,45 +16046,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127302664</v>
+        <v>127303932</v>
       </c>
       <c r="B157" t="n">
-        <v>79177</v>
+        <v>91330</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443777</v>
+        <v>443689</v>
       </c>
       <c r="R157" t="n">
-        <v>7010051</v>
+        <v>7009719</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16114,11 +16114,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -16127,26 +16137,41 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127299814</v>
+        <v>127303915</v>
       </c>
       <c r="B158" t="n">
-        <v>91330</v>
+        <v>79099</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16154,34 +16179,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>444084</v>
+        <v>443965</v>
       </c>
       <c r="R158" t="n">
-        <v>7010048</v>
+        <v>7010163</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16211,11 +16236,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16224,61 +16259,76 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127303915</v>
+        <v>127302664</v>
       </c>
       <c r="B159" t="n">
-        <v>79099</v>
+        <v>79177</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443965</v>
+        <v>443777</v>
       </c>
       <c r="R159" t="n">
-        <v>7010163</v>
+        <v>7010051</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16308,21 +16358,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -16331,31 +16371,16 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16556,7 +16581,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127303932</v>
+        <v>127299814</v>
       </c>
       <c r="B162" t="n">
         <v>91330</v>
@@ -16587,14 +16612,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443689</v>
+        <v>444084</v>
       </c>
       <c r="R162" t="n">
-        <v>7009719</v>
+        <v>7010048</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16624,21 +16649,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
@@ -16647,31 +16662,16 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127311483</v>
+        <v>127311006</v>
       </c>
       <c r="B195" t="n">
-        <v>92032</v>
+        <v>75140</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19940,34 +19940,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>67</v>
+        <v>6486</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Haratjärnen, Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443711</v>
+        <v>444031</v>
       </c>
       <c r="R195" t="n">
-        <v>7010048</v>
+        <v>7010078</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20026,45 +20026,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127311026</v>
+        <v>127311483</v>
       </c>
       <c r="B196" t="n">
-        <v>91626</v>
+        <v>92032</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443721</v>
+        <v>443711</v>
       </c>
       <c r="R196" t="n">
-        <v>7009852</v>
+        <v>7010048</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20123,7 +20123,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127311016</v>
+        <v>127311026</v>
       </c>
       <c r="B197" t="n">
         <v>91626</v>
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443914</v>
+        <v>443721</v>
       </c>
       <c r="R197" t="n">
-        <v>7009959</v>
+        <v>7009852</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20220,7 +20220,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127311021</v>
+        <v>127311016</v>
       </c>
       <c r="B198" t="n">
         <v>91626</v>
@@ -20255,10 +20255,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>444283</v>
+        <v>443914</v>
       </c>
       <c r="R198" t="n">
-        <v>7010242</v>
+        <v>7009959</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20317,32 +20317,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127311006</v>
+        <v>127311021</v>
       </c>
       <c r="B199" t="n">
-        <v>75140</v>
+        <v>91626</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>444031</v>
+        <v>444283</v>
       </c>
       <c r="R199" t="n">
-        <v>7010078</v>
+        <v>7010242</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20511,10 +20511,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127311020</v>
+        <v>127310993</v>
       </c>
       <c r="B201" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20522,21 +20522,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>444252</v>
+        <v>443730</v>
       </c>
       <c r="R201" t="n">
-        <v>7010325</v>
+        <v>7009851</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127310993</v>
+        <v>127311020</v>
       </c>
       <c r="B202" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20619,21 +20619,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>443730</v>
+        <v>444252</v>
       </c>
       <c r="R202" t="n">
-        <v>7009851</v>
+        <v>7010325</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -24113,10 +24113,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127311029</v>
+        <v>127310994</v>
       </c>
       <c r="B238" t="n">
-        <v>75064</v>
+        <v>91330</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24124,21 +24124,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24148,10 +24148,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>444127</v>
+        <v>443734</v>
       </c>
       <c r="R238" t="n">
-        <v>7010058</v>
+        <v>7009841</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24210,32 +24210,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127311004</v>
+        <v>127311029</v>
       </c>
       <c r="B239" t="n">
-        <v>75140</v>
+        <v>75064</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6486</v>
+        <v>1460</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24245,10 +24245,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>444086</v>
+        <v>444127</v>
       </c>
       <c r="R239" t="n">
-        <v>7010102</v>
+        <v>7010058</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24307,32 +24307,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127310994</v>
+        <v>127311004</v>
       </c>
       <c r="B240" t="n">
-        <v>91330</v>
+        <v>75140</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24342,10 +24342,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>443734</v>
+        <v>444086</v>
       </c>
       <c r="R240" t="n">
-        <v>7009841</v>
+        <v>7010102</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24889,10 +24889,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127311038</v>
+        <v>127311008</v>
       </c>
       <c r="B246" t="n">
-        <v>79177</v>
+        <v>75140</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -24900,21 +24900,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -24924,10 +24924,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>444108</v>
+        <v>443750</v>
       </c>
       <c r="R246" t="n">
-        <v>7010013</v>
+        <v>7010074</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -24986,10 +24986,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127311008</v>
+        <v>127311038</v>
       </c>
       <c r="B247" t="n">
-        <v>75140</v>
+        <v>79177</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24997,21 +24997,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25021,10 +25021,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>443750</v>
+        <v>444108</v>
       </c>
       <c r="R247" t="n">
-        <v>7010074</v>
+        <v>7010013</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127171750</v>
+        <v>127171794</v>
       </c>
       <c r="B38" t="n">
-        <v>75140</v>
+        <v>91348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443811</v>
+        <v>443868</v>
       </c>
       <c r="R38" t="n">
-        <v>7009946</v>
+        <v>7009783</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127171733</v>
+        <v>127171750</v>
       </c>
       <c r="B39" t="n">
-        <v>91330</v>
+        <v>75140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443799</v>
+        <v>443811</v>
       </c>
       <c r="R39" t="n">
-        <v>7009908</v>
+        <v>7009946</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127171795</v>
+        <v>127171772</v>
       </c>
       <c r="B40" t="n">
-        <v>91348</v>
+        <v>91626</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443763</v>
+        <v>443665</v>
       </c>
       <c r="R40" t="n">
-        <v>7009828</v>
+        <v>7009633</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127171794</v>
+        <v>127171733</v>
       </c>
       <c r="B41" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443868</v>
+        <v>443799</v>
       </c>
       <c r="R41" t="n">
-        <v>7009783</v>
+        <v>7009908</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127171789</v>
+        <v>127171795</v>
       </c>
       <c r="B42" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443942</v>
+        <v>443763</v>
       </c>
       <c r="R42" t="n">
-        <v>7010153</v>
+        <v>7009828</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127171772</v>
+        <v>127171789</v>
       </c>
       <c r="B43" t="n">
-        <v>91626</v>
+        <v>91344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443665</v>
+        <v>443942</v>
       </c>
       <c r="R43" t="n">
-        <v>7009633</v>
+        <v>7010153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127171777</v>
+        <v>127171751</v>
       </c>
       <c r="B86" t="n">
-        <v>79177</v>
+        <v>75140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444030</v>
+        <v>443751</v>
       </c>
       <c r="R86" t="n">
-        <v>7010188</v>
+        <v>7009735</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8964,32 +8964,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127171751</v>
+        <v>127171801</v>
       </c>
       <c r="B87" t="n">
-        <v>75140</v>
+        <v>88733</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6486</v>
+        <v>510</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443751</v>
+        <v>443690</v>
       </c>
       <c r="R87" t="n">
-        <v>7009735</v>
+        <v>7009636</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9061,32 +9061,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127171801</v>
+        <v>127171777</v>
       </c>
       <c r="B88" t="n">
-        <v>88733</v>
+        <v>79177</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>510</v>
+        <v>1249</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9096,10 +9096,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443690</v>
+        <v>444030</v>
       </c>
       <c r="R88" t="n">
-        <v>7009636</v>
+        <v>7010188</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9255,32 +9255,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127171779</v>
+        <v>127171768</v>
       </c>
       <c r="B90" t="n">
-        <v>79177</v>
+        <v>91626</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443829</v>
+        <v>443694</v>
       </c>
       <c r="R90" t="n">
-        <v>7010003</v>
+        <v>7009672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9352,32 +9352,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127171768</v>
+        <v>127171779</v>
       </c>
       <c r="B91" t="n">
-        <v>91626</v>
+        <v>79177</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>1249</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443694</v>
+        <v>443829</v>
       </c>
       <c r="R91" t="n">
-        <v>7009672</v>
+        <v>7010003</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10128,32 +10128,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127171773</v>
+        <v>127171745</v>
       </c>
       <c r="B99" t="n">
-        <v>91699</v>
+        <v>80150</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1506</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443696</v>
+        <v>443708</v>
       </c>
       <c r="R99" t="n">
-        <v>7009647</v>
+        <v>7009649</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10225,32 +10225,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127171745</v>
+        <v>127171773</v>
       </c>
       <c r="B100" t="n">
-        <v>80150</v>
+        <v>91699</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443708</v>
+        <v>443696</v>
       </c>
       <c r="R100" t="n">
-        <v>7009649</v>
+        <v>7009647</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13910,45 +13910,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127299816</v>
+        <v>127303920</v>
       </c>
       <c r="B136" t="n">
-        <v>91330</v>
+        <v>100537</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444022</v>
+        <v>443902</v>
       </c>
       <c r="R136" t="n">
-        <v>7010055</v>
+        <v>7010174</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13978,9 +13978,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -13995,22 +14010,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127302658</v>
+        <v>127299816</v>
       </c>
       <c r="B137" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14018,34 +14033,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443777</v>
+        <v>444022</v>
       </c>
       <c r="R137" t="n">
-        <v>7010050</v>
+        <v>7010055</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14092,22 +14107,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127302666</v>
+        <v>127302658</v>
       </c>
       <c r="B138" t="n">
-        <v>91326</v>
+        <v>91626</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14115,21 +14130,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14139,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443769</v>
+        <v>443777</v>
       </c>
       <c r="R138" t="n">
-        <v>7010089</v>
+        <v>7010050</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14201,10 +14216,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302670</v>
+        <v>127302666</v>
       </c>
       <c r="B139" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14212,21 +14227,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14236,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444114</v>
+        <v>443769</v>
       </c>
       <c r="R139" t="n">
-        <v>7010064</v>
+        <v>7010089</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14298,45 +14313,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127303920</v>
+        <v>127302668</v>
       </c>
       <c r="B140" t="n">
-        <v>100537</v>
+        <v>91344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>222771</v>
+        <v>1204</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443902</v>
+        <v>443816</v>
       </c>
       <c r="R140" t="n">
-        <v>7010174</v>
+        <v>7009788</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14366,24 +14381,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14398,19 +14398,19 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127302668</v>
+        <v>127302670</v>
       </c>
       <c r="B141" t="n">
         <v>91344</v>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443816</v>
+        <v>444114</v>
       </c>
       <c r="R141" t="n">
-        <v>7009788</v>
+        <v>7010064</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127302636</v>
+        <v>127302655</v>
       </c>
       <c r="B182" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18589,21 +18589,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443640</v>
+        <v>443907</v>
       </c>
       <c r="R182" t="n">
-        <v>7010000</v>
+        <v>7010185</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18675,7 +18675,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127302627</v>
+        <v>127302636</v>
       </c>
       <c r="B183" t="n">
         <v>91330</v>
@@ -18710,10 +18710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>444031</v>
+        <v>443640</v>
       </c>
       <c r="R183" t="n">
-        <v>7010049</v>
+        <v>7010000</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18772,7 +18772,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127302640</v>
+        <v>127302627</v>
       </c>
       <c r="B184" t="n">
         <v>91330</v>
@@ -18807,10 +18807,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443738</v>
+        <v>444031</v>
       </c>
       <c r="R184" t="n">
-        <v>7009862</v>
+        <v>7010049</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18869,10 +18869,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127302655</v>
+        <v>127302640</v>
       </c>
       <c r="B185" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18880,21 +18880,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18904,10 +18904,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443907</v>
+        <v>443738</v>
       </c>
       <c r="R185" t="n">
-        <v>7010185</v>
+        <v>7009862</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18966,45 +18966,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127303925</v>
+        <v>127302624</v>
       </c>
       <c r="B186" t="n">
-        <v>79177</v>
+        <v>91330</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443627</v>
+        <v>444005</v>
       </c>
       <c r="R186" t="n">
-        <v>7009957</v>
+        <v>7009910</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19034,21 +19034,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -19057,38 +19047,23 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127302624</v>
+        <v>127303928</v>
       </c>
       <c r="B187" t="n">
         <v>91330</v>
@@ -19119,14 +19094,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>444005</v>
+        <v>443698</v>
       </c>
       <c r="R187" t="n">
-        <v>7009910</v>
+        <v>7009874</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19156,11 +19131,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -19169,48 +19154,63 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127303928</v>
+        <v>127303925</v>
       </c>
       <c r="B188" t="n">
-        <v>91330</v>
+        <v>79177</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19220,10 +19220,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>443698</v>
+        <v>443627</v>
       </c>
       <c r="R188" t="n">
-        <v>7009874</v>
+        <v>7009957</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20996,10 +20996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127310987</v>
+        <v>127311018</v>
       </c>
       <c r="B206" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21007,21 +21007,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21031,10 +21031,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>443973</v>
+        <v>444250</v>
       </c>
       <c r="R206" t="n">
-        <v>7010146</v>
+        <v>7010307</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21093,10 +21093,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127311018</v>
+        <v>127310987</v>
       </c>
       <c r="B207" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21104,21 +21104,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21128,10 +21128,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>444250</v>
+        <v>443973</v>
       </c>
       <c r="R207" t="n">
-        <v>7010307</v>
+        <v>7010146</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21785,32 +21785,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127311036</v>
+        <v>127310989</v>
       </c>
       <c r="B214" t="n">
-        <v>91699</v>
+        <v>91330</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21820,10 +21820,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>443694</v>
+        <v>443910</v>
       </c>
       <c r="R214" t="n">
-        <v>7009882</v>
+        <v>7010191</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21882,32 +21882,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127311033</v>
+        <v>127311037</v>
       </c>
       <c r="B215" t="n">
-        <v>75064</v>
+        <v>79177</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1460</v>
+        <v>1249</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21917,10 +21917,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>444055</v>
+        <v>443844</v>
       </c>
       <c r="R215" t="n">
-        <v>7010052</v>
+        <v>7009886</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21979,32 +21979,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127310989</v>
+        <v>127311036</v>
       </c>
       <c r="B216" t="n">
-        <v>91330</v>
+        <v>91699</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22014,10 +22014,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>443910</v>
+        <v>443694</v>
       </c>
       <c r="R216" t="n">
-        <v>7010191</v>
+        <v>7009882</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22076,32 +22076,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127311037</v>
+        <v>127311033</v>
       </c>
       <c r="B217" t="n">
-        <v>79177</v>
+        <v>75064</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1249</v>
+        <v>1460</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22111,10 +22111,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>443844</v>
+        <v>444055</v>
       </c>
       <c r="R217" t="n">
-        <v>7009886</v>
+        <v>7010052</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23531,10 +23531,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127311024</v>
+        <v>127310988</v>
       </c>
       <c r="B232" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23542,21 +23542,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23566,10 +23566,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>443987</v>
+        <v>443937</v>
       </c>
       <c r="R232" t="n">
-        <v>7010155</v>
+        <v>7010167</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23628,10 +23628,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127311025</v>
+        <v>127311050</v>
       </c>
       <c r="B233" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23639,21 +23639,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23663,10 +23663,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>443634</v>
+        <v>443756</v>
       </c>
       <c r="R233" t="n">
-        <v>7009878</v>
+        <v>7010085</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23725,10 +23725,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127310988</v>
+        <v>127311051</v>
       </c>
       <c r="B234" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23736,21 +23736,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23760,10 +23760,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443937</v>
+        <v>443729</v>
       </c>
       <c r="R234" t="n">
-        <v>7010167</v>
+        <v>7009862</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23822,10 +23822,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127311050</v>
+        <v>127311027</v>
       </c>
       <c r="B235" t="n">
-        <v>91348</v>
+        <v>75064</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23833,21 +23833,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5432</v>
+        <v>1460</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23857,10 +23857,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443756</v>
+        <v>444316</v>
       </c>
       <c r="R235" t="n">
-        <v>7010085</v>
+        <v>7010269</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23919,10 +23919,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127311051</v>
+        <v>127311024</v>
       </c>
       <c r="B236" t="n">
-        <v>91348</v>
+        <v>91626</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23930,21 +23930,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23954,10 +23954,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>443729</v>
+        <v>443987</v>
       </c>
       <c r="R236" t="n">
-        <v>7009862</v>
+        <v>7010155</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24016,10 +24016,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127311027</v>
+        <v>127311025</v>
       </c>
       <c r="B237" t="n">
-        <v>75064</v>
+        <v>91626</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24027,21 +24027,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24051,10 +24051,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>444316</v>
+        <v>443634</v>
       </c>
       <c r="R237" t="n">
-        <v>7010269</v>
+        <v>7009878</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24889,10 +24889,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127311038</v>
+        <v>127311008</v>
       </c>
       <c r="B246" t="n">
-        <v>79177</v>
+        <v>75140</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -24900,21 +24900,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -24924,10 +24924,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>444108</v>
+        <v>443750</v>
       </c>
       <c r="R246" t="n">
-        <v>7010013</v>
+        <v>7010074</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -24986,10 +24986,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127311008</v>
+        <v>127311038</v>
       </c>
       <c r="B247" t="n">
-        <v>75140</v>
+        <v>79177</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24997,21 +24997,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25021,10 +25021,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>443750</v>
+        <v>444108</v>
       </c>
       <c r="R247" t="n">
-        <v>7010074</v>
+        <v>7010013</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26053,32 +26053,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127311001</v>
+        <v>127310985</v>
       </c>
       <c r="B258" t="n">
-        <v>92032</v>
+        <v>91330</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>443716</v>
+        <v>444090</v>
       </c>
       <c r="R258" t="n">
-        <v>7010053</v>
+        <v>7009966</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26150,10 +26150,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127311043</v>
+        <v>127310984</v>
       </c>
       <c r="B259" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26161,21 +26161,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26185,10 +26185,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>443639</v>
+        <v>444048</v>
       </c>
       <c r="R259" t="n">
-        <v>7010011</v>
+        <v>7009932</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26247,10 +26247,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127310985</v>
+        <v>127311043</v>
       </c>
       <c r="B260" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26258,21 +26258,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26282,10 +26282,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>444090</v>
+        <v>443639</v>
       </c>
       <c r="R260" t="n">
-        <v>7009966</v>
+        <v>7010011</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26344,32 +26344,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127310984</v>
+        <v>127311001</v>
       </c>
       <c r="B261" t="n">
-        <v>91330</v>
+        <v>92032</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26379,10 +26379,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>444048</v>
+        <v>443716</v>
       </c>
       <c r="R261" t="n">
-        <v>7009932</v>
+        <v>7010053</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127054791</v>
+        <v>127054780</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>91628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444024</v>
+        <v>443665</v>
       </c>
       <c r="R4" t="n">
-        <v>7009956</v>
+        <v>7009647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127054780</v>
+        <v>127054772</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443665</v>
+        <v>443748</v>
       </c>
       <c r="R5" t="n">
-        <v>7009647</v>
+        <v>7009749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127054772</v>
+        <v>127054791</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443748</v>
+        <v>444024</v>
       </c>
       <c r="R6" t="n">
-        <v>7009749</v>
+        <v>7009956</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127054778</v>
+        <v>127054781</v>
       </c>
       <c r="B16" t="n">
-        <v>91628</v>
+        <v>91701</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443693</v>
+        <v>443695</v>
       </c>
       <c r="R16" t="n">
-        <v>7009697</v>
+        <v>7009658</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2114,11 +2114,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127054783</v>
+        <v>127054778</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>91628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444045</v>
+        <v>443693</v>
       </c>
       <c r="R17" t="n">
-        <v>7010128</v>
+        <v>7009697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2211,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,32 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127054781</v>
+        <v>127054783</v>
       </c>
       <c r="B18" t="n">
-        <v>91701</v>
+        <v>91346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443695</v>
+        <v>444045</v>
       </c>
       <c r="R18" t="n">
-        <v>7009658</v>
+        <v>7010128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127171795</v>
+        <v>127171750</v>
       </c>
       <c r="B38" t="n">
-        <v>91350</v>
+        <v>75142</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443763</v>
+        <v>443811</v>
       </c>
       <c r="R38" t="n">
-        <v>7009828</v>
+        <v>7009946</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127171794</v>
+        <v>127171733</v>
       </c>
       <c r="B39" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443868</v>
+        <v>443799</v>
       </c>
       <c r="R39" t="n">
-        <v>7009783</v>
+        <v>7009908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127171750</v>
+        <v>127171772</v>
       </c>
       <c r="B40" t="n">
-        <v>75142</v>
+        <v>91628</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443811</v>
+        <v>443665</v>
       </c>
       <c r="R40" t="n">
-        <v>7009946</v>
+        <v>7009633</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127171772</v>
+        <v>127171795</v>
       </c>
       <c r="B41" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443665</v>
+        <v>443763</v>
       </c>
       <c r="R41" t="n">
-        <v>7009633</v>
+        <v>7009828</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127171733</v>
+        <v>127171794</v>
       </c>
       <c r="B42" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443799</v>
+        <v>443868</v>
       </c>
       <c r="R42" t="n">
-        <v>7009908</v>
+        <v>7009783</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127171797</v>
+        <v>127171757</v>
       </c>
       <c r="B45" t="n">
-        <v>91350</v>
+        <v>91786</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443694</v>
+        <v>443706</v>
       </c>
       <c r="R45" t="n">
-        <v>7009702</v>
+        <v>7009637</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4975,32 +4975,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127171739</v>
+        <v>127171797</v>
       </c>
       <c r="B46" t="n">
-        <v>92029</v>
+        <v>91350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444045</v>
+        <v>443694</v>
       </c>
       <c r="R46" t="n">
-        <v>7010113</v>
+        <v>7009702</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5072,32 +5072,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127171757</v>
+        <v>127171739</v>
       </c>
       <c r="B47" t="n">
-        <v>91786</v>
+        <v>92029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443706</v>
+        <v>444045</v>
       </c>
       <c r="R47" t="n">
-        <v>7009637</v>
+        <v>7010113</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5460,32 +5460,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171763</v>
+        <v>127171747</v>
       </c>
       <c r="B51" t="n">
-        <v>91628</v>
+        <v>75142</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444018</v>
+        <v>443962</v>
       </c>
       <c r="R51" t="n">
-        <v>7010190</v>
+        <v>7009915</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171762</v>
+        <v>127171763</v>
       </c>
       <c r="B52" t="n">
         <v>91628</v>
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443999</v>
+        <v>444018</v>
       </c>
       <c r="R52" t="n">
-        <v>7010217</v>
+        <v>7010190</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5654,7 +5654,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127171760</v>
+        <v>127171762</v>
       </c>
       <c r="B53" t="n">
         <v>91628</v>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443882</v>
+        <v>443999</v>
       </c>
       <c r="R53" t="n">
-        <v>7009800</v>
+        <v>7010217</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5751,32 +5751,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127171774</v>
+        <v>127171760</v>
       </c>
       <c r="B54" t="n">
-        <v>79179</v>
+        <v>91628</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443612</v>
+        <v>443882</v>
       </c>
       <c r="R54" t="n">
-        <v>7009871</v>
+        <v>7009800</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5848,57 +5848,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127171746</v>
+        <v>127171740</v>
       </c>
       <c r="B55" t="n">
-        <v>57660</v>
+        <v>92029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443702</v>
+        <v>444029</v>
       </c>
       <c r="R55" t="n">
-        <v>7009658</v>
+        <v>7010202</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5957,10 +5945,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127171747</v>
+        <v>127171774</v>
       </c>
       <c r="B56" t="n">
-        <v>75142</v>
+        <v>79179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5968,21 +5956,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5992,10 +5980,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443962</v>
+        <v>443612</v>
       </c>
       <c r="R56" t="n">
-        <v>7009915</v>
+        <v>7009871</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6054,45 +6042,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127171740</v>
+        <v>127171746</v>
       </c>
       <c r="B57" t="n">
-        <v>92029</v>
+        <v>57660</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444029</v>
+        <v>443702</v>
       </c>
       <c r="R57" t="n">
-        <v>7010202</v>
+        <v>7009658</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6539,32 +6539,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171791</v>
+        <v>127171749</v>
       </c>
       <c r="B62" t="n">
-        <v>91346</v>
+        <v>75142</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443740</v>
+        <v>443940</v>
       </c>
       <c r="R62" t="n">
-        <v>7009800</v>
+        <v>7010148</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6636,10 +6636,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127171770</v>
+        <v>127171791</v>
       </c>
       <c r="B63" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6647,21 +6647,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443701</v>
+        <v>443740</v>
       </c>
       <c r="R63" t="n">
-        <v>7009625</v>
+        <v>7009800</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6733,10 +6733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171749</v>
+        <v>127171775</v>
       </c>
       <c r="B64" t="n">
-        <v>75142</v>
+        <v>79179</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6744,21 +6744,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443940</v>
+        <v>443959</v>
       </c>
       <c r="R64" t="n">
-        <v>7010148</v>
+        <v>7009897</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6830,32 +6830,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127171775</v>
+        <v>127171770</v>
       </c>
       <c r="B65" t="n">
-        <v>79179</v>
+        <v>91628</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443959</v>
+        <v>443701</v>
       </c>
       <c r="R65" t="n">
-        <v>7009897</v>
+        <v>7009625</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127171798</v>
+        <v>127171730</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443680</v>
+        <v>443904</v>
       </c>
       <c r="R66" t="n">
-        <v>7009642</v>
+        <v>7010041</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7024,10 +7024,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127171725</v>
+        <v>127171798</v>
       </c>
       <c r="B67" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443925</v>
+        <v>443680</v>
       </c>
       <c r="R67" t="n">
-        <v>7010042</v>
+        <v>7009642</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127171730</v>
+        <v>127171725</v>
       </c>
       <c r="B68" t="n">
-        <v>91332</v>
+        <v>75144</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443904</v>
+        <v>443925</v>
       </c>
       <c r="R68" t="n">
-        <v>7010041</v>
+        <v>7010042</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7218,32 +7218,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127171769</v>
+        <v>127171744</v>
       </c>
       <c r="B69" t="n">
-        <v>91628</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443709</v>
+        <v>443782</v>
       </c>
       <c r="R69" t="n">
-        <v>7009666</v>
+        <v>7009804</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,32 +7315,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127171744</v>
+        <v>127171796</v>
       </c>
       <c r="B70" t="n">
-        <v>80152</v>
+        <v>91350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443782</v>
+        <v>443799</v>
       </c>
       <c r="R70" t="n">
-        <v>7009804</v>
+        <v>7009774</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127171796</v>
+        <v>127171769</v>
       </c>
       <c r="B71" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443799</v>
+        <v>443709</v>
       </c>
       <c r="R71" t="n">
-        <v>7009774</v>
+        <v>7009666</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8382,32 +8382,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127171738</v>
+        <v>127171758</v>
       </c>
       <c r="B81" t="n">
-        <v>92029</v>
+        <v>91628</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444071</v>
+        <v>443520</v>
       </c>
       <c r="R81" t="n">
-        <v>7010048</v>
+        <v>7009912</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8479,10 +8479,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127171758</v>
+        <v>127171793</v>
       </c>
       <c r="B82" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8490,21 +8490,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443520</v>
+        <v>443669</v>
       </c>
       <c r="R82" t="n">
-        <v>7009912</v>
+        <v>7009641</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8576,32 +8576,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127171793</v>
+        <v>127171738</v>
       </c>
       <c r="B83" t="n">
-        <v>91346</v>
+        <v>92029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8611,10 +8611,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443669</v>
+        <v>444071</v>
       </c>
       <c r="R83" t="n">
-        <v>7009641</v>
+        <v>7010048</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8867,32 +8867,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127171801</v>
+        <v>127171751</v>
       </c>
       <c r="B86" t="n">
-        <v>88735</v>
+        <v>75142</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>510</v>
+        <v>6486</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443690</v>
+        <v>443751</v>
       </c>
       <c r="R86" t="n">
-        <v>7009636</v>
+        <v>7009735</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8964,32 +8964,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127171751</v>
+        <v>127171801</v>
       </c>
       <c r="B87" t="n">
-        <v>75142</v>
+        <v>88735</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6486</v>
+        <v>510</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443751</v>
+        <v>443690</v>
       </c>
       <c r="R87" t="n">
-        <v>7009735</v>
+        <v>7009636</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9643,10 +9643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127171729</v>
+        <v>127171780</v>
       </c>
       <c r="B94" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9654,21 +9654,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444018</v>
+        <v>443594</v>
       </c>
       <c r="R94" t="n">
-        <v>7010176</v>
+        <v>7009896</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127171728</v>
+        <v>127171729</v>
       </c>
       <c r="B95" t="n">
         <v>91332</v>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443634</v>
+        <v>444018</v>
       </c>
       <c r="R95" t="n">
-        <v>7009855</v>
+        <v>7010176</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9837,10 +9837,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127171780</v>
+        <v>127171728</v>
       </c>
       <c r="B96" t="n">
-        <v>80123</v>
+        <v>91332</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9848,21 +9848,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443594</v>
+        <v>443634</v>
       </c>
       <c r="R96" t="n">
-        <v>7009896</v>
+        <v>7009855</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10128,32 +10128,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127171773</v>
+        <v>127171745</v>
       </c>
       <c r="B99" t="n">
-        <v>91701</v>
+        <v>80152</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1506</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443696</v>
+        <v>443708</v>
       </c>
       <c r="R99" t="n">
-        <v>7009647</v>
+        <v>7009649</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10225,32 +10225,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127171745</v>
+        <v>127171773</v>
       </c>
       <c r="B100" t="n">
-        <v>80152</v>
+        <v>91701</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443708</v>
+        <v>443696</v>
       </c>
       <c r="R100" t="n">
-        <v>7009649</v>
+        <v>7009647</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10322,32 +10322,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127171726</v>
+        <v>127171781</v>
       </c>
       <c r="B101" t="n">
-        <v>91297</v>
+        <v>80123</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443752</v>
+        <v>443861</v>
       </c>
       <c r="R101" t="n">
-        <v>7009813</v>
+        <v>7009776</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10516,10 +10516,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127171741</v>
+        <v>127171726</v>
       </c>
       <c r="B103" t="n">
-        <v>92029</v>
+        <v>91297</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10527,21 +10527,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10551,10 +10551,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443691</v>
+        <v>443752</v>
       </c>
       <c r="R103" t="n">
-        <v>7009636</v>
+        <v>7009813</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10613,32 +10613,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127171781</v>
+        <v>127171741</v>
       </c>
       <c r="B104" t="n">
-        <v>80123</v>
+        <v>92029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443861</v>
+        <v>443691</v>
       </c>
       <c r="R104" t="n">
-        <v>7009776</v>
+        <v>7009636</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11098,10 +11098,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127302649</v>
+        <v>127302632</v>
       </c>
       <c r="B109" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11109,21 +11109,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444329</v>
+        <v>443773</v>
       </c>
       <c r="R109" t="n">
-        <v>7010232</v>
+        <v>7010102</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11195,45 +11195,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127303918</v>
+        <v>127302649</v>
       </c>
       <c r="B110" t="n">
-        <v>97476</v>
+        <v>91628</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>222741</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443944</v>
+        <v>444329</v>
       </c>
       <c r="R110" t="n">
-        <v>7010169</v>
+        <v>7010232</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11263,19 +11263,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>18:28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11290,22 +11280,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127302632</v>
+        <v>127302642</v>
       </c>
       <c r="B111" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11313,34 +11303,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443773</v>
+        <v>444096</v>
       </c>
       <c r="R111" t="n">
-        <v>7010102</v>
+        <v>7010088</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11373,6 +11371,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11399,53 +11402,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127302642</v>
+        <v>127303918</v>
       </c>
       <c r="B112" t="n">
-        <v>57663</v>
+        <v>97476</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444096</v>
+        <v>443944</v>
       </c>
       <c r="R112" t="n">
-        <v>7010088</v>
+        <v>7010169</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11475,14 +11470,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11497,12 +11497,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127302641</v>
+        <v>127303924</v>
       </c>
       <c r="B117" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,34 +11933,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444203</v>
+        <v>443651</v>
       </c>
       <c r="R117" t="n">
-        <v>7010082</v>
+        <v>7010015</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11990,14 +11990,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12008,26 +12013,41 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127303924</v>
+        <v>127302641</v>
       </c>
       <c r="B118" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12035,34 +12055,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443651</v>
+        <v>444203</v>
       </c>
       <c r="R118" t="n">
-        <v>7010015</v>
+        <v>7010082</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12092,19 +12112,14 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12115,31 +12130,16 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127302657</v>
+        <v>127302676</v>
       </c>
       <c r="B120" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12259,21 +12259,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443766</v>
+        <v>443737</v>
       </c>
       <c r="R120" t="n">
-        <v>7010076</v>
+        <v>7009850</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12345,7 +12345,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127302661</v>
+        <v>127302657</v>
       </c>
       <c r="B121" t="n">
         <v>91628</v>
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443698</v>
+        <v>443766</v>
       </c>
       <c r="R121" t="n">
-        <v>7009876</v>
+        <v>7010076</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127302676</v>
+        <v>127302661</v>
       </c>
       <c r="B123" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12550,21 +12550,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443737</v>
+        <v>443698</v>
       </c>
       <c r="R123" t="n">
-        <v>7009850</v>
+        <v>7009876</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12636,10 +12636,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127299830</v>
+        <v>127299818</v>
       </c>
       <c r="B124" t="n">
-        <v>92002</v>
+        <v>75142</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12647,21 +12647,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>898</v>
+        <v>6486</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12671,10 +12671,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444057</v>
+        <v>444299</v>
       </c>
       <c r="R124" t="n">
-        <v>7010071</v>
+        <v>7010246</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12733,32 +12733,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127299819</v>
+        <v>127299830</v>
       </c>
       <c r="B125" t="n">
-        <v>91628</v>
+        <v>92002</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444269</v>
+        <v>444057</v>
       </c>
       <c r="R125" t="n">
-        <v>7010299</v>
+        <v>7010071</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12830,10 +12830,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127303899</v>
+        <v>127299819</v>
       </c>
       <c r="B126" t="n">
-        <v>79020</v>
+        <v>91628</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12841,34 +12841,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444289</v>
+        <v>444269</v>
       </c>
       <c r="R126" t="n">
-        <v>7010247</v>
+        <v>7010299</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,19 +12898,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>20:30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -12925,22 +12915,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127302629</v>
+        <v>127303905</v>
       </c>
       <c r="B127" t="n">
-        <v>91332</v>
+        <v>75066</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12948,34 +12938,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443988</v>
+        <v>444019</v>
       </c>
       <c r="R127" t="n">
-        <v>7010097</v>
+        <v>7010089</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13005,11 +12995,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13018,26 +13018,41 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127303905</v>
+        <v>127302629</v>
       </c>
       <c r="B128" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13045,34 +13060,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444019</v>
+        <v>443988</v>
       </c>
       <c r="R128" t="n">
-        <v>7010089</v>
+        <v>7010097</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13102,21 +13117,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13125,76 +13130,61 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127299818</v>
+        <v>127303899</v>
       </c>
       <c r="B129" t="n">
-        <v>75142</v>
+        <v>79020</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444299</v>
+        <v>444289</v>
       </c>
       <c r="R129" t="n">
-        <v>7010246</v>
+        <v>7010247</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13224,9 +13214,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13241,22 +13241,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127303913</v>
+        <v>127302634</v>
       </c>
       <c r="B130" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13264,34 +13264,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443984</v>
+        <v>443749</v>
       </c>
       <c r="R130" t="n">
-        <v>7010138</v>
+        <v>7010018</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13321,21 +13321,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -13344,41 +13334,26 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127302634</v>
+        <v>127303913</v>
       </c>
       <c r="B131" t="n">
-        <v>91332</v>
+        <v>75066</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13386,34 +13361,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443749</v>
+        <v>443984</v>
       </c>
       <c r="R131" t="n">
-        <v>7010018</v>
+        <v>7010138</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13443,11 +13418,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -13456,26 +13441,41 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127302660</v>
+        <v>127302669</v>
       </c>
       <c r="B132" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443679</v>
+        <v>443852</v>
       </c>
       <c r="R132" t="n">
-        <v>7009872</v>
+        <v>7009880</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13569,10 +13569,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127302669</v>
+        <v>127302660</v>
       </c>
       <c r="B133" t="n">
-        <v>91346</v>
+        <v>91628</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13580,21 +13580,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13604,10 +13604,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443852</v>
+        <v>443679</v>
       </c>
       <c r="R133" t="n">
-        <v>7009880</v>
+        <v>7009872</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13910,10 +13910,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127302658</v>
+        <v>127299816</v>
       </c>
       <c r="B136" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13921,34 +13921,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443777</v>
+        <v>444022</v>
       </c>
       <c r="R136" t="n">
-        <v>7010050</v>
+        <v>7010055</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13995,12 +13995,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14298,45 +14298,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127303920</v>
+        <v>127302658</v>
       </c>
       <c r="B140" t="n">
-        <v>100539</v>
+        <v>91628</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443902</v>
+        <v>443777</v>
       </c>
       <c r="R140" t="n">
-        <v>7010174</v>
+        <v>7010050</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14366,24 +14366,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14398,57 +14383,57 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127299816</v>
+        <v>127303920</v>
       </c>
       <c r="B141" t="n">
-        <v>91332</v>
+        <v>100539</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444022</v>
+        <v>443902</v>
       </c>
       <c r="R141" t="n">
-        <v>7010055</v>
+        <v>7010174</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14478,9 +14463,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14495,57 +14495,57 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127303910</v>
+        <v>127302646</v>
       </c>
       <c r="B142" t="n">
-        <v>79276</v>
+        <v>91628</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6459</v>
+        <v>658</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443992</v>
+        <v>443843</v>
       </c>
       <c r="R142" t="n">
-        <v>7010143</v>
+        <v>7009837</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14575,21 +14575,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -14598,41 +14588,26 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127302646</v>
+        <v>127302671</v>
       </c>
       <c r="B143" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14640,21 +14615,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14664,10 +14639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>443843</v>
+        <v>443664</v>
       </c>
       <c r="R143" t="n">
-        <v>7009837</v>
+        <v>7009683</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14726,32 +14701,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127302671</v>
+        <v>127302679</v>
       </c>
       <c r="B144" t="n">
-        <v>91346</v>
+        <v>92002</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14761,10 +14736,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>443664</v>
+        <v>444009</v>
       </c>
       <c r="R144" t="n">
-        <v>7009683</v>
+        <v>7010058</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14823,45 +14798,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127302679</v>
+        <v>127303910</v>
       </c>
       <c r="B145" t="n">
-        <v>92002</v>
+        <v>79276</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>898</v>
+        <v>6459</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>444009</v>
+        <v>443992</v>
       </c>
       <c r="R145" t="n">
-        <v>7010058</v>
+        <v>7010143</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14891,11 +14866,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -14904,48 +14889,63 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127303898</v>
+        <v>127303907</v>
       </c>
       <c r="B146" t="n">
-        <v>80123</v>
+        <v>98783</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14955,10 +14955,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>444047</v>
+        <v>444006</v>
       </c>
       <c r="R146" t="n">
-        <v>7009927</v>
+        <v>7010126</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15027,10 +15027,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127302650</v>
+        <v>127302639</v>
       </c>
       <c r="B147" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15038,21 +15038,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15062,10 +15062,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>444093</v>
+        <v>443697</v>
       </c>
       <c r="R147" t="n">
-        <v>7010086</v>
+        <v>7009873</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15124,10 +15124,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127302639</v>
+        <v>127302650</v>
       </c>
       <c r="B148" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15135,21 +15135,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15159,10 +15159,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>443697</v>
+        <v>444093</v>
       </c>
       <c r="R148" t="n">
-        <v>7009873</v>
+        <v>7010086</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15221,32 +15221,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127303907</v>
+        <v>127303898</v>
       </c>
       <c r="B149" t="n">
-        <v>98783</v>
+        <v>80123</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15256,10 +15256,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>444006</v>
+        <v>444047</v>
       </c>
       <c r="R149" t="n">
-        <v>7010126</v>
+        <v>7009927</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15328,10 +15328,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127299824</v>
+        <v>127302648</v>
       </c>
       <c r="B150" t="n">
-        <v>91346</v>
+        <v>91628</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15339,34 +15339,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>444076</v>
+        <v>444005</v>
       </c>
       <c r="R150" t="n">
-        <v>7010048</v>
+        <v>7009910</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15413,22 +15413,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127302648</v>
+        <v>127302643</v>
       </c>
       <c r="B151" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15436,34 +15436,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>444005</v>
+        <v>443735</v>
       </c>
       <c r="R151" t="n">
-        <v>7009910</v>
+        <v>7009851</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15496,6 +15504,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15522,10 +15535,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127302643</v>
+        <v>127299824</v>
       </c>
       <c r="B152" t="n">
-        <v>57663</v>
+        <v>91346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15533,42 +15546,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443735</v>
+        <v>444076</v>
       </c>
       <c r="R152" t="n">
-        <v>7009851</v>
+        <v>7010048</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15603,11 +15608,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -15620,19 +15620,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127299813</v>
+        <v>127302638</v>
       </c>
       <c r="B153" t="n">
         <v>91332</v>
@@ -15663,14 +15663,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>444303</v>
+        <v>443679</v>
       </c>
       <c r="R153" t="n">
-        <v>7010251</v>
+        <v>7009870</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15717,12 +15717,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -15851,32 +15851,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127302638</v>
+        <v>127302644</v>
       </c>
       <c r="B155" t="n">
-        <v>91332</v>
+        <v>91786</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15886,10 +15886,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443679</v>
+        <v>443970</v>
       </c>
       <c r="R155" t="n">
-        <v>7009870</v>
+        <v>7009897</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15930,6 +15930,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -15948,45 +15949,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127302644</v>
+        <v>127299813</v>
       </c>
       <c r="B156" t="n">
-        <v>91786</v>
+        <v>91332</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443970</v>
+        <v>444303</v>
       </c>
       <c r="R156" t="n">
-        <v>7009897</v>
+        <v>7010251</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16027,29 +16028,28 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127299814</v>
+        <v>127299821</v>
       </c>
       <c r="B157" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16057,21 +16057,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16081,10 +16081,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>444084</v>
+        <v>444255</v>
       </c>
       <c r="R157" t="n">
-        <v>7010048</v>
+        <v>7010318</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16143,7 +16143,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127299821</v>
+        <v>127302652</v>
       </c>
       <c r="B158" t="n">
         <v>91628</v>
@@ -16174,14 +16174,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>444255</v>
+        <v>443999</v>
       </c>
       <c r="R158" t="n">
-        <v>7010318</v>
+        <v>7010076</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16228,22 +16228,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127302652</v>
+        <v>127303932</v>
       </c>
       <c r="B159" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16251,34 +16251,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443999</v>
+        <v>443689</v>
       </c>
       <c r="R159" t="n">
-        <v>7010076</v>
+        <v>7009719</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16308,11 +16308,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -16321,16 +16331,31 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16459,45 +16484,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127303932</v>
+        <v>127302664</v>
       </c>
       <c r="B161" t="n">
-        <v>91332</v>
+        <v>79179</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443689</v>
+        <v>443777</v>
       </c>
       <c r="R161" t="n">
-        <v>7009719</v>
+        <v>7010051</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16527,21 +16552,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -16550,76 +16565,61 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127302664</v>
+        <v>127299814</v>
       </c>
       <c r="B162" t="n">
-        <v>79179</v>
+        <v>91332</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443777</v>
+        <v>444084</v>
       </c>
       <c r="R162" t="n">
-        <v>7010051</v>
+        <v>7010048</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16666,22 +16666,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127299827</v>
+        <v>127303914</v>
       </c>
       <c r="B163" t="n">
-        <v>91350</v>
+        <v>75066</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16689,34 +16689,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>1460</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>444241</v>
+        <v>443985</v>
       </c>
       <c r="R163" t="n">
-        <v>7010317</v>
+        <v>7010134</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16746,11 +16746,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -16759,16 +16769,31 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -16872,45 +16897,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127303914</v>
+        <v>127302645</v>
       </c>
       <c r="B165" t="n">
-        <v>75066</v>
+        <v>91786</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1460</v>
+        <v>1209</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>443985</v>
+        <v>443997</v>
       </c>
       <c r="R165" t="n">
-        <v>7010134</v>
+        <v>7010102</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16940,99 +16965,75 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127302645</v>
+        <v>127299827</v>
       </c>
       <c r="B166" t="n">
-        <v>91786</v>
+        <v>91350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>443997</v>
+        <v>444241</v>
       </c>
       <c r="R166" t="n">
-        <v>7010102</v>
+        <v>7010317</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17073,64 +17074,63 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127303912</v>
+        <v>127302678</v>
       </c>
       <c r="B167" t="n">
-        <v>75142</v>
+        <v>91350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>443984</v>
+        <v>443705</v>
       </c>
       <c r="R167" t="n">
-        <v>7010138</v>
+        <v>7009844</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17160,19 +17160,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>19:01</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>19:01</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17187,57 +17177,57 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127302678</v>
+        <v>127303912</v>
       </c>
       <c r="B168" t="n">
-        <v>91350</v>
+        <v>75142</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443705</v>
+        <v>443984</v>
       </c>
       <c r="R168" t="n">
-        <v>7009844</v>
+        <v>7010138</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17267,9 +17257,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17284,22 +17284,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127302628</v>
+        <v>127302665</v>
       </c>
       <c r="B169" t="n">
-        <v>91332</v>
+        <v>91739</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17307,21 +17307,16 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17331,10 +17326,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443999</v>
+        <v>444252</v>
       </c>
       <c r="R169" t="n">
-        <v>7010076</v>
+        <v>7010193</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17375,6 +17370,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17490,10 +17486,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127302665</v>
+        <v>127302628</v>
       </c>
       <c r="B171" t="n">
-        <v>91739</v>
+        <v>91332</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17501,16 +17497,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17520,10 +17521,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>444252</v>
+        <v>443999</v>
       </c>
       <c r="R171" t="n">
-        <v>7010193</v>
+        <v>7010076</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17564,7 +17565,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17680,10 +17680,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127302651</v>
+        <v>127302673</v>
       </c>
       <c r="B173" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17691,21 +17691,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17715,10 +17715,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>444007</v>
+        <v>443884</v>
       </c>
       <c r="R173" t="n">
-        <v>7010058</v>
+        <v>7010169</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17777,10 +17777,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302673</v>
+        <v>127302633</v>
       </c>
       <c r="B174" t="n">
-        <v>91346</v>
+        <v>91332</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443884</v>
+        <v>443747</v>
       </c>
       <c r="R174" t="n">
-        <v>7010169</v>
+        <v>7010019</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17874,10 +17874,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127302633</v>
+        <v>127302651</v>
       </c>
       <c r="B175" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17885,21 +17885,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17909,10 +17909,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443747</v>
+        <v>444007</v>
       </c>
       <c r="R175" t="n">
-        <v>7010019</v>
+        <v>7010058</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127302655</v>
+        <v>127302636</v>
       </c>
       <c r="B182" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18589,21 +18589,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443907</v>
+        <v>443640</v>
       </c>
       <c r="R182" t="n">
-        <v>7010185</v>
+        <v>7010000</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18675,7 +18675,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127302636</v>
+        <v>127302627</v>
       </c>
       <c r="B183" t="n">
         <v>91332</v>
@@ -18710,10 +18710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443640</v>
+        <v>444031</v>
       </c>
       <c r="R183" t="n">
-        <v>7010000</v>
+        <v>7010049</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18772,7 +18772,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127302627</v>
+        <v>127302640</v>
       </c>
       <c r="B184" t="n">
         <v>91332</v>
@@ -18807,10 +18807,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>444031</v>
+        <v>443738</v>
       </c>
       <c r="R184" t="n">
-        <v>7010049</v>
+        <v>7009862</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18869,10 +18869,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127302640</v>
+        <v>127302655</v>
       </c>
       <c r="B185" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18880,21 +18880,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18904,10 +18904,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443738</v>
+        <v>443907</v>
       </c>
       <c r="R185" t="n">
-        <v>7009862</v>
+        <v>7010185</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19638,10 +19638,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127302647</v>
+        <v>127302672</v>
       </c>
       <c r="B192" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19649,21 +19649,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19673,10 +19673,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443989</v>
+        <v>443978</v>
       </c>
       <c r="R192" t="n">
-        <v>7009901</v>
+        <v>7010133</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19735,10 +19735,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127302672</v>
+        <v>127302647</v>
       </c>
       <c r="B193" t="n">
-        <v>91346</v>
+        <v>91628</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19746,21 +19746,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19770,10 +19770,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443978</v>
+        <v>443989</v>
       </c>
       <c r="R193" t="n">
-        <v>7010133</v>
+        <v>7009901</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19929,32 +19929,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127311006</v>
+        <v>127311026</v>
       </c>
       <c r="B195" t="n">
-        <v>75142</v>
+        <v>91628</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>444031</v>
+        <v>443721</v>
       </c>
       <c r="R195" t="n">
-        <v>7010078</v>
+        <v>7009852</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20026,7 +20026,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127311026</v>
+        <v>127311016</v>
       </c>
       <c r="B196" t="n">
         <v>91628</v>
@@ -20061,10 +20061,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443721</v>
+        <v>443914</v>
       </c>
       <c r="R196" t="n">
-        <v>7009852</v>
+        <v>7009959</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20123,45 +20123,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127311016</v>
+        <v>127311483</v>
       </c>
       <c r="B197" t="n">
-        <v>91628</v>
+        <v>92034</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443914</v>
+        <v>443711</v>
       </c>
       <c r="R197" t="n">
-        <v>7009959</v>
+        <v>7010048</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20220,45 +20220,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127311483</v>
+        <v>127311021</v>
       </c>
       <c r="B198" t="n">
-        <v>92034</v>
+        <v>91628</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>67</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Haratjärnen, Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>443711</v>
+        <v>444283</v>
       </c>
       <c r="R198" t="n">
-        <v>7010048</v>
+        <v>7010242</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20317,32 +20317,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127311021</v>
+        <v>127311006</v>
       </c>
       <c r="B199" t="n">
-        <v>91628</v>
+        <v>75142</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>444283</v>
+        <v>444031</v>
       </c>
       <c r="R199" t="n">
-        <v>7010242</v>
+        <v>7010078</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20511,10 +20511,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127311020</v>
+        <v>127310993</v>
       </c>
       <c r="B201" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20522,21 +20522,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>444252</v>
+        <v>443730</v>
       </c>
       <c r="R201" t="n">
-        <v>7010325</v>
+        <v>7009851</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127310993</v>
+        <v>127311020</v>
       </c>
       <c r="B202" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20619,21 +20619,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>443730</v>
+        <v>444252</v>
       </c>
       <c r="R202" t="n">
-        <v>7009851</v>
+        <v>7010325</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20705,32 +20705,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127311031</v>
+        <v>127311011</v>
       </c>
       <c r="B203" t="n">
-        <v>75066</v>
+        <v>91786</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1460</v>
+        <v>1209</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>444124</v>
+        <v>444037</v>
       </c>
       <c r="R203" t="n">
-        <v>7010021</v>
+        <v>7010055</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20802,32 +20802,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127311011</v>
+        <v>127311032</v>
       </c>
       <c r="B204" t="n">
-        <v>91786</v>
+        <v>75066</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1209</v>
+        <v>1460</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20837,10 +20837,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>444037</v>
+        <v>444097</v>
       </c>
       <c r="R204" t="n">
-        <v>7010055</v>
+        <v>7010029</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20899,7 +20899,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127311032</v>
+        <v>127311031</v>
       </c>
       <c r="B205" t="n">
         <v>75066</v>
@@ -20934,10 +20934,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>444097</v>
+        <v>444124</v>
       </c>
       <c r="R205" t="n">
-        <v>7010029</v>
+        <v>7010021</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20996,10 +20996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127310987</v>
+        <v>127311018</v>
       </c>
       <c r="B206" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21007,21 +21007,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21031,10 +21031,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>443973</v>
+        <v>444250</v>
       </c>
       <c r="R206" t="n">
-        <v>7010146</v>
+        <v>7010307</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21093,10 +21093,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127310997</v>
+        <v>127310987</v>
       </c>
       <c r="B207" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21104,42 +21104,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443735</v>
+        <v>443973</v>
       </c>
       <c r="R207" t="n">
-        <v>7009858</v>
+        <v>7010146</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21172,11 +21164,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21203,10 +21190,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127311018</v>
+        <v>127310997</v>
       </c>
       <c r="B208" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21214,34 +21201,42 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>444250</v>
+        <v>443735</v>
       </c>
       <c r="R208" t="n">
-        <v>7010307</v>
+        <v>7009858</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21274,6 +21269,11 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21397,32 +21397,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127311052</v>
+        <v>127311039</v>
       </c>
       <c r="B210" t="n">
-        <v>79020</v>
+        <v>79179</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21432,10 +21432,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443874</v>
+        <v>443626</v>
       </c>
       <c r="R210" t="n">
-        <v>7009953</v>
+        <v>7009924</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21494,10 +21494,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127311042</v>
+        <v>127311052</v>
       </c>
       <c r="B211" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21505,21 +21505,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21529,10 +21529,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>443919</v>
+        <v>443874</v>
       </c>
       <c r="R211" t="n">
-        <v>7010183</v>
+        <v>7009953</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21591,32 +21591,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127311039</v>
+        <v>127311042</v>
       </c>
       <c r="B212" t="n">
-        <v>79179</v>
+        <v>80123</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21626,10 +21626,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>443626</v>
+        <v>443919</v>
       </c>
       <c r="R212" t="n">
-        <v>7009924</v>
+        <v>7010183</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21688,32 +21688,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310989</v>
+        <v>127310996</v>
       </c>
       <c r="B213" t="n">
-        <v>91332</v>
+        <v>92029</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21723,10 +21723,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>443910</v>
+        <v>444091</v>
       </c>
       <c r="R213" t="n">
-        <v>7010191</v>
+        <v>7010088</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21785,32 +21785,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127311037</v>
+        <v>127311033</v>
       </c>
       <c r="B214" t="n">
-        <v>79179</v>
+        <v>75066</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1249</v>
+        <v>1460</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21820,10 +21820,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>443844</v>
+        <v>444055</v>
       </c>
       <c r="R214" t="n">
-        <v>7009886</v>
+        <v>7010052</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21882,32 +21882,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127310996</v>
+        <v>127311036</v>
       </c>
       <c r="B215" t="n">
-        <v>92029</v>
+        <v>91701</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>3298</v>
+        <v>1506</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21917,10 +21917,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>444091</v>
+        <v>443694</v>
       </c>
       <c r="R215" t="n">
-        <v>7010088</v>
+        <v>7009882</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21979,32 +21979,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127311036</v>
+        <v>127310989</v>
       </c>
       <c r="B216" t="n">
-        <v>91701</v>
+        <v>91332</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22014,10 +22014,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>443694</v>
+        <v>443910</v>
       </c>
       <c r="R216" t="n">
-        <v>7009882</v>
+        <v>7010191</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22076,32 +22076,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127311033</v>
+        <v>127311037</v>
       </c>
       <c r="B217" t="n">
-        <v>75066</v>
+        <v>79179</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1460</v>
+        <v>1249</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22111,10 +22111,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>444055</v>
+        <v>443844</v>
       </c>
       <c r="R217" t="n">
-        <v>7010052</v>
+        <v>7009886</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22270,32 +22270,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127311054</v>
+        <v>127311012</v>
       </c>
       <c r="B219" t="n">
-        <v>79020</v>
+        <v>91786</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22305,10 +22305,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>443698</v>
+        <v>443967</v>
       </c>
       <c r="R219" t="n">
-        <v>7010030</v>
+        <v>7010143</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22367,32 +22367,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127311012</v>
+        <v>127311054</v>
       </c>
       <c r="B220" t="n">
-        <v>91786</v>
+        <v>79020</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22402,10 +22402,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>443967</v>
+        <v>443698</v>
       </c>
       <c r="R220" t="n">
-        <v>7010143</v>
+        <v>7010030</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22464,32 +22464,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127310999</v>
+        <v>127311047</v>
       </c>
       <c r="B221" t="n">
-        <v>80152</v>
+        <v>91346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22499,10 +22499,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>444089</v>
+        <v>444088</v>
       </c>
       <c r="R221" t="n">
-        <v>7010006</v>
+        <v>7010038</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22561,32 +22561,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127311047</v>
+        <v>127310999</v>
       </c>
       <c r="B222" t="n">
-        <v>91346</v>
+        <v>80152</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22596,10 +22596,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>444088</v>
+        <v>444089</v>
       </c>
       <c r="R222" t="n">
-        <v>7010038</v>
+        <v>7010006</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22755,10 +22755,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127311041</v>
+        <v>127311034</v>
       </c>
       <c r="B224" t="n">
-        <v>80123</v>
+        <v>75066</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22766,21 +22766,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22790,10 +22790,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>444094</v>
+        <v>444026</v>
       </c>
       <c r="R224" t="n">
-        <v>7010004</v>
+        <v>7010076</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22852,10 +22852,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127311059</v>
+        <v>127311030</v>
       </c>
       <c r="B225" t="n">
-        <v>88735</v>
+        <v>75066</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22863,21 +22863,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>510</v>
+        <v>1460</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>444272</v>
+        <v>444131</v>
       </c>
       <c r="R225" t="n">
-        <v>7010237</v>
+        <v>7010038</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22949,10 +22949,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127311022</v>
+        <v>127310995</v>
       </c>
       <c r="B226" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22960,21 +22960,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>444108</v>
+        <v>443689</v>
       </c>
       <c r="R226" t="n">
-        <v>7010040</v>
+        <v>7009728</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23046,7 +23046,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127310995</v>
+        <v>127310990</v>
       </c>
       <c r="B227" t="n">
         <v>91332</v>
@@ -23081,10 +23081,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>443689</v>
+        <v>443745</v>
       </c>
       <c r="R227" t="n">
-        <v>7009728</v>
+        <v>7010081</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23143,10 +23143,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127310990</v>
+        <v>127311059</v>
       </c>
       <c r="B228" t="n">
-        <v>91332</v>
+        <v>88735</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23154,21 +23154,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23178,10 +23178,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>443745</v>
+        <v>444272</v>
       </c>
       <c r="R228" t="n">
-        <v>7010081</v>
+        <v>7010237</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23240,10 +23240,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127311030</v>
+        <v>127310986</v>
       </c>
       <c r="B229" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23251,21 +23251,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>444131</v>
+        <v>444046</v>
       </c>
       <c r="R229" t="n">
-        <v>7010038</v>
+        <v>7010063</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127311034</v>
+        <v>127311022</v>
       </c>
       <c r="B230" t="n">
-        <v>75066</v>
+        <v>91628</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23348,21 +23348,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23372,10 +23372,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>444026</v>
+        <v>444108</v>
       </c>
       <c r="R230" t="n">
-        <v>7010076</v>
+        <v>7010040</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23434,10 +23434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127310986</v>
+        <v>127311041</v>
       </c>
       <c r="B231" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23445,21 +23445,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444046</v>
+        <v>444094</v>
       </c>
       <c r="R231" t="n">
-        <v>7010063</v>
+        <v>7010004</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23531,10 +23531,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127311050</v>
+        <v>127311027</v>
       </c>
       <c r="B232" t="n">
-        <v>91350</v>
+        <v>75066</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23542,21 +23542,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5432</v>
+        <v>1460</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23566,10 +23566,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>443756</v>
+        <v>444316</v>
       </c>
       <c r="R232" t="n">
-        <v>7010085</v>
+        <v>7010269</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23725,10 +23725,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127311024</v>
+        <v>127311050</v>
       </c>
       <c r="B234" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23736,21 +23736,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23760,10 +23760,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443987</v>
+        <v>443756</v>
       </c>
       <c r="R234" t="n">
-        <v>7010155</v>
+        <v>7010085</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23822,7 +23822,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127311025</v>
+        <v>127311024</v>
       </c>
       <c r="B235" t="n">
         <v>91628</v>
@@ -23857,10 +23857,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443634</v>
+        <v>443987</v>
       </c>
       <c r="R235" t="n">
-        <v>7009878</v>
+        <v>7010155</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23919,10 +23919,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127311027</v>
+        <v>127310988</v>
       </c>
       <c r="B236" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23930,21 +23930,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23954,10 +23954,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>444316</v>
+        <v>443937</v>
       </c>
       <c r="R236" t="n">
-        <v>7010269</v>
+        <v>7010167</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24016,10 +24016,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127310988</v>
+        <v>127311025</v>
       </c>
       <c r="B237" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24027,21 +24027,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24051,10 +24051,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>443937</v>
+        <v>443634</v>
       </c>
       <c r="R237" t="n">
-        <v>7010167</v>
+        <v>7009878</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24113,32 +24113,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127311004</v>
+        <v>127311029</v>
       </c>
       <c r="B238" t="n">
-        <v>75142</v>
+        <v>75066</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6486</v>
+        <v>1460</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24148,10 +24148,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>444086</v>
+        <v>444127</v>
       </c>
       <c r="R238" t="n">
-        <v>7010102</v>
+        <v>7010058</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24307,32 +24307,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127311029</v>
+        <v>127311004</v>
       </c>
       <c r="B240" t="n">
-        <v>75066</v>
+        <v>75142</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1460</v>
+        <v>6486</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24342,10 +24342,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>444127</v>
+        <v>444086</v>
       </c>
       <c r="R240" t="n">
-        <v>7010058</v>
+        <v>7010102</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24404,10 +24404,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127311023</v>
+        <v>127311048</v>
       </c>
       <c r="B241" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24415,21 +24415,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24439,10 +24439,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>444039</v>
+        <v>444000</v>
       </c>
       <c r="R241" t="n">
-        <v>7010073</v>
+        <v>7009885</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24501,10 +24501,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127311053</v>
+        <v>127311023</v>
       </c>
       <c r="B242" t="n">
-        <v>79020</v>
+        <v>91628</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24512,21 +24512,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24536,10 +24536,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>443960</v>
+        <v>444039</v>
       </c>
       <c r="R242" t="n">
-        <v>7010126</v>
+        <v>7010073</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24598,32 +24598,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127311007</v>
+        <v>127310991</v>
       </c>
       <c r="B243" t="n">
-        <v>75142</v>
+        <v>91332</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6486</v>
+        <v>1202</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24633,10 +24633,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>443893</v>
+        <v>443609</v>
       </c>
       <c r="R243" t="n">
-        <v>7010175</v>
+        <v>7009974</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24695,10 +24695,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127311048</v>
+        <v>127311053</v>
       </c>
       <c r="B244" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24706,21 +24706,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -24730,10 +24730,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>444000</v>
+        <v>443960</v>
       </c>
       <c r="R244" t="n">
-        <v>7009885</v>
+        <v>7010126</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24792,32 +24792,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127310991</v>
+        <v>127311007</v>
       </c>
       <c r="B245" t="n">
-        <v>91332</v>
+        <v>75142</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -24827,10 +24827,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>443609</v>
+        <v>443893</v>
       </c>
       <c r="R245" t="n">
-        <v>7009974</v>
+        <v>7010175</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25471,32 +25471,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127311009</v>
+        <v>127311014</v>
       </c>
       <c r="B252" t="n">
-        <v>80124</v>
+        <v>91786</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25506,10 +25506,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>444133</v>
+        <v>443719</v>
       </c>
       <c r="R252" t="n">
-        <v>7010104</v>
+        <v>7009858</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25568,10 +25568,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127311010</v>
+        <v>127310992</v>
       </c>
       <c r="B253" t="n">
-        <v>80124</v>
+        <v>91332</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25579,21 +25579,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>443921</v>
+        <v>443635</v>
       </c>
       <c r="R253" t="n">
-        <v>7010190</v>
+        <v>7009927</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25665,32 +25665,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127311014</v>
+        <v>127311009</v>
       </c>
       <c r="B254" t="n">
-        <v>91786</v>
+        <v>80124</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -25700,10 +25700,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>443719</v>
+        <v>444133</v>
       </c>
       <c r="R254" t="n">
-        <v>7009858</v>
+        <v>7010104</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25762,10 +25762,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127310992</v>
+        <v>127311010</v>
       </c>
       <c r="B255" t="n">
-        <v>91332</v>
+        <v>80124</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -25773,21 +25773,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -25797,10 +25797,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>443635</v>
+        <v>443921</v>
       </c>
       <c r="R255" t="n">
-        <v>7009927</v>
+        <v>7010190</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26053,32 +26053,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127311001</v>
+        <v>127311043</v>
       </c>
       <c r="B258" t="n">
-        <v>92034</v>
+        <v>80123</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>443716</v>
+        <v>443639</v>
       </c>
       <c r="R258" t="n">
-        <v>7010053</v>
+        <v>7010011</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26344,32 +26344,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127311043</v>
+        <v>127311001</v>
       </c>
       <c r="B261" t="n">
-        <v>80123</v>
+        <v>92034</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26379,10 +26379,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>443639</v>
+        <v>443716</v>
       </c>
       <c r="R261" t="n">
-        <v>7010011</v>
+        <v>7010053</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26441,7 +26441,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127063410</v>
+        <v>127063414</v>
       </c>
       <c r="B262" t="n">
         <v>57663</v>
@@ -26476,10 +26476,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>444171</v>
+        <v>444463</v>
       </c>
       <c r="R262" t="n">
-        <v>7010149</v>
+        <v>7010311</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -26543,7 +26543,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127063414</v>
+        <v>127063410</v>
       </c>
       <c r="B263" t="n">
         <v>57663</v>
@@ -26578,10 +26578,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>444463</v>
+        <v>444171</v>
       </c>
       <c r="R263" t="n">
-        <v>7010311</v>
+        <v>7010149</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26618,7 +26618,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD263" t="b">

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -6927,10 +6927,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127171730</v>
+        <v>127171798</v>
       </c>
       <c r="B66" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443904</v>
+        <v>443680</v>
       </c>
       <c r="R66" t="n">
-        <v>7010041</v>
+        <v>7009642</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7024,10 +7024,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127171798</v>
+        <v>127171725</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>75144</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443680</v>
+        <v>443925</v>
       </c>
       <c r="R67" t="n">
-        <v>7009642</v>
+        <v>7010042</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127171725</v>
+        <v>127171730</v>
       </c>
       <c r="B68" t="n">
-        <v>75144</v>
+        <v>91332</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443925</v>
+        <v>443904</v>
       </c>
       <c r="R68" t="n">
-        <v>7010042</v>
+        <v>7010041</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -12636,45 +12636,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127299818</v>
+        <v>127303905</v>
       </c>
       <c r="B124" t="n">
-        <v>75142</v>
+        <v>75066</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6486</v>
+        <v>1460</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444299</v>
+        <v>444019</v>
       </c>
       <c r="R124" t="n">
-        <v>7010246</v>
+        <v>7010089</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12704,11 +12704,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -12717,61 +12727,76 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127299830</v>
+        <v>127302629</v>
       </c>
       <c r="B125" t="n">
-        <v>92002</v>
+        <v>91332</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444057</v>
+        <v>443988</v>
       </c>
       <c r="R125" t="n">
-        <v>7010071</v>
+        <v>7010097</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12818,22 +12843,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127299819</v>
+        <v>127303899</v>
       </c>
       <c r="B126" t="n">
-        <v>91628</v>
+        <v>79020</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12841,34 +12866,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444269</v>
+        <v>444289</v>
       </c>
       <c r="R126" t="n">
-        <v>7010299</v>
+        <v>7010247</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,9 +12923,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -12915,57 +12950,57 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127303905</v>
+        <v>127299830</v>
       </c>
       <c r="B127" t="n">
-        <v>75066</v>
+        <v>92002</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1460</v>
+        <v>898</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444019</v>
+        <v>444057</v>
       </c>
       <c r="R127" t="n">
-        <v>7010089</v>
+        <v>7010071</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,21 +13030,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13018,41 +13043,26 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127302629</v>
+        <v>127299819</v>
       </c>
       <c r="B128" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13060,34 +13070,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443988</v>
+        <v>444269</v>
       </c>
       <c r="R128" t="n">
-        <v>7010097</v>
+        <v>7010299</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13134,57 +13144,57 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127303899</v>
+        <v>127299818</v>
       </c>
       <c r="B129" t="n">
-        <v>79020</v>
+        <v>75142</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444289</v>
+        <v>444299</v>
       </c>
       <c r="R129" t="n">
-        <v>7010247</v>
+        <v>7010246</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,19 +13224,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>20:30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13241,12 +13241,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14007,45 +14007,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127302666</v>
+        <v>127303920</v>
       </c>
       <c r="B137" t="n">
-        <v>91328</v>
+        <v>100539</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>222771</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443769</v>
+        <v>443902</v>
       </c>
       <c r="R137" t="n">
-        <v>7010089</v>
+        <v>7010174</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14075,9 +14075,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14092,22 +14107,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127302668</v>
+        <v>127302666</v>
       </c>
       <c r="B138" t="n">
-        <v>91346</v>
+        <v>91328</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14115,21 +14130,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14139,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443816</v>
+        <v>443769</v>
       </c>
       <c r="R138" t="n">
-        <v>7009788</v>
+        <v>7010089</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14201,7 +14216,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302670</v>
+        <v>127302668</v>
       </c>
       <c r="B139" t="n">
         <v>91346</v>
@@ -14236,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444114</v>
+        <v>443816</v>
       </c>
       <c r="R139" t="n">
-        <v>7010064</v>
+        <v>7009788</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14298,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127302658</v>
+        <v>127302670</v>
       </c>
       <c r="B140" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14309,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14333,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443777</v>
+        <v>444114</v>
       </c>
       <c r="R140" t="n">
-        <v>7010050</v>
+        <v>7010064</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14395,45 +14410,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127303920</v>
+        <v>127302658</v>
       </c>
       <c r="B141" t="n">
-        <v>100539</v>
+        <v>91628</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443902</v>
+        <v>443777</v>
       </c>
       <c r="R141" t="n">
-        <v>7010174</v>
+        <v>7010050</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14463,24 +14478,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14495,12 +14495,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15632,7 +15632,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127302638</v>
+        <v>127299813</v>
       </c>
       <c r="B153" t="n">
         <v>91332</v>
@@ -15663,14 +15663,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443679</v>
+        <v>444303</v>
       </c>
       <c r="R153" t="n">
-        <v>7009870</v>
+        <v>7010251</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15717,22 +15717,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127303930</v>
+        <v>127302638</v>
       </c>
       <c r="B154" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15740,34 +15740,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443689</v>
+        <v>443679</v>
       </c>
       <c r="R154" t="n">
-        <v>7009719</v>
+        <v>7009870</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15797,21 +15797,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -15820,76 +15810,61 @@
       </c>
       <c r="AG154" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127302644</v>
+        <v>127303930</v>
       </c>
       <c r="B155" t="n">
-        <v>91786</v>
+        <v>91628</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443970</v>
+        <v>443689</v>
       </c>
       <c r="R155" t="n">
-        <v>7009897</v>
+        <v>7009719</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15919,75 +15894,99 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127299813</v>
+        <v>127302644</v>
       </c>
       <c r="B156" t="n">
-        <v>91332</v>
+        <v>91786</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>444303</v>
+        <v>443970</v>
       </c>
       <c r="R156" t="n">
-        <v>7010251</v>
+        <v>7009897</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16028,18 +16027,19 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16143,10 +16143,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127302652</v>
+        <v>127299814</v>
       </c>
       <c r="B158" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16154,34 +16154,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443999</v>
+        <v>444084</v>
       </c>
       <c r="R158" t="n">
-        <v>7010076</v>
+        <v>7010048</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16228,22 +16228,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127303932</v>
+        <v>127302652</v>
       </c>
       <c r="B159" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16251,34 +16251,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443689</v>
+        <v>443999</v>
       </c>
       <c r="R159" t="n">
-        <v>7009719</v>
+        <v>7010076</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16308,21 +16308,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -16331,41 +16321,26 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127303915</v>
+        <v>127303932</v>
       </c>
       <c r="B160" t="n">
-        <v>79101</v>
+        <v>91332</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16373,21 +16348,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16397,10 +16372,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443965</v>
+        <v>443689</v>
       </c>
       <c r="R160" t="n">
-        <v>7010163</v>
+        <v>7009719</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16432,7 +16407,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16442,7 +16417,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16484,45 +16459,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127302664</v>
+        <v>127303915</v>
       </c>
       <c r="B161" t="n">
-        <v>79179</v>
+        <v>79101</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443777</v>
+        <v>443965</v>
       </c>
       <c r="R161" t="n">
-        <v>7010051</v>
+        <v>7010163</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16552,11 +16527,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -16565,61 +16550,76 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127299814</v>
+        <v>127302664</v>
       </c>
       <c r="B162" t="n">
-        <v>91332</v>
+        <v>79179</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>444084</v>
+        <v>443777</v>
       </c>
       <c r="R162" t="n">
-        <v>7010048</v>
+        <v>7010051</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16666,12 +16666,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17092,10 +17092,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127302678</v>
+        <v>127299823</v>
       </c>
       <c r="B167" t="n">
-        <v>91350</v>
+        <v>80123</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17103,34 +17103,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>443705</v>
+        <v>444412</v>
       </c>
       <c r="R167" t="n">
-        <v>7009844</v>
+        <v>7010433</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17177,57 +17177,57 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127303912</v>
+        <v>127302678</v>
       </c>
       <c r="B168" t="n">
-        <v>75142</v>
+        <v>91350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443984</v>
+        <v>443705</v>
       </c>
       <c r="R168" t="n">
-        <v>7010138</v>
+        <v>7009844</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17257,19 +17257,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>19:01</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>19:01</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17284,22 +17274,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127302665</v>
+        <v>127302628</v>
       </c>
       <c r="B169" t="n">
-        <v>91739</v>
+        <v>91332</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17307,16 +17297,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17326,10 +17321,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>444252</v>
+        <v>443999</v>
       </c>
       <c r="R169" t="n">
-        <v>7010193</v>
+        <v>7010076</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17370,7 +17365,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17389,45 +17383,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127299823</v>
+        <v>127303912</v>
       </c>
       <c r="B170" t="n">
-        <v>80123</v>
+        <v>75142</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>6486</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>444412</v>
+        <v>443984</v>
       </c>
       <c r="R170" t="n">
-        <v>7010433</v>
+        <v>7010138</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17457,9 +17451,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17474,22 +17478,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127302628</v>
+        <v>127302665</v>
       </c>
       <c r="B171" t="n">
-        <v>91332</v>
+        <v>91739</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17497,21 +17501,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17521,10 +17520,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>443999</v>
+        <v>444252</v>
       </c>
       <c r="R171" t="n">
-        <v>7010076</v>
+        <v>7010193</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17565,6 +17564,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17583,10 +17583,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127299822</v>
+        <v>127302673</v>
       </c>
       <c r="B172" t="n">
-        <v>80123</v>
+        <v>91346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17594,34 +17594,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>444113</v>
+        <v>443884</v>
       </c>
       <c r="R172" t="n">
-        <v>7010093</v>
+        <v>7010169</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17668,22 +17668,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127302673</v>
+        <v>127302633</v>
       </c>
       <c r="B173" t="n">
-        <v>91346</v>
+        <v>91332</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17691,21 +17691,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17715,10 +17715,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443884</v>
+        <v>443747</v>
       </c>
       <c r="R173" t="n">
-        <v>7010169</v>
+        <v>7010019</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17777,10 +17777,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302633</v>
+        <v>127302651</v>
       </c>
       <c r="B174" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443747</v>
+        <v>444007</v>
       </c>
       <c r="R174" t="n">
-        <v>7010019</v>
+        <v>7010058</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17874,10 +17874,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127302651</v>
+        <v>127299822</v>
       </c>
       <c r="B175" t="n">
-        <v>91628</v>
+        <v>80123</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17885,34 +17885,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>444007</v>
+        <v>444113</v>
       </c>
       <c r="R175" t="n">
-        <v>7010058</v>
+        <v>7010093</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17959,12 +17959,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -21688,32 +21688,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310996</v>
+        <v>127310989</v>
       </c>
       <c r="B213" t="n">
-        <v>92029</v>
+        <v>91332</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21723,10 +21723,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>444091</v>
+        <v>443910</v>
       </c>
       <c r="R213" t="n">
-        <v>7010088</v>
+        <v>7010191</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21785,32 +21785,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127311033</v>
+        <v>127311037</v>
       </c>
       <c r="B214" t="n">
-        <v>75066</v>
+        <v>79179</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1460</v>
+        <v>1249</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21820,10 +21820,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>444055</v>
+        <v>443844</v>
       </c>
       <c r="R214" t="n">
-        <v>7010052</v>
+        <v>7009886</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21882,32 +21882,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127311036</v>
+        <v>127310996</v>
       </c>
       <c r="B215" t="n">
-        <v>91701</v>
+        <v>92029</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1506</v>
+        <v>3298</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21917,10 +21917,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>443694</v>
+        <v>444091</v>
       </c>
       <c r="R215" t="n">
-        <v>7009882</v>
+        <v>7010088</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21979,10 +21979,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127310989</v>
+        <v>127311033</v>
       </c>
       <c r="B216" t="n">
-        <v>91332</v>
+        <v>75066</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21990,21 +21990,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22014,10 +22014,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>443910</v>
+        <v>444055</v>
       </c>
       <c r="R216" t="n">
-        <v>7010191</v>
+        <v>7010052</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22076,10 +22076,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127311037</v>
+        <v>127311036</v>
       </c>
       <c r="B217" t="n">
-        <v>79179</v>
+        <v>91701</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22087,21 +22087,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1249</v>
+        <v>1506</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22111,10 +22111,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>443844</v>
+        <v>443694</v>
       </c>
       <c r="R217" t="n">
-        <v>7009886</v>
+        <v>7009882</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22270,32 +22270,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127311012</v>
+        <v>127311054</v>
       </c>
       <c r="B219" t="n">
-        <v>91786</v>
+        <v>79020</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22305,10 +22305,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>443967</v>
+        <v>443698</v>
       </c>
       <c r="R219" t="n">
-        <v>7010143</v>
+        <v>7010030</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22367,32 +22367,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127311054</v>
+        <v>127311012</v>
       </c>
       <c r="B220" t="n">
-        <v>79020</v>
+        <v>91786</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22402,10 +22402,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>443698</v>
+        <v>443967</v>
       </c>
       <c r="R220" t="n">
-        <v>7010030</v>
+        <v>7010143</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24889,10 +24889,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127311008</v>
+        <v>127311038</v>
       </c>
       <c r="B246" t="n">
-        <v>75142</v>
+        <v>79179</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -24900,21 +24900,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -24924,10 +24924,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>443750</v>
+        <v>444108</v>
       </c>
       <c r="R246" t="n">
-        <v>7010074</v>
+        <v>7010013</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -24986,10 +24986,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127311038</v>
+        <v>127311008</v>
       </c>
       <c r="B247" t="n">
-        <v>79179</v>
+        <v>75142</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24997,21 +24997,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25021,10 +25021,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>444108</v>
+        <v>443750</v>
       </c>
       <c r="R247" t="n">
-        <v>7010013</v>
+        <v>7010074</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26053,10 +26053,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127311043</v>
+        <v>127310985</v>
       </c>
       <c r="B258" t="n">
-        <v>80123</v>
+        <v>91332</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26064,21 +26064,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>443639</v>
+        <v>444090</v>
       </c>
       <c r="R258" t="n">
-        <v>7010011</v>
+        <v>7009966</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26150,7 +26150,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127310985</v>
+        <v>127310984</v>
       </c>
       <c r="B259" t="n">
         <v>91332</v>
@@ -26185,10 +26185,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>444090</v>
+        <v>444048</v>
       </c>
       <c r="R259" t="n">
-        <v>7009966</v>
+        <v>7009932</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26247,32 +26247,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127310984</v>
+        <v>127311001</v>
       </c>
       <c r="B260" t="n">
-        <v>91332</v>
+        <v>92034</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26282,10 +26282,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>444048</v>
+        <v>443716</v>
       </c>
       <c r="R260" t="n">
-        <v>7009932</v>
+        <v>7010053</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26344,32 +26344,32 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127311001</v>
+        <v>127311043</v>
       </c>
       <c r="B261" t="n">
-        <v>92034</v>
+        <v>80123</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26379,10 +26379,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>443716</v>
+        <v>443639</v>
       </c>
       <c r="R261" t="n">
-        <v>7010053</v>
+        <v>7010011</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127054772</v>
+        <v>127054791</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443748</v>
+        <v>444024</v>
       </c>
       <c r="R5" t="n">
-        <v>7009749</v>
+        <v>7009956</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127054791</v>
+        <v>127054772</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444024</v>
+        <v>443748</v>
       </c>
       <c r="R6" t="n">
-        <v>7009956</v>
+        <v>7009749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127054790</v>
+        <v>127054762</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>75144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443700</v>
+        <v>443835</v>
       </c>
       <c r="R10" t="n">
-        <v>7009788</v>
+        <v>7010003</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127054762</v>
+        <v>127054790</v>
       </c>
       <c r="B11" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443835</v>
+        <v>443700</v>
       </c>
       <c r="R11" t="n">
-        <v>7010003</v>
+        <v>7009788</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127054785</v>
+        <v>127054792</v>
       </c>
       <c r="B20" t="n">
-        <v>91346</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443748</v>
+        <v>443826</v>
       </c>
       <c r="R20" t="n">
-        <v>7009749</v>
+        <v>7009979</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127054792</v>
+        <v>127054785</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>91346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443826</v>
+        <v>443748</v>
       </c>
       <c r="R21" t="n">
-        <v>7009979</v>
+        <v>7009749</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127054779</v>
+        <v>127054789</v>
       </c>
       <c r="B22" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443684</v>
+        <v>443770</v>
       </c>
       <c r="R22" t="n">
-        <v>7009641</v>
+        <v>7009721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2834,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127054789</v>
+        <v>127054779</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443770</v>
+        <v>443684</v>
       </c>
       <c r="R24" t="n">
-        <v>7009721</v>
+        <v>7009641</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,6 +2900,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127171750</v>
+        <v>127171795</v>
       </c>
       <c r="B38" t="n">
-        <v>75142</v>
+        <v>91350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443811</v>
+        <v>443763</v>
       </c>
       <c r="R38" t="n">
-        <v>7009946</v>
+        <v>7009828</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127171733</v>
+        <v>127171794</v>
       </c>
       <c r="B39" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443799</v>
+        <v>443868</v>
       </c>
       <c r="R39" t="n">
-        <v>7009908</v>
+        <v>7009783</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127171772</v>
+        <v>127171750</v>
       </c>
       <c r="B40" t="n">
-        <v>91628</v>
+        <v>75142</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443665</v>
+        <v>443811</v>
       </c>
       <c r="R40" t="n">
-        <v>7009633</v>
+        <v>7009946</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127171795</v>
+        <v>127171733</v>
       </c>
       <c r="B41" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443763</v>
+        <v>443799</v>
       </c>
       <c r="R41" t="n">
-        <v>7009828</v>
+        <v>7009908</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127171794</v>
+        <v>127171772</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443868</v>
+        <v>443665</v>
       </c>
       <c r="R42" t="n">
-        <v>7009783</v>
+        <v>7009633</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127171748</v>
+        <v>127171778</v>
       </c>
       <c r="B44" t="n">
-        <v>75142</v>
+        <v>79179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4792,21 +4792,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6486</v>
+        <v>1249</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444052</v>
+        <v>443849</v>
       </c>
       <c r="R44" t="n">
-        <v>7010134</v>
+        <v>7010007</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127171757</v>
+        <v>127171797</v>
       </c>
       <c r="B45" t="n">
-        <v>91786</v>
+        <v>91350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443706</v>
+        <v>443694</v>
       </c>
       <c r="R45" t="n">
-        <v>7009637</v>
+        <v>7009702</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4975,32 +4975,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127171797</v>
+        <v>127171739</v>
       </c>
       <c r="B46" t="n">
-        <v>91350</v>
+        <v>92029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443694</v>
+        <v>444045</v>
       </c>
       <c r="R46" t="n">
-        <v>7009702</v>
+        <v>7010113</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5072,32 +5072,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127171739</v>
+        <v>127171748</v>
       </c>
       <c r="B47" t="n">
-        <v>92029</v>
+        <v>75142</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>6486</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444045</v>
+        <v>444052</v>
       </c>
       <c r="R47" t="n">
-        <v>7010113</v>
+        <v>7010134</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127171778</v>
+        <v>127171757</v>
       </c>
       <c r="B48" t="n">
-        <v>79179</v>
+        <v>91786</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1249</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443849</v>
+        <v>443706</v>
       </c>
       <c r="R48" t="n">
-        <v>7010007</v>
+        <v>7009637</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5460,32 +5460,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171747</v>
+        <v>127171763</v>
       </c>
       <c r="B51" t="n">
-        <v>75142</v>
+        <v>91628</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443962</v>
+        <v>444018</v>
       </c>
       <c r="R51" t="n">
-        <v>7009915</v>
+        <v>7010190</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171763</v>
+        <v>127171762</v>
       </c>
       <c r="B52" t="n">
         <v>91628</v>
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444018</v>
+        <v>443999</v>
       </c>
       <c r="R52" t="n">
-        <v>7010190</v>
+        <v>7010217</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5654,7 +5654,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127171762</v>
+        <v>127171760</v>
       </c>
       <c r="B53" t="n">
         <v>91628</v>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443999</v>
+        <v>443882</v>
       </c>
       <c r="R53" t="n">
-        <v>7010217</v>
+        <v>7009800</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5751,32 +5751,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127171760</v>
+        <v>127171774</v>
       </c>
       <c r="B54" t="n">
-        <v>91628</v>
+        <v>79179</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1249</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443882</v>
+        <v>443612</v>
       </c>
       <c r="R54" t="n">
-        <v>7009800</v>
+        <v>7009871</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5945,45 +5945,57 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127171774</v>
+        <v>127171746</v>
       </c>
       <c r="B56" t="n">
-        <v>79179</v>
+        <v>57660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1249</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443612</v>
+        <v>443702</v>
       </c>
       <c r="R56" t="n">
-        <v>7009871</v>
+        <v>7009658</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6042,57 +6054,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127171746</v>
+        <v>127171747</v>
       </c>
       <c r="B57" t="n">
-        <v>57660</v>
+        <v>75142</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6486</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443702</v>
+        <v>443962</v>
       </c>
       <c r="R57" t="n">
-        <v>7009658</v>
+        <v>7009915</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7218,32 +7218,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127171744</v>
+        <v>127171796</v>
       </c>
       <c r="B69" t="n">
-        <v>80152</v>
+        <v>91350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443782</v>
+        <v>443799</v>
       </c>
       <c r="R69" t="n">
-        <v>7009804</v>
+        <v>7009774</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,10 +7315,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127171796</v>
+        <v>127171769</v>
       </c>
       <c r="B70" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7326,21 +7326,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443799</v>
+        <v>443709</v>
       </c>
       <c r="R70" t="n">
-        <v>7009774</v>
+        <v>7009666</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,32 +7412,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127171769</v>
+        <v>127171744</v>
       </c>
       <c r="B71" t="n">
-        <v>91628</v>
+        <v>80152</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443709</v>
+        <v>443782</v>
       </c>
       <c r="R71" t="n">
-        <v>7009666</v>
+        <v>7009804</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8576,32 +8576,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127171738</v>
+        <v>127171776</v>
       </c>
       <c r="B83" t="n">
-        <v>92029</v>
+        <v>79179</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8611,10 +8611,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444071</v>
+        <v>444054</v>
       </c>
       <c r="R83" t="n">
-        <v>7010048</v>
+        <v>7010026</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8673,32 +8673,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127171776</v>
+        <v>127171761</v>
       </c>
       <c r="B84" t="n">
-        <v>79179</v>
+        <v>91628</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8711,7 +8711,7 @@
         <v>444054</v>
       </c>
       <c r="R84" t="n">
-        <v>7010026</v>
+        <v>7010086</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8770,32 +8770,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127171761</v>
+        <v>127171738</v>
       </c>
       <c r="B85" t="n">
-        <v>91628</v>
+        <v>92029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444054</v>
+        <v>444071</v>
       </c>
       <c r="R85" t="n">
-        <v>7010086</v>
+        <v>7010048</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8867,32 +8867,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127171751</v>
+        <v>127171801</v>
       </c>
       <c r="B86" t="n">
-        <v>75142</v>
+        <v>88735</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6486</v>
+        <v>510</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443751</v>
+        <v>443690</v>
       </c>
       <c r="R86" t="n">
-        <v>7009735</v>
+        <v>7009636</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8964,32 +8964,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127171801</v>
+        <v>127171777</v>
       </c>
       <c r="B87" t="n">
-        <v>88735</v>
+        <v>79179</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>510</v>
+        <v>1249</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443690</v>
+        <v>444030</v>
       </c>
       <c r="R87" t="n">
-        <v>7009636</v>
+        <v>7010188</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9061,10 +9061,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127171777</v>
+        <v>127171751</v>
       </c>
       <c r="B88" t="n">
-        <v>79179</v>
+        <v>75142</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9072,21 +9072,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9096,10 +9096,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444030</v>
+        <v>443751</v>
       </c>
       <c r="R88" t="n">
-        <v>7010188</v>
+        <v>7009735</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9934,32 +9934,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127171802</v>
+        <v>127171731</v>
       </c>
       <c r="B97" t="n">
-        <v>80158</v>
+        <v>91332</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443853</v>
+        <v>443827</v>
       </c>
       <c r="R97" t="n">
-        <v>7009799</v>
+        <v>7009979</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10031,32 +10031,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127171731</v>
+        <v>127171802</v>
       </c>
       <c r="B98" t="n">
-        <v>91332</v>
+        <v>80158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443827</v>
+        <v>443853</v>
       </c>
       <c r="R98" t="n">
-        <v>7009979</v>
+        <v>7009799</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10322,10 +10322,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127171781</v>
+        <v>127171764</v>
       </c>
       <c r="B101" t="n">
-        <v>80123</v>
+        <v>91628</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10333,21 +10333,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443861</v>
+        <v>443826</v>
       </c>
       <c r="R101" t="n">
-        <v>7009776</v>
+        <v>7009951</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10419,32 +10419,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127171752</v>
+        <v>127171726</v>
       </c>
       <c r="B102" t="n">
-        <v>75142</v>
+        <v>91297</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6486</v>
+        <v>5447</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443685</v>
+        <v>443752</v>
       </c>
       <c r="R102" t="n">
-        <v>7009691</v>
+        <v>7009813</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10516,10 +10516,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127171726</v>
+        <v>127171741</v>
       </c>
       <c r="B103" t="n">
-        <v>91297</v>
+        <v>92029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10527,21 +10527,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10551,10 +10551,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443752</v>
+        <v>443691</v>
       </c>
       <c r="R103" t="n">
-        <v>7009813</v>
+        <v>7009636</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10613,32 +10613,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127171741</v>
+        <v>127171781</v>
       </c>
       <c r="B104" t="n">
-        <v>92029</v>
+        <v>80123</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443691</v>
+        <v>443861</v>
       </c>
       <c r="R104" t="n">
-        <v>7009636</v>
+        <v>7009776</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10710,32 +10710,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127171764</v>
+        <v>127171752</v>
       </c>
       <c r="B105" t="n">
-        <v>91628</v>
+        <v>75142</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10745,10 +10745,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443826</v>
+        <v>443685</v>
       </c>
       <c r="R105" t="n">
-        <v>7009951</v>
+        <v>7009691</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11001,10 +11001,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127302675</v>
+        <v>127302649</v>
       </c>
       <c r="B108" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11012,21 +11012,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443823</v>
+        <v>444329</v>
       </c>
       <c r="R108" t="n">
-        <v>7010119</v>
+        <v>7010232</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11098,45 +11098,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127302632</v>
+        <v>127303918</v>
       </c>
       <c r="B109" t="n">
-        <v>91332</v>
+        <v>97476</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>222741</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443773</v>
+        <v>443944</v>
       </c>
       <c r="R109" t="n">
-        <v>7010102</v>
+        <v>7010169</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11166,9 +11166,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11183,22 +11193,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127302649</v>
+        <v>127302632</v>
       </c>
       <c r="B110" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11206,21 +11216,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11230,10 +11240,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444329</v>
+        <v>443773</v>
       </c>
       <c r="R110" t="n">
-        <v>7010232</v>
+        <v>7010102</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11292,10 +11302,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127302642</v>
+        <v>127302675</v>
       </c>
       <c r="B111" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11303,42 +11313,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444096</v>
+        <v>443823</v>
       </c>
       <c r="R111" t="n">
-        <v>7010088</v>
+        <v>7010119</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11371,11 +11373,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11402,45 +11399,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127303918</v>
+        <v>127302642</v>
       </c>
       <c r="B112" t="n">
-        <v>97476</v>
+        <v>57663</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443944</v>
+        <v>444096</v>
       </c>
       <c r="R112" t="n">
-        <v>7010169</v>
+        <v>7010088</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11470,19 +11475,14 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>18:28</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11497,12 +11497,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127303924</v>
+        <v>127302641</v>
       </c>
       <c r="B117" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,34 +11933,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443651</v>
+        <v>444203</v>
       </c>
       <c r="R117" t="n">
-        <v>7010015</v>
+        <v>7010082</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11990,19 +11990,14 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12013,41 +12008,26 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127302641</v>
+        <v>127299820</v>
       </c>
       <c r="B118" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12055,34 +12035,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444203</v>
+        <v>444007</v>
       </c>
       <c r="R118" t="n">
-        <v>7010082</v>
+        <v>7010102</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12119,7 +12099,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>14 fruktkroppar</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12134,19 +12114,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127299820</v>
+        <v>127303924</v>
       </c>
       <c r="B119" t="n">
         <v>91628</v>
@@ -12177,14 +12157,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444007</v>
+        <v>443651</v>
       </c>
       <c r="R119" t="n">
-        <v>7010102</v>
+        <v>7010015</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12214,14 +12194,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>14 fruktkroppar</t>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12232,16 +12217,31 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127302657</v>
+        <v>127302637</v>
       </c>
       <c r="B121" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12356,21 +12356,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443766</v>
+        <v>443618</v>
       </c>
       <c r="R121" t="n">
-        <v>7010076</v>
+        <v>7009972</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12442,10 +12442,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127302637</v>
+        <v>127302657</v>
       </c>
       <c r="B122" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12453,21 +12453,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12477,10 +12477,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443618</v>
+        <v>443766</v>
       </c>
       <c r="R122" t="n">
-        <v>7009972</v>
+        <v>7010076</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12636,10 +12636,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127303905</v>
+        <v>127302629</v>
       </c>
       <c r="B124" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12647,34 +12647,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444019</v>
+        <v>443988</v>
       </c>
       <c r="R124" t="n">
-        <v>7010089</v>
+        <v>7010097</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12704,21 +12704,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -12727,41 +12717,26 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127302629</v>
+        <v>127303905</v>
       </c>
       <c r="B125" t="n">
-        <v>91332</v>
+        <v>75066</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12769,34 +12744,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443988</v>
+        <v>444019</v>
       </c>
       <c r="R125" t="n">
-        <v>7010097</v>
+        <v>7010089</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12826,11 +12801,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -12839,16 +12824,31 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13253,10 +13253,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127302634</v>
+        <v>127303913</v>
       </c>
       <c r="B130" t="n">
-        <v>91332</v>
+        <v>75066</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13264,34 +13264,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443749</v>
+        <v>443984</v>
       </c>
       <c r="R130" t="n">
-        <v>7010018</v>
+        <v>7010138</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13321,11 +13321,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -13334,26 +13344,41 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127303913</v>
+        <v>127302634</v>
       </c>
       <c r="B131" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13361,34 +13386,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443984</v>
+        <v>443749</v>
       </c>
       <c r="R131" t="n">
-        <v>7010138</v>
+        <v>7010018</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13418,21 +13443,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -13441,31 +13456,16 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13569,45 +13569,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127302660</v>
+        <v>127303916</v>
       </c>
       <c r="B133" t="n">
-        <v>91628</v>
+        <v>75142</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443679</v>
+        <v>443956</v>
       </c>
       <c r="R133" t="n">
-        <v>7009872</v>
+        <v>7010157</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13637,11 +13637,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -13650,48 +13660,63 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127303916</v>
+        <v>127303906</v>
       </c>
       <c r="B134" t="n">
-        <v>75142</v>
+        <v>79106</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6486</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13701,10 +13726,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443956</v>
+        <v>444000</v>
       </c>
       <c r="R134" t="n">
-        <v>7010157</v>
+        <v>7010124</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13736,7 +13761,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -13746,7 +13771,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13788,45 +13813,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127303906</v>
+        <v>127302660</v>
       </c>
       <c r="B135" t="n">
-        <v>79106</v>
+        <v>91628</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6450</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444000</v>
+        <v>443679</v>
       </c>
       <c r="R135" t="n">
-        <v>7010124</v>
+        <v>7009872</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13856,21 +13881,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -13879,31 +13894,16 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14007,45 +14007,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127303920</v>
+        <v>127302666</v>
       </c>
       <c r="B137" t="n">
-        <v>100539</v>
+        <v>91328</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222771</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443902</v>
+        <v>443769</v>
       </c>
       <c r="R137" t="n">
-        <v>7010174</v>
+        <v>7010089</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14075,24 +14075,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14107,22 +14092,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127302666</v>
+        <v>127302668</v>
       </c>
       <c r="B138" t="n">
-        <v>91328</v>
+        <v>91346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,21 +14115,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14139,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443769</v>
+        <v>443816</v>
       </c>
       <c r="R138" t="n">
-        <v>7010089</v>
+        <v>7009788</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14216,7 +14201,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302668</v>
+        <v>127302670</v>
       </c>
       <c r="B139" t="n">
         <v>91346</v>
@@ -14251,10 +14236,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443816</v>
+        <v>444114</v>
       </c>
       <c r="R139" t="n">
-        <v>7009788</v>
+        <v>7010064</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14313,10 +14298,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127302670</v>
+        <v>127302658</v>
       </c>
       <c r="B140" t="n">
-        <v>91346</v>
+        <v>91628</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14309,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14333,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444114</v>
+        <v>443777</v>
       </c>
       <c r="R140" t="n">
-        <v>7010064</v>
+        <v>7010050</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14410,45 +14395,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127302658</v>
+        <v>127303920</v>
       </c>
       <c r="B141" t="n">
-        <v>91628</v>
+        <v>100539</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443777</v>
+        <v>443902</v>
       </c>
       <c r="R141" t="n">
-        <v>7010050</v>
+        <v>7010174</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14478,9 +14463,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14495,57 +14495,57 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127302646</v>
+        <v>127303910</v>
       </c>
       <c r="B142" t="n">
-        <v>91628</v>
+        <v>79276</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>658</v>
+        <v>6459</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443843</v>
+        <v>443992</v>
       </c>
       <c r="R142" t="n">
-        <v>7009837</v>
+        <v>7010143</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14575,11 +14575,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -14588,26 +14598,41 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127302671</v>
+        <v>127302646</v>
       </c>
       <c r="B143" t="n">
-        <v>91346</v>
+        <v>91628</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14615,21 +14640,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14664,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>443664</v>
+        <v>443843</v>
       </c>
       <c r="R143" t="n">
-        <v>7009683</v>
+        <v>7009837</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14798,45 +14823,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127303910</v>
+        <v>127302671</v>
       </c>
       <c r="B145" t="n">
-        <v>79276</v>
+        <v>91346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6459</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443992</v>
+        <v>443664</v>
       </c>
       <c r="R145" t="n">
-        <v>7010143</v>
+        <v>7009683</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14866,21 +14891,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -14889,76 +14904,61 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127303907</v>
+        <v>127302639</v>
       </c>
       <c r="B146" t="n">
-        <v>98783</v>
+        <v>91332</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>444006</v>
+        <v>443697</v>
       </c>
       <c r="R146" t="n">
-        <v>7010126</v>
+        <v>7009873</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14988,19 +14988,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15015,22 +15005,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127302639</v>
+        <v>127303898</v>
       </c>
       <c r="B147" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15038,34 +15028,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>443697</v>
+        <v>444047</v>
       </c>
       <c r="R147" t="n">
-        <v>7009873</v>
+        <v>7009927</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15095,9 +15085,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15112,12 +15112,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -15221,32 +15221,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127303898</v>
+        <v>127303907</v>
       </c>
       <c r="B149" t="n">
-        <v>80123</v>
+        <v>98783</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15256,10 +15256,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>444047</v>
+        <v>444006</v>
       </c>
       <c r="R149" t="n">
-        <v>7009927</v>
+        <v>7010126</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15328,10 +15328,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127302648</v>
+        <v>127299824</v>
       </c>
       <c r="B150" t="n">
-        <v>91628</v>
+        <v>91346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15339,34 +15339,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>444005</v>
+        <v>444076</v>
       </c>
       <c r="R150" t="n">
-        <v>7009910</v>
+        <v>7010048</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15413,22 +15413,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127302643</v>
+        <v>127302648</v>
       </c>
       <c r="B151" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15436,42 +15436,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443735</v>
+        <v>444005</v>
       </c>
       <c r="R151" t="n">
-        <v>7009851</v>
+        <v>7009910</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15504,11 +15496,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15535,10 +15522,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127299824</v>
+        <v>127302643</v>
       </c>
       <c r="B152" t="n">
-        <v>91346</v>
+        <v>57663</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15546,34 +15533,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>444076</v>
+        <v>443735</v>
       </c>
       <c r="R152" t="n">
-        <v>7010048</v>
+        <v>7009851</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15608,6 +15603,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -15620,19 +15620,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127299813</v>
+        <v>127302638</v>
       </c>
       <c r="B153" t="n">
         <v>91332</v>
@@ -15663,14 +15663,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>444303</v>
+        <v>443679</v>
       </c>
       <c r="R153" t="n">
-        <v>7010251</v>
+        <v>7009870</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15717,44 +15717,44 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127302638</v>
+        <v>127302644</v>
       </c>
       <c r="B154" t="n">
-        <v>91332</v>
+        <v>91786</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15764,10 +15764,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443679</v>
+        <v>443970</v>
       </c>
       <c r="R154" t="n">
-        <v>7009870</v>
+        <v>7009897</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15808,6 +15808,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -15826,10 +15827,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127303930</v>
+        <v>127299813</v>
       </c>
       <c r="B155" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15837,34 +15838,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443689</v>
+        <v>444303</v>
       </c>
       <c r="R155" t="n">
-        <v>7009719</v>
+        <v>7010251</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15894,21 +15895,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -15917,76 +15908,61 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127302644</v>
+        <v>127303930</v>
       </c>
       <c r="B156" t="n">
-        <v>91786</v>
+        <v>91628</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443970</v>
+        <v>443689</v>
       </c>
       <c r="R156" t="n">
-        <v>7009897</v>
+        <v>7009719</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16016,75 +15992,99 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127299821</v>
+        <v>127302664</v>
       </c>
       <c r="B157" t="n">
-        <v>91628</v>
+        <v>79179</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>1249</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>444255</v>
+        <v>443777</v>
       </c>
       <c r="R157" t="n">
-        <v>7010318</v>
+        <v>7010051</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16131,12 +16131,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16240,7 +16240,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127302652</v>
+        <v>127299821</v>
       </c>
       <c r="B159" t="n">
         <v>91628</v>
@@ -16271,14 +16271,14 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443999</v>
+        <v>444255</v>
       </c>
       <c r="R159" t="n">
-        <v>7010076</v>
+        <v>7010318</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16325,12 +16325,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16581,32 +16581,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127302664</v>
+        <v>127302652</v>
       </c>
       <c r="B162" t="n">
-        <v>79179</v>
+        <v>91628</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16616,10 +16616,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443777</v>
+        <v>443999</v>
       </c>
       <c r="R162" t="n">
-        <v>7010051</v>
+        <v>7010076</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16678,10 +16678,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127303914</v>
+        <v>127299827</v>
       </c>
       <c r="B163" t="n">
-        <v>75066</v>
+        <v>91350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16689,34 +16689,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1460</v>
+        <v>5432</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>443985</v>
+        <v>444241</v>
       </c>
       <c r="R163" t="n">
-        <v>7010134</v>
+        <v>7010317</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16746,21 +16746,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -16769,31 +16759,16 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -16897,45 +16872,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127302645</v>
+        <v>127303914</v>
       </c>
       <c r="B165" t="n">
-        <v>91786</v>
+        <v>75066</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1209</v>
+        <v>1460</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>443997</v>
+        <v>443985</v>
       </c>
       <c r="R165" t="n">
-        <v>7010102</v>
+        <v>7010134</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16965,75 +16940,99 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127299827</v>
+        <v>127302645</v>
       </c>
       <c r="B166" t="n">
-        <v>91350</v>
+        <v>91786</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>444241</v>
+        <v>443997</v>
       </c>
       <c r="R166" t="n">
-        <v>7010317</v>
+        <v>7010102</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17074,28 +17073,29 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127299823</v>
+        <v>127302628</v>
       </c>
       <c r="B167" t="n">
-        <v>80123</v>
+        <v>91332</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17103,34 +17103,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>444412</v>
+        <v>443999</v>
       </c>
       <c r="R167" t="n">
-        <v>7010433</v>
+        <v>7010076</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17177,22 +17177,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127302678</v>
+        <v>127299823</v>
       </c>
       <c r="B168" t="n">
-        <v>91350</v>
+        <v>80123</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17200,34 +17200,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443705</v>
+        <v>444412</v>
       </c>
       <c r="R168" t="n">
-        <v>7009844</v>
+        <v>7010433</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17274,57 +17274,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127302628</v>
+        <v>127303912</v>
       </c>
       <c r="B169" t="n">
-        <v>91332</v>
+        <v>75142</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443999</v>
+        <v>443984</v>
       </c>
       <c r="R169" t="n">
-        <v>7010076</v>
+        <v>7010138</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17354,9 +17354,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17371,57 +17381,57 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127303912</v>
+        <v>127302678</v>
       </c>
       <c r="B170" t="n">
-        <v>75142</v>
+        <v>91350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>443984</v>
+        <v>443705</v>
       </c>
       <c r="R170" t="n">
-        <v>7010138</v>
+        <v>7009844</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17451,19 +17461,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>19:01</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>19:01</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17478,12 +17478,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -17583,10 +17583,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127302673</v>
+        <v>127299822</v>
       </c>
       <c r="B172" t="n">
-        <v>91346</v>
+        <v>80123</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17594,34 +17594,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>443884</v>
+        <v>444113</v>
       </c>
       <c r="R172" t="n">
-        <v>7010169</v>
+        <v>7010093</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17668,22 +17668,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127302633</v>
+        <v>127302673</v>
       </c>
       <c r="B173" t="n">
-        <v>91332</v>
+        <v>91346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17691,21 +17691,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17715,10 +17715,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443747</v>
+        <v>443884</v>
       </c>
       <c r="R173" t="n">
-        <v>7010019</v>
+        <v>7010169</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17777,10 +17777,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302651</v>
+        <v>127302633</v>
       </c>
       <c r="B174" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>444007</v>
+        <v>443747</v>
       </c>
       <c r="R174" t="n">
-        <v>7010058</v>
+        <v>7010019</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17874,10 +17874,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127299822</v>
+        <v>127302651</v>
       </c>
       <c r="B175" t="n">
-        <v>80123</v>
+        <v>91628</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17885,34 +17885,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>444113</v>
+        <v>444007</v>
       </c>
       <c r="R175" t="n">
-        <v>7010093</v>
+        <v>7010058</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17959,12 +17959,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -18262,7 +18262,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127302654</v>
+        <v>127303909</v>
       </c>
       <c r="B179" t="n">
         <v>91628</v>
@@ -18293,14 +18293,14 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443964</v>
+        <v>443991</v>
       </c>
       <c r="R179" t="n">
-        <v>7010137</v>
+        <v>7010145</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18330,11 +18330,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -18343,23 +18353,38 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127303909</v>
+        <v>127302654</v>
       </c>
       <c r="B180" t="n">
         <v>91628</v>
@@ -18390,14 +18415,14 @@
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443991</v>
+        <v>443964</v>
       </c>
       <c r="R180" t="n">
-        <v>7010145</v>
+        <v>7010137</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18427,21 +18452,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
@@ -18450,41 +18465,26 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127299829</v>
+        <v>127302636</v>
       </c>
       <c r="B181" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18492,34 +18492,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>444259</v>
+        <v>443640</v>
       </c>
       <c r="R181" t="n">
-        <v>7010202</v>
+        <v>7010000</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18566,19 +18566,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127302636</v>
+        <v>127302627</v>
       </c>
       <c r="B182" t="n">
         <v>91332</v>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443640</v>
+        <v>444031</v>
       </c>
       <c r="R182" t="n">
-        <v>7010000</v>
+        <v>7010049</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18675,7 +18675,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127302627</v>
+        <v>127302640</v>
       </c>
       <c r="B183" t="n">
         <v>91332</v>
@@ -18710,10 +18710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>444031</v>
+        <v>443738</v>
       </c>
       <c r="R183" t="n">
-        <v>7010049</v>
+        <v>7009862</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18772,10 +18772,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127302640</v>
+        <v>127299829</v>
       </c>
       <c r="B184" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18783,34 +18783,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443738</v>
+        <v>444259</v>
       </c>
       <c r="R184" t="n">
-        <v>7009862</v>
+        <v>7010202</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18857,12 +18857,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -18966,10 +18966,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127303922</v>
+        <v>127303925</v>
       </c>
       <c r="B186" t="n">
-        <v>91692</v>
+        <v>79179</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18977,21 +18977,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2063</v>
+        <v>1249</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19001,10 +19001,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443745</v>
+        <v>443627</v>
       </c>
       <c r="R186" t="n">
-        <v>7010077</v>
+        <v>7009957</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19058,9 +19058,19 @@
       <c r="AG186" t="b">
         <v>0</v>
       </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>På/intill död granticka på grov granlåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -19078,45 +19088,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127303925</v>
+        <v>127302624</v>
       </c>
       <c r="B187" t="n">
-        <v>79179</v>
+        <v>91332</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443627</v>
+        <v>444005</v>
       </c>
       <c r="R187" t="n">
-        <v>7009957</v>
+        <v>7009910</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19146,21 +19156,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -19169,76 +19169,61 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127302624</v>
+        <v>127303922</v>
       </c>
       <c r="B188" t="n">
-        <v>91332</v>
+        <v>91692</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>444005</v>
+        <v>443745</v>
       </c>
       <c r="R188" t="n">
-        <v>7009910</v>
+        <v>7010077</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19268,11 +19253,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
@@ -19281,16 +19276,21 @@
       </c>
       <c r="AG188" t="b">
         <v>0</v>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>På/intill död granticka på grov granlåga.</t>
+        </is>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
@@ -19419,10 +19419,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127303927</v>
+        <v>127299817</v>
       </c>
       <c r="B190" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19430,34 +19430,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443629</v>
+        <v>444242</v>
       </c>
       <c r="R190" t="n">
-        <v>7009887</v>
+        <v>7010316</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19487,21 +19487,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -19510,41 +19500,26 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127302663</v>
+        <v>127303927</v>
       </c>
       <c r="B191" t="n">
-        <v>91628</v>
+        <v>79020</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19552,34 +19527,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443671</v>
+        <v>443629</v>
       </c>
       <c r="R191" t="n">
-        <v>7009726</v>
+        <v>7009887</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19609,11 +19584,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
@@ -19622,26 +19607,41 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127302672</v>
+        <v>127302663</v>
       </c>
       <c r="B192" t="n">
-        <v>91346</v>
+        <v>91628</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19649,21 +19649,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19673,10 +19673,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443978</v>
+        <v>443671</v>
       </c>
       <c r="R192" t="n">
-        <v>7010133</v>
+        <v>7009726</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19832,10 +19832,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127299817</v>
+        <v>127302672</v>
       </c>
       <c r="B194" t="n">
-        <v>91332</v>
+        <v>91346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19843,34 +19843,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>444242</v>
+        <v>443978</v>
       </c>
       <c r="R194" t="n">
-        <v>7010316</v>
+        <v>7010133</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19917,19 +19917,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127311026</v>
+        <v>127311016</v>
       </c>
       <c r="B195" t="n">
         <v>91628</v>
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443721</v>
+        <v>443914</v>
       </c>
       <c r="R195" t="n">
-        <v>7009852</v>
+        <v>7009959</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20026,45 +20026,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127311016</v>
+        <v>127311483</v>
       </c>
       <c r="B196" t="n">
-        <v>91628</v>
+        <v>92034</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443914</v>
+        <v>443711</v>
       </c>
       <c r="R196" t="n">
-        <v>7009959</v>
+        <v>7010048</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20123,45 +20123,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127311483</v>
+        <v>127311026</v>
       </c>
       <c r="B197" t="n">
-        <v>92034</v>
+        <v>91628</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>67</v>
+        <v>658</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Haratjärnen, Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443711</v>
+        <v>443721</v>
       </c>
       <c r="R197" t="n">
-        <v>7010048</v>
+        <v>7009852</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20317,32 +20317,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127311006</v>
+        <v>127311003</v>
       </c>
       <c r="B199" t="n">
-        <v>75142</v>
+        <v>57505</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6486</v>
+        <v>102621</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>444031</v>
+        <v>443820</v>
       </c>
       <c r="R199" t="n">
-        <v>7010078</v>
+        <v>7009812</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20414,32 +20414,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127311003</v>
+        <v>127311006</v>
       </c>
       <c r="B200" t="n">
-        <v>57505</v>
+        <v>75142</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>102621</v>
+        <v>6486</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20449,10 +20449,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>443820</v>
+        <v>444031</v>
       </c>
       <c r="R200" t="n">
-        <v>7009812</v>
+        <v>7010078</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127311020</v>
+        <v>127311031</v>
       </c>
       <c r="B202" t="n">
-        <v>91628</v>
+        <v>75066</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20619,21 +20619,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>658</v>
+        <v>1460</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>444252</v>
+        <v>444124</v>
       </c>
       <c r="R202" t="n">
-        <v>7010325</v>
+        <v>7010021</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20899,10 +20899,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127311031</v>
+        <v>127311020</v>
       </c>
       <c r="B205" t="n">
-        <v>75066</v>
+        <v>91628</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20910,21 +20910,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20934,10 +20934,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>444124</v>
+        <v>444252</v>
       </c>
       <c r="R205" t="n">
-        <v>7010021</v>
+        <v>7010325</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20996,10 +20996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127311018</v>
+        <v>127310987</v>
       </c>
       <c r="B206" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21007,21 +21007,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21031,10 +21031,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>444250</v>
+        <v>443973</v>
       </c>
       <c r="R206" t="n">
-        <v>7010307</v>
+        <v>7010146</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21093,10 +21093,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127310987</v>
+        <v>127310997</v>
       </c>
       <c r="B207" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21104,34 +21104,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443973</v>
+        <v>443735</v>
       </c>
       <c r="R207" t="n">
-        <v>7010146</v>
+        <v>7009858</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21164,6 +21172,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21190,10 +21203,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127310997</v>
+        <v>127311018</v>
       </c>
       <c r="B208" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21201,42 +21214,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>443735</v>
+        <v>444250</v>
       </c>
       <c r="R208" t="n">
-        <v>7009858</v>
+        <v>7010307</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21269,11 +21274,6 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21688,32 +21688,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310989</v>
+        <v>127310996</v>
       </c>
       <c r="B213" t="n">
-        <v>91332</v>
+        <v>92029</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21723,10 +21723,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>443910</v>
+        <v>444091</v>
       </c>
       <c r="R213" t="n">
-        <v>7010191</v>
+        <v>7010088</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21785,32 +21785,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127311037</v>
+        <v>127310989</v>
       </c>
       <c r="B214" t="n">
-        <v>79179</v>
+        <v>91332</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21820,10 +21820,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>443844</v>
+        <v>443910</v>
       </c>
       <c r="R214" t="n">
-        <v>7009886</v>
+        <v>7010191</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21882,32 +21882,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127310996</v>
+        <v>127311037</v>
       </c>
       <c r="B215" t="n">
-        <v>92029</v>
+        <v>79179</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21917,10 +21917,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>444091</v>
+        <v>443844</v>
       </c>
       <c r="R215" t="n">
-        <v>7010088</v>
+        <v>7009886</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21979,32 +21979,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127311033</v>
+        <v>127311036</v>
       </c>
       <c r="B216" t="n">
-        <v>75066</v>
+        <v>91701</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1460</v>
+        <v>1506</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22014,10 +22014,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>444055</v>
+        <v>443694</v>
       </c>
       <c r="R216" t="n">
-        <v>7010052</v>
+        <v>7009882</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22076,32 +22076,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127311036</v>
+        <v>127311033</v>
       </c>
       <c r="B217" t="n">
-        <v>91701</v>
+        <v>75066</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1506</v>
+        <v>1460</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22111,10 +22111,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>443694</v>
+        <v>444055</v>
       </c>
       <c r="R217" t="n">
-        <v>7009882</v>
+        <v>7010052</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22270,32 +22270,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127311054</v>
+        <v>127311012</v>
       </c>
       <c r="B219" t="n">
-        <v>79020</v>
+        <v>91786</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22305,10 +22305,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>443698</v>
+        <v>443967</v>
       </c>
       <c r="R219" t="n">
-        <v>7010030</v>
+        <v>7010143</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22367,32 +22367,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127311012</v>
+        <v>127311054</v>
       </c>
       <c r="B220" t="n">
-        <v>91786</v>
+        <v>79020</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22402,10 +22402,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>443967</v>
+        <v>443698</v>
       </c>
       <c r="R220" t="n">
-        <v>7010143</v>
+        <v>7010030</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22464,32 +22464,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127311047</v>
+        <v>127310999</v>
       </c>
       <c r="B221" t="n">
-        <v>91346</v>
+        <v>80152</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22499,10 +22499,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>444088</v>
+        <v>444089</v>
       </c>
       <c r="R221" t="n">
-        <v>7010038</v>
+        <v>7010006</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22561,32 +22561,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127310999</v>
+        <v>127311047</v>
       </c>
       <c r="B222" t="n">
-        <v>80152</v>
+        <v>91346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22596,10 +22596,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>444089</v>
+        <v>444088</v>
       </c>
       <c r="R222" t="n">
-        <v>7010006</v>
+        <v>7010038</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22755,10 +22755,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127311034</v>
+        <v>127310995</v>
       </c>
       <c r="B224" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22766,21 +22766,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22790,10 +22790,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>444026</v>
+        <v>443689</v>
       </c>
       <c r="R224" t="n">
-        <v>7010076</v>
+        <v>7009728</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22852,10 +22852,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127311030</v>
+        <v>127310990</v>
       </c>
       <c r="B225" t="n">
-        <v>75066</v>
+        <v>91332</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22863,21 +22863,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>444131</v>
+        <v>443745</v>
       </c>
       <c r="R225" t="n">
-        <v>7010038</v>
+        <v>7010081</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22949,10 +22949,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127310995</v>
+        <v>127311030</v>
       </c>
       <c r="B226" t="n">
-        <v>91332</v>
+        <v>75066</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22960,21 +22960,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443689</v>
+        <v>444131</v>
       </c>
       <c r="R226" t="n">
-        <v>7009728</v>
+        <v>7010038</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23046,10 +23046,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127310990</v>
+        <v>127311034</v>
       </c>
       <c r="B227" t="n">
-        <v>91332</v>
+        <v>75066</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23057,21 +23057,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23081,10 +23081,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>443745</v>
+        <v>444026</v>
       </c>
       <c r="R227" t="n">
-        <v>7010081</v>
+        <v>7010076</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23143,10 +23143,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127311059</v>
+        <v>127310986</v>
       </c>
       <c r="B228" t="n">
-        <v>88735</v>
+        <v>91332</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23154,21 +23154,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23178,10 +23178,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>444272</v>
+        <v>444046</v>
       </c>
       <c r="R228" t="n">
-        <v>7010237</v>
+        <v>7010063</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23240,10 +23240,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127310986</v>
+        <v>127311041</v>
       </c>
       <c r="B229" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23251,21 +23251,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>444046</v>
+        <v>444094</v>
       </c>
       <c r="R229" t="n">
-        <v>7010063</v>
+        <v>7010004</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127311022</v>
+        <v>127311059</v>
       </c>
       <c r="B230" t="n">
-        <v>91628</v>
+        <v>88735</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23348,21 +23348,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23372,10 +23372,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>444108</v>
+        <v>444272</v>
       </c>
       <c r="R230" t="n">
-        <v>7010040</v>
+        <v>7010237</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23434,10 +23434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127311041</v>
+        <v>127311022</v>
       </c>
       <c r="B231" t="n">
-        <v>80123</v>
+        <v>91628</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23445,21 +23445,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444094</v>
+        <v>444108</v>
       </c>
       <c r="R231" t="n">
-        <v>7010004</v>
+        <v>7010040</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23628,10 +23628,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127311051</v>
+        <v>127310988</v>
       </c>
       <c r="B233" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23639,21 +23639,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23663,10 +23663,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>443729</v>
+        <v>443937</v>
       </c>
       <c r="R233" t="n">
-        <v>7009862</v>
+        <v>7010167</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23822,10 +23822,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127311024</v>
+        <v>127311051</v>
       </c>
       <c r="B235" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23833,21 +23833,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23857,10 +23857,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443987</v>
+        <v>443729</v>
       </c>
       <c r="R235" t="n">
-        <v>7010155</v>
+        <v>7009862</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23919,10 +23919,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127310988</v>
+        <v>127311024</v>
       </c>
       <c r="B236" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23930,21 +23930,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23954,10 +23954,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>443937</v>
+        <v>443987</v>
       </c>
       <c r="R236" t="n">
-        <v>7010167</v>
+        <v>7010155</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24113,32 +24113,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127311029</v>
+        <v>127311004</v>
       </c>
       <c r="B238" t="n">
-        <v>75066</v>
+        <v>75142</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1460</v>
+        <v>6486</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24148,10 +24148,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>444127</v>
+        <v>444086</v>
       </c>
       <c r="R238" t="n">
-        <v>7010058</v>
+        <v>7010102</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24307,32 +24307,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127311004</v>
+        <v>127311029</v>
       </c>
       <c r="B240" t="n">
-        <v>75142</v>
+        <v>75066</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6486</v>
+        <v>1460</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24342,10 +24342,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>444086</v>
+        <v>444127</v>
       </c>
       <c r="R240" t="n">
-        <v>7010102</v>
+        <v>7010058</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24404,10 +24404,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127311048</v>
+        <v>127311023</v>
       </c>
       <c r="B241" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24415,21 +24415,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24439,10 +24439,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>444000</v>
+        <v>444039</v>
       </c>
       <c r="R241" t="n">
-        <v>7009885</v>
+        <v>7010073</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24501,10 +24501,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127311023</v>
+        <v>127310991</v>
       </c>
       <c r="B242" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24512,21 +24512,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24536,10 +24536,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>444039</v>
+        <v>443609</v>
       </c>
       <c r="R242" t="n">
-        <v>7010073</v>
+        <v>7009974</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24598,10 +24598,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127310991</v>
+        <v>127311053</v>
       </c>
       <c r="B243" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24609,21 +24609,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24633,10 +24633,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>443609</v>
+        <v>443960</v>
       </c>
       <c r="R243" t="n">
-        <v>7009974</v>
+        <v>7010126</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24695,32 +24695,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127311053</v>
+        <v>127311007</v>
       </c>
       <c r="B244" t="n">
-        <v>79020</v>
+        <v>75142</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -24730,10 +24730,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>443960</v>
+        <v>443893</v>
       </c>
       <c r="R244" t="n">
-        <v>7010126</v>
+        <v>7010175</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24792,32 +24792,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127311007</v>
+        <v>127311048</v>
       </c>
       <c r="B245" t="n">
-        <v>75142</v>
+        <v>91350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -24827,10 +24827,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>443893</v>
+        <v>444000</v>
       </c>
       <c r="R245" t="n">
-        <v>7010175</v>
+        <v>7009885</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25471,32 +25471,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127311014</v>
+        <v>127311009</v>
       </c>
       <c r="B252" t="n">
-        <v>91786</v>
+        <v>80124</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25506,10 +25506,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>443719</v>
+        <v>444133</v>
       </c>
       <c r="R252" t="n">
-        <v>7009858</v>
+        <v>7010104</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25568,10 +25568,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127310992</v>
+        <v>127311010</v>
       </c>
       <c r="B253" t="n">
-        <v>91332</v>
+        <v>80124</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25579,21 +25579,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>443635</v>
+        <v>443921</v>
       </c>
       <c r="R253" t="n">
-        <v>7009927</v>
+        <v>7010190</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25665,32 +25665,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127311009</v>
+        <v>127311014</v>
       </c>
       <c r="B254" t="n">
-        <v>80124</v>
+        <v>91786</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -25700,10 +25700,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>444133</v>
+        <v>443719</v>
       </c>
       <c r="R254" t="n">
-        <v>7010104</v>
+        <v>7009858</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25762,10 +25762,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127311010</v>
+        <v>127310992</v>
       </c>
       <c r="B255" t="n">
-        <v>80124</v>
+        <v>91332</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -25773,21 +25773,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -25797,10 +25797,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>443921</v>
+        <v>443635</v>
       </c>
       <c r="R255" t="n">
-        <v>7010190</v>
+        <v>7009927</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26053,32 +26053,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127310985</v>
+        <v>127311001</v>
       </c>
       <c r="B258" t="n">
-        <v>91332</v>
+        <v>92034</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>444090</v>
+        <v>443716</v>
       </c>
       <c r="R258" t="n">
-        <v>7009966</v>
+        <v>7010053</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26150,7 +26150,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127310984</v>
+        <v>127310985</v>
       </c>
       <c r="B259" t="n">
         <v>91332</v>
@@ -26185,10 +26185,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>444048</v>
+        <v>444090</v>
       </c>
       <c r="R259" t="n">
-        <v>7009932</v>
+        <v>7009966</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26247,32 +26247,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127311001</v>
+        <v>127310984</v>
       </c>
       <c r="B260" t="n">
-        <v>92034</v>
+        <v>91332</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26282,10 +26282,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>443716</v>
+        <v>444048</v>
       </c>
       <c r="R260" t="n">
-        <v>7010053</v>
+        <v>7009932</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -11001,45 +11001,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127302632</v>
+        <v>127303918</v>
       </c>
       <c r="B108" t="n">
-        <v>91350</v>
+        <v>97494</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>222741</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443773</v>
+        <v>443944</v>
       </c>
       <c r="R108" t="n">
-        <v>7010102</v>
+        <v>7010169</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11069,9 +11069,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11086,22 +11096,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127302675</v>
+        <v>127302642</v>
       </c>
       <c r="B109" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11109,34 +11119,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443823</v>
+        <v>444096</v>
       </c>
       <c r="R109" t="n">
-        <v>7010119</v>
+        <v>7010088</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11169,6 +11187,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11195,45 +11218,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127303918</v>
+        <v>127302632</v>
       </c>
       <c r="B110" t="n">
-        <v>97494</v>
+        <v>91350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>222741</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443944</v>
+        <v>443773</v>
       </c>
       <c r="R110" t="n">
-        <v>7010169</v>
+        <v>7010102</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11263,19 +11286,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>18:28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11290,12 +11303,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11399,10 +11412,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127302642</v>
+        <v>127302675</v>
       </c>
       <c r="B112" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11410,42 +11423,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444096</v>
+        <v>443823</v>
       </c>
       <c r="R112" t="n">
-        <v>7010088</v>
+        <v>7010119</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11478,11 +11483,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Troliga gamla bohål, 3-4m upp i bruten grantickeangripen gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11825,7 +11825,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127303924</v>
+        <v>127299820</v>
       </c>
       <c r="B116" t="n">
         <v>91646</v>
@@ -11856,14 +11856,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443651</v>
+        <v>444007</v>
       </c>
       <c r="R116" t="n">
-        <v>7010015</v>
+        <v>7010102</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11893,19 +11893,14 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>14 fruktkroppar</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11916,41 +11911,26 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127302641</v>
+        <v>127303924</v>
       </c>
       <c r="B117" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11958,34 +11938,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444203</v>
+        <v>443651</v>
       </c>
       <c r="R117" t="n">
-        <v>7010082</v>
+        <v>7010015</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12015,14 +11995,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12033,26 +12018,41 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127299820</v>
+        <v>127302641</v>
       </c>
       <c r="B118" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12060,34 +12060,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444007</v>
+        <v>444203</v>
       </c>
       <c r="R118" t="n">
-        <v>7010102</v>
+        <v>7010082</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12124,7 +12124,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>14 fruktkroppar</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12139,12 +12139,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127302657</v>
+        <v>127302637</v>
       </c>
       <c r="B120" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12259,21 +12259,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443766</v>
+        <v>443618</v>
       </c>
       <c r="R120" t="n">
-        <v>7010076</v>
+        <v>7009972</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12345,7 +12345,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127302661</v>
+        <v>127302657</v>
       </c>
       <c r="B121" t="n">
         <v>91646</v>
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443698</v>
+        <v>443766</v>
       </c>
       <c r="R121" t="n">
-        <v>7009876</v>
+        <v>7010076</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12442,10 +12442,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127302676</v>
+        <v>127302661</v>
       </c>
       <c r="B122" t="n">
-        <v>91368</v>
+        <v>91646</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12453,21 +12453,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12477,10 +12477,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443737</v>
+        <v>443698</v>
       </c>
       <c r="R122" t="n">
-        <v>7009850</v>
+        <v>7009876</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127302637</v>
+        <v>127302676</v>
       </c>
       <c r="B123" t="n">
-        <v>91350</v>
+        <v>91368</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12550,21 +12550,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443618</v>
+        <v>443737</v>
       </c>
       <c r="R123" t="n">
-        <v>7009972</v>
+        <v>7009850</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12830,45 +12830,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127302629</v>
+        <v>127299818</v>
       </c>
       <c r="B126" t="n">
-        <v>91350</v>
+        <v>75151</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443988</v>
+        <v>444299</v>
       </c>
       <c r="R126" t="n">
-        <v>7010097</v>
+        <v>7010246</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12915,22 +12915,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127303905</v>
+        <v>127302629</v>
       </c>
       <c r="B127" t="n">
-        <v>75075</v>
+        <v>91350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12938,34 +12938,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444019</v>
+        <v>443988</v>
       </c>
       <c r="R127" t="n">
-        <v>7010089</v>
+        <v>7010097</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,21 +12995,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13018,41 +13008,26 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127303899</v>
+        <v>127303905</v>
       </c>
       <c r="B128" t="n">
-        <v>79029</v>
+        <v>75075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13060,21 +13035,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13084,10 +13059,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444289</v>
+        <v>444019</v>
       </c>
       <c r="R128" t="n">
-        <v>7010247</v>
+        <v>7010089</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13119,7 +13094,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13129,7 +13104,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13140,6 +13115,21 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
@@ -13156,45 +13146,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127299818</v>
+        <v>127303899</v>
       </c>
       <c r="B129" t="n">
-        <v>75151</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444299</v>
+        <v>444289</v>
       </c>
       <c r="R129" t="n">
-        <v>7010246</v>
+        <v>7010247</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13224,9 +13214,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13241,22 +13241,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127303913</v>
+        <v>127302634</v>
       </c>
       <c r="B130" t="n">
-        <v>75075</v>
+        <v>91350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13264,34 +13264,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443984</v>
+        <v>443749</v>
       </c>
       <c r="R130" t="n">
-        <v>7010138</v>
+        <v>7010018</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13321,21 +13321,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -13344,41 +13334,26 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127302634</v>
+        <v>127303913</v>
       </c>
       <c r="B131" t="n">
-        <v>91350</v>
+        <v>75075</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13386,34 +13361,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443749</v>
+        <v>443984</v>
       </c>
       <c r="R131" t="n">
-        <v>7010018</v>
+        <v>7010138</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13443,11 +13418,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -13456,61 +13441,76 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127303906</v>
+        <v>127302669</v>
       </c>
       <c r="B132" t="n">
-        <v>79115</v>
+        <v>91364</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6450</v>
+        <v>1204</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444000</v>
+        <v>443852</v>
       </c>
       <c r="R132" t="n">
-        <v>7010124</v>
+        <v>7009880</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13540,21 +13540,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -13563,76 +13553,61 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127303916</v>
+        <v>127302660</v>
       </c>
       <c r="B133" t="n">
-        <v>75151</v>
+        <v>91646</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443956</v>
+        <v>443679</v>
       </c>
       <c r="R133" t="n">
-        <v>7010157</v>
+        <v>7009872</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13662,21 +13637,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -13685,76 +13650,61 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127302660</v>
+        <v>127303916</v>
       </c>
       <c r="B134" t="n">
-        <v>91646</v>
+        <v>75151</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443679</v>
+        <v>443956</v>
       </c>
       <c r="R134" t="n">
-        <v>7009872</v>
+        <v>7010157</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13784,11 +13734,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -13797,61 +13757,76 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127302669</v>
+        <v>127303906</v>
       </c>
       <c r="B135" t="n">
-        <v>91364</v>
+        <v>79115</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>443852</v>
+        <v>444000</v>
       </c>
       <c r="R135" t="n">
-        <v>7009880</v>
+        <v>7010124</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13881,11 +13856,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -13894,61 +13879,76 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127302658</v>
+        <v>127303920</v>
       </c>
       <c r="B136" t="n">
-        <v>91646</v>
+        <v>100557</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443777</v>
+        <v>443902</v>
       </c>
       <c r="R136" t="n">
-        <v>7010050</v>
+        <v>7010174</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13978,9 +13978,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -13995,57 +14010,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127303920</v>
+        <v>127299816</v>
       </c>
       <c r="B137" t="n">
-        <v>100557</v>
+        <v>91350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443902</v>
+        <v>444022</v>
       </c>
       <c r="R137" t="n">
-        <v>7010174</v>
+        <v>7010055</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14075,24 +14090,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Allmän i sluttningen.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14107,22 +14107,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127299816</v>
+        <v>127302666</v>
       </c>
       <c r="B138" t="n">
-        <v>91350</v>
+        <v>91346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,34 +14130,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444022</v>
+        <v>443769</v>
       </c>
       <c r="R138" t="n">
-        <v>7010055</v>
+        <v>7010089</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14204,22 +14204,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302666</v>
+        <v>127302668</v>
       </c>
       <c r="B139" t="n">
-        <v>91346</v>
+        <v>91364</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14227,21 +14227,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443769</v>
+        <v>443816</v>
       </c>
       <c r="R139" t="n">
-        <v>7010089</v>
+        <v>7009788</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14313,7 +14313,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127302668</v>
+        <v>127302670</v>
       </c>
       <c r="B140" t="n">
         <v>91364</v>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443816</v>
+        <v>444114</v>
       </c>
       <c r="R140" t="n">
-        <v>7009788</v>
+        <v>7010064</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14410,10 +14410,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127302670</v>
+        <v>127302658</v>
       </c>
       <c r="B141" t="n">
-        <v>91364</v>
+        <v>91646</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,21 +14421,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444114</v>
+        <v>443777</v>
       </c>
       <c r="R141" t="n">
-        <v>7010064</v>
+        <v>7010050</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14604,32 +14604,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127302671</v>
+        <v>127302679</v>
       </c>
       <c r="B143" t="n">
-        <v>91364</v>
+        <v>92020</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>443664</v>
+        <v>444009</v>
       </c>
       <c r="R143" t="n">
-        <v>7009683</v>
+        <v>7010058</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14701,32 +14701,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127302679</v>
+        <v>127302671</v>
       </c>
       <c r="B144" t="n">
-        <v>92020</v>
+        <v>91364</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14736,10 +14736,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>444009</v>
+        <v>443664</v>
       </c>
       <c r="R144" t="n">
-        <v>7010058</v>
+        <v>7009683</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14920,10 +14920,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127302650</v>
+        <v>127302639</v>
       </c>
       <c r="B146" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14931,21 +14931,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14955,10 +14955,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>444093</v>
+        <v>443697</v>
       </c>
       <c r="R146" t="n">
-        <v>7010086</v>
+        <v>7009873</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15017,10 +15017,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127302639</v>
+        <v>127303898</v>
       </c>
       <c r="B147" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15028,34 +15028,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>443697</v>
+        <v>444047</v>
       </c>
       <c r="R147" t="n">
-        <v>7009873</v>
+        <v>7009927</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15085,9 +15085,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15102,57 +15112,57 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127303907</v>
+        <v>127302650</v>
       </c>
       <c r="B148" t="n">
-        <v>98801</v>
+        <v>91646</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219880</v>
+        <v>658</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>444006</v>
+        <v>444093</v>
       </c>
       <c r="R148" t="n">
-        <v>7010126</v>
+        <v>7010086</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15182,19 +15192,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15209,44 +15209,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127303898</v>
+        <v>127303907</v>
       </c>
       <c r="B149" t="n">
-        <v>80132</v>
+        <v>98801</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15256,10 +15256,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>444047</v>
+        <v>444006</v>
       </c>
       <c r="R149" t="n">
-        <v>7009927</v>
+        <v>7010126</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15425,10 +15425,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127302648</v>
+        <v>127302643</v>
       </c>
       <c r="B151" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15436,34 +15436,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>444005</v>
+        <v>443735</v>
       </c>
       <c r="R151" t="n">
-        <v>7009910</v>
+        <v>7009851</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15496,6 +15504,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15522,10 +15535,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127302643</v>
+        <v>127302648</v>
       </c>
       <c r="B152" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15533,42 +15546,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443735</v>
+        <v>444005</v>
       </c>
       <c r="R152" t="n">
-        <v>7009851</v>
+        <v>7009910</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15601,11 +15606,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16046,10 +16046,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127299821</v>
+        <v>127303915</v>
       </c>
       <c r="B157" t="n">
-        <v>91646</v>
+        <v>79110</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16057,34 +16057,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>444255</v>
+        <v>443965</v>
       </c>
       <c r="R157" t="n">
-        <v>7010318</v>
+        <v>7010163</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16114,11 +16114,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -16127,23 +16137,38 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127303932</v>
+        <v>127299814</v>
       </c>
       <c r="B158" t="n">
         <v>91350</v>
@@ -16174,14 +16199,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443689</v>
+        <v>444084</v>
       </c>
       <c r="R158" t="n">
-        <v>7009719</v>
+        <v>7010048</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16211,21 +16236,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16234,76 +16249,61 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127302664</v>
+        <v>127299821</v>
       </c>
       <c r="B159" t="n">
-        <v>79188</v>
+        <v>91646</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1249</v>
+        <v>658</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443777</v>
+        <v>444255</v>
       </c>
       <c r="R159" t="n">
-        <v>7010051</v>
+        <v>7010318</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16350,22 +16350,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127302652</v>
+        <v>127303932</v>
       </c>
       <c r="B160" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16373,34 +16373,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443999</v>
+        <v>443689</v>
       </c>
       <c r="R160" t="n">
-        <v>7010076</v>
+        <v>7009719</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16430,11 +16430,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -16443,61 +16453,76 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127303915</v>
+        <v>127302664</v>
       </c>
       <c r="B161" t="n">
-        <v>79110</v>
+        <v>79188</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443965</v>
+        <v>443777</v>
       </c>
       <c r="R161" t="n">
-        <v>7010163</v>
+        <v>7010051</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16527,21 +16552,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -16550,41 +16565,26 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127299814</v>
+        <v>127302652</v>
       </c>
       <c r="B162" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16592,34 +16592,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>444084</v>
+        <v>443999</v>
       </c>
       <c r="R162" t="n">
-        <v>7010048</v>
+        <v>7010076</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16666,22 +16666,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127299827</v>
+        <v>127302630</v>
       </c>
       <c r="B163" t="n">
-        <v>91368</v>
+        <v>91350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16689,34 +16689,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>444241</v>
+        <v>443979</v>
       </c>
       <c r="R163" t="n">
-        <v>7010317</v>
+        <v>7010134</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16763,44 +16763,44 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127302630</v>
+        <v>127302645</v>
       </c>
       <c r="B164" t="n">
-        <v>91350</v>
+        <v>91804</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16810,10 +16810,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>443979</v>
+        <v>443997</v>
       </c>
       <c r="R164" t="n">
-        <v>7010134</v>
+        <v>7010102</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16854,6 +16854,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -16872,10 +16873,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127303914</v>
+        <v>127299827</v>
       </c>
       <c r="B165" t="n">
-        <v>75075</v>
+        <v>91368</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16883,34 +16884,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1460</v>
+        <v>5432</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>443985</v>
+        <v>444241</v>
       </c>
       <c r="R165" t="n">
-        <v>7010134</v>
+        <v>7010317</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16940,21 +16941,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -16963,76 +16954,61 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127302645</v>
+        <v>127303914</v>
       </c>
       <c r="B166" t="n">
-        <v>91804</v>
+        <v>75075</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1209</v>
+        <v>1460</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>443997</v>
+        <v>443985</v>
       </c>
       <c r="R166" t="n">
-        <v>7010102</v>
+        <v>7010134</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17062,30 +17038,54 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -17189,10 +17189,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127302678</v>
+        <v>127302628</v>
       </c>
       <c r="B168" t="n">
-        <v>91368</v>
+        <v>91350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17200,21 +17200,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17224,10 +17224,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443705</v>
+        <v>443999</v>
       </c>
       <c r="R168" t="n">
-        <v>7009844</v>
+        <v>7010076</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17286,10 +17286,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127302628</v>
+        <v>127302678</v>
       </c>
       <c r="B169" t="n">
-        <v>91350</v>
+        <v>91368</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17297,21 +17297,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17321,10 +17321,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443999</v>
+        <v>443705</v>
       </c>
       <c r="R169" t="n">
-        <v>7010076</v>
+        <v>7009844</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17583,10 +17583,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127302651</v>
+        <v>127299822</v>
       </c>
       <c r="B172" t="n">
-        <v>91646</v>
+        <v>80132</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17594,34 +17594,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>444007</v>
+        <v>444113</v>
       </c>
       <c r="R172" t="n">
-        <v>7010058</v>
+        <v>7010093</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17668,22 +17668,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127302633</v>
+        <v>127302673</v>
       </c>
       <c r="B173" t="n">
-        <v>91350</v>
+        <v>91364</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17691,21 +17691,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17715,10 +17715,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443747</v>
+        <v>443884</v>
       </c>
       <c r="R173" t="n">
-        <v>7010019</v>
+        <v>7010169</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17777,10 +17777,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302673</v>
+        <v>127302633</v>
       </c>
       <c r="B174" t="n">
-        <v>91364</v>
+        <v>91350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443884</v>
+        <v>443747</v>
       </c>
       <c r="R174" t="n">
-        <v>7010169</v>
+        <v>7010019</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17874,10 +17874,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127299822</v>
+        <v>127302651</v>
       </c>
       <c r="B175" t="n">
-        <v>80132</v>
+        <v>91646</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17885,34 +17885,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>444113</v>
+        <v>444007</v>
       </c>
       <c r="R175" t="n">
-        <v>7010093</v>
+        <v>7010058</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17959,22 +17959,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127302659</v>
+        <v>127299815</v>
       </c>
       <c r="B176" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17982,34 +17982,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>443722</v>
+        <v>444084</v>
       </c>
       <c r="R176" t="n">
-        <v>7010007</v>
+        <v>7010049</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18056,19 +18056,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127302653</v>
+        <v>127302659</v>
       </c>
       <c r="B177" t="n">
         <v>91646</v>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443979</v>
+        <v>443722</v>
       </c>
       <c r="R177" t="n">
-        <v>7010133</v>
+        <v>7010007</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127302654</v>
+        <v>127302653</v>
       </c>
       <c r="B178" t="n">
         <v>91646</v>
@@ -18200,10 +18200,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>443964</v>
+        <v>443979</v>
       </c>
       <c r="R178" t="n">
-        <v>7010137</v>
+        <v>7010133</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18262,7 +18262,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127303909</v>
+        <v>127302654</v>
       </c>
       <c r="B179" t="n">
         <v>91646</v>
@@ -18293,14 +18293,14 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443991</v>
+        <v>443964</v>
       </c>
       <c r="R179" t="n">
-        <v>7010145</v>
+        <v>7010137</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18330,21 +18330,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -18353,41 +18343,26 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127299815</v>
+        <v>127303909</v>
       </c>
       <c r="B180" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18395,34 +18370,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>444084</v>
+        <v>443991</v>
       </c>
       <c r="R180" t="n">
-        <v>7010049</v>
+        <v>7010145</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18452,11 +18427,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
@@ -18465,16 +18450,31 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127302655</v>
+        <v>127302640</v>
       </c>
       <c r="B182" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18589,21 +18589,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443907</v>
+        <v>443738</v>
       </c>
       <c r="R182" t="n">
-        <v>7010185</v>
+        <v>7009862</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18869,10 +18869,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127302640</v>
+        <v>127302655</v>
       </c>
       <c r="B185" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18880,21 +18880,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18904,10 +18904,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443738</v>
+        <v>443907</v>
       </c>
       <c r="R185" t="n">
-        <v>7009862</v>
+        <v>7010185</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19419,10 +19419,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127299817</v>
+        <v>127302663</v>
       </c>
       <c r="B190" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19430,34 +19430,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>444242</v>
+        <v>443671</v>
       </c>
       <c r="R190" t="n">
-        <v>7010316</v>
+        <v>7009726</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19504,12 +19504,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -19613,10 +19613,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127303927</v>
+        <v>127302647</v>
       </c>
       <c r="B192" t="n">
-        <v>79029</v>
+        <v>91646</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19624,34 +19624,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443629</v>
+        <v>443989</v>
       </c>
       <c r="R192" t="n">
-        <v>7009887</v>
+        <v>7009901</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19681,21 +19681,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
@@ -19704,41 +19694,26 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127302663</v>
+        <v>127303927</v>
       </c>
       <c r="B193" t="n">
-        <v>91646</v>
+        <v>79029</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19746,34 +19721,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443671</v>
+        <v>443629</v>
       </c>
       <c r="R193" t="n">
-        <v>7009726</v>
+        <v>7009887</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19803,11 +19778,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -19816,26 +19801,41 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127302647</v>
+        <v>127299817</v>
       </c>
       <c r="B194" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19843,34 +19843,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>443989</v>
+        <v>444242</v>
       </c>
       <c r="R194" t="n">
-        <v>7009901</v>
+        <v>7010316</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19917,57 +19917,57 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127311003</v>
+        <v>127311483</v>
       </c>
       <c r="B195" t="n">
-        <v>57514</v>
+        <v>92052</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>102621</v>
+        <v>67</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443820</v>
+        <v>443711</v>
       </c>
       <c r="R195" t="n">
-        <v>7009812</v>
+        <v>7010048</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20026,32 +20026,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127311026</v>
+        <v>127311006</v>
       </c>
       <c r="B196" t="n">
-        <v>91646</v>
+        <v>75151</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20061,10 +20061,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443721</v>
+        <v>444031</v>
       </c>
       <c r="R196" t="n">
-        <v>7009852</v>
+        <v>7010078</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20123,7 +20123,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127311016</v>
+        <v>127311026</v>
       </c>
       <c r="B197" t="n">
         <v>91646</v>
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443914</v>
+        <v>443721</v>
       </c>
       <c r="R197" t="n">
-        <v>7009959</v>
+        <v>7009852</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20220,45 +20220,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127311483</v>
+        <v>127311016</v>
       </c>
       <c r="B198" t="n">
-        <v>92052</v>
+        <v>91646</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>67</v>
+        <v>658</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Haratjärnen, Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>443711</v>
+        <v>443914</v>
       </c>
       <c r="R198" t="n">
-        <v>7010048</v>
+        <v>7009959</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20414,32 +20414,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127311006</v>
+        <v>127311003</v>
       </c>
       <c r="B200" t="n">
-        <v>75151</v>
+        <v>57514</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6486</v>
+        <v>102621</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20449,10 +20449,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>444031</v>
+        <v>443820</v>
       </c>
       <c r="R200" t="n">
-        <v>7010078</v>
+        <v>7009812</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20511,10 +20511,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127311020</v>
+        <v>127310993</v>
       </c>
       <c r="B201" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20522,21 +20522,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>444252</v>
+        <v>443730</v>
       </c>
       <c r="R201" t="n">
-        <v>7010325</v>
+        <v>7009851</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20608,32 +20608,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127310993</v>
+        <v>127311011</v>
       </c>
       <c r="B202" t="n">
-        <v>91350</v>
+        <v>91804</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>443730</v>
+        <v>444037</v>
       </c>
       <c r="R202" t="n">
-        <v>7009851</v>
+        <v>7010055</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20705,10 +20705,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127311031</v>
+        <v>127311020</v>
       </c>
       <c r="B203" t="n">
-        <v>75075</v>
+        <v>91646</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20716,21 +20716,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>444124</v>
+        <v>444252</v>
       </c>
       <c r="R203" t="n">
-        <v>7010021</v>
+        <v>7010325</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20802,32 +20802,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127311011</v>
+        <v>127311031</v>
       </c>
       <c r="B204" t="n">
-        <v>91804</v>
+        <v>75075</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1209</v>
+        <v>1460</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20837,10 +20837,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>444037</v>
+        <v>444124</v>
       </c>
       <c r="R204" t="n">
-        <v>7010055</v>
+        <v>7010021</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20996,10 +20996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127310997</v>
+        <v>127311018</v>
       </c>
       <c r="B206" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21007,42 +21007,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>443735</v>
+        <v>444250</v>
       </c>
       <c r="R206" t="n">
-        <v>7009858</v>
+        <v>7010307</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21075,11 +21067,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21106,10 +21093,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127311018</v>
+        <v>127310997</v>
       </c>
       <c r="B207" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21117,34 +21104,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>444250</v>
+        <v>443735</v>
       </c>
       <c r="R207" t="n">
-        <v>7010307</v>
+        <v>7009858</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21177,6 +21172,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21397,10 +21397,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127311042</v>
+        <v>127311052</v>
       </c>
       <c r="B210" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21408,21 +21408,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21432,10 +21432,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443919</v>
+        <v>443874</v>
       </c>
       <c r="R210" t="n">
-        <v>7010183</v>
+        <v>7009953</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21494,32 +21494,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127311039</v>
+        <v>127311042</v>
       </c>
       <c r="B211" t="n">
-        <v>79188</v>
+        <v>80132</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21529,10 +21529,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>443626</v>
+        <v>443919</v>
       </c>
       <c r="R211" t="n">
-        <v>7009924</v>
+        <v>7010183</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21591,32 +21591,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127311052</v>
+        <v>127311039</v>
       </c>
       <c r="B212" t="n">
-        <v>79029</v>
+        <v>79188</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21626,10 +21626,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>443874</v>
+        <v>443626</v>
       </c>
       <c r="R212" t="n">
-        <v>7009953</v>
+        <v>7009924</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21688,32 +21688,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127310996</v>
+        <v>127310989</v>
       </c>
       <c r="B213" t="n">
-        <v>92047</v>
+        <v>91350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21723,10 +21723,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>444091</v>
+        <v>443910</v>
       </c>
       <c r="R213" t="n">
-        <v>7010088</v>
+        <v>7010191</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22076,32 +22076,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127310989</v>
+        <v>127310996</v>
       </c>
       <c r="B217" t="n">
-        <v>91350</v>
+        <v>92047</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22111,10 +22111,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>443910</v>
+        <v>444091</v>
       </c>
       <c r="R217" t="n">
-        <v>7010191</v>
+        <v>7010088</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22270,32 +22270,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127311054</v>
+        <v>127311012</v>
       </c>
       <c r="B219" t="n">
-        <v>79029</v>
+        <v>91804</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22305,10 +22305,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>443698</v>
+        <v>443967</v>
       </c>
       <c r="R219" t="n">
-        <v>7010030</v>
+        <v>7010143</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22367,32 +22367,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127311012</v>
+        <v>127311054</v>
       </c>
       <c r="B220" t="n">
-        <v>91804</v>
+        <v>79029</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22402,10 +22402,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>443967</v>
+        <v>443698</v>
       </c>
       <c r="R220" t="n">
-        <v>7010143</v>
+        <v>7010030</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22464,32 +22464,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127311047</v>
+        <v>127310998</v>
       </c>
       <c r="B221" t="n">
-        <v>91364</v>
+        <v>100557</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1204</v>
+        <v>222771</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22499,10 +22499,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>444088</v>
+        <v>443946</v>
       </c>
       <c r="R221" t="n">
-        <v>7010038</v>
+        <v>7010139</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22561,32 +22561,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127310999</v>
+        <v>127311047</v>
       </c>
       <c r="B222" t="n">
-        <v>80161</v>
+        <v>91364</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22596,10 +22596,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>444089</v>
+        <v>444088</v>
       </c>
       <c r="R222" t="n">
-        <v>7010006</v>
+        <v>7010038</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22658,10 +22658,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127310998</v>
+        <v>127310999</v>
       </c>
       <c r="B223" t="n">
-        <v>100557</v>
+        <v>80161</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22669,21 +22669,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>222771</v>
+        <v>6462</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22693,10 +22693,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>443946</v>
+        <v>444089</v>
       </c>
       <c r="R223" t="n">
-        <v>7010139</v>
+        <v>7010006</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22852,10 +22852,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127311022</v>
+        <v>127310995</v>
       </c>
       <c r="B225" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22863,21 +22863,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>444108</v>
+        <v>443689</v>
       </c>
       <c r="R225" t="n">
-        <v>7010040</v>
+        <v>7009728</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22949,7 +22949,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127310995</v>
+        <v>127310990</v>
       </c>
       <c r="B226" t="n">
         <v>91350</v>
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443689</v>
+        <v>443745</v>
       </c>
       <c r="R226" t="n">
-        <v>7009728</v>
+        <v>7010081</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23046,7 +23046,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127310990</v>
+        <v>127310986</v>
       </c>
       <c r="B227" t="n">
         <v>91350</v>
@@ -23081,10 +23081,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>443745</v>
+        <v>444046</v>
       </c>
       <c r="R227" t="n">
-        <v>7010081</v>
+        <v>7010063</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127310986</v>
+        <v>127311041</v>
       </c>
       <c r="B230" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23348,21 +23348,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23372,10 +23372,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>444046</v>
+        <v>444094</v>
       </c>
       <c r="R230" t="n">
-        <v>7010063</v>
+        <v>7010004</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23434,10 +23434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127311041</v>
+        <v>127311022</v>
       </c>
       <c r="B231" t="n">
-        <v>80132</v>
+        <v>91646</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23445,21 +23445,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444094</v>
+        <v>444108</v>
       </c>
       <c r="R231" t="n">
-        <v>7010004</v>
+        <v>7010040</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23531,10 +23531,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127311024</v>
+        <v>127310988</v>
       </c>
       <c r="B232" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23542,21 +23542,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23566,10 +23566,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>443987</v>
+        <v>443937</v>
       </c>
       <c r="R232" t="n">
-        <v>7010155</v>
+        <v>7010167</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23628,7 +23628,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127311025</v>
+        <v>127311024</v>
       </c>
       <c r="B233" t="n">
         <v>91646</v>
@@ -23663,10 +23663,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>443634</v>
+        <v>443987</v>
       </c>
       <c r="R233" t="n">
-        <v>7009878</v>
+        <v>7010155</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23725,10 +23725,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127311051</v>
+        <v>127311025</v>
       </c>
       <c r="B234" t="n">
-        <v>91368</v>
+        <v>91646</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23736,21 +23736,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23760,10 +23760,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443729</v>
+        <v>443634</v>
       </c>
       <c r="R234" t="n">
-        <v>7009862</v>
+        <v>7009878</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23822,10 +23822,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127311050</v>
+        <v>127311027</v>
       </c>
       <c r="B235" t="n">
-        <v>91368</v>
+        <v>75075</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23833,21 +23833,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5432</v>
+        <v>1460</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23857,10 +23857,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>443756</v>
+        <v>444316</v>
       </c>
       <c r="R235" t="n">
-        <v>7010085</v>
+        <v>7010269</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23919,10 +23919,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127311027</v>
+        <v>127311050</v>
       </c>
       <c r="B236" t="n">
-        <v>75075</v>
+        <v>91368</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23930,21 +23930,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1460</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23954,10 +23954,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>444316</v>
+        <v>443756</v>
       </c>
       <c r="R236" t="n">
-        <v>7010269</v>
+        <v>7010085</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24016,10 +24016,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127310988</v>
+        <v>127311051</v>
       </c>
       <c r="B237" t="n">
-        <v>91350</v>
+        <v>91368</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24027,21 +24027,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24051,10 +24051,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>443937</v>
+        <v>443729</v>
       </c>
       <c r="R237" t="n">
-        <v>7010167</v>
+        <v>7009862</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24404,10 +24404,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127311048</v>
+        <v>127310991</v>
       </c>
       <c r="B241" t="n">
-        <v>91368</v>
+        <v>91350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24415,21 +24415,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24439,10 +24439,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>444000</v>
+        <v>443609</v>
       </c>
       <c r="R241" t="n">
-        <v>7009885</v>
+        <v>7009974</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24501,10 +24501,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127310991</v>
+        <v>127311023</v>
       </c>
       <c r="B242" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24512,21 +24512,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24536,10 +24536,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>443609</v>
+        <v>444039</v>
       </c>
       <c r="R242" t="n">
-        <v>7009974</v>
+        <v>7010073</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24598,10 +24598,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127311053</v>
+        <v>127311048</v>
       </c>
       <c r="B243" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24609,21 +24609,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24633,10 +24633,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>443960</v>
+        <v>444000</v>
       </c>
       <c r="R243" t="n">
-        <v>7010126</v>
+        <v>7009885</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24695,32 +24695,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127311007</v>
+        <v>127311053</v>
       </c>
       <c r="B244" t="n">
-        <v>75151</v>
+        <v>79029</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -24730,10 +24730,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>443893</v>
+        <v>443960</v>
       </c>
       <c r="R244" t="n">
-        <v>7010175</v>
+        <v>7010126</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24792,32 +24792,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127311023</v>
+        <v>127311007</v>
       </c>
       <c r="B245" t="n">
-        <v>91646</v>
+        <v>75151</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -24827,10 +24827,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>444039</v>
+        <v>443893</v>
       </c>
       <c r="R245" t="n">
-        <v>7010073</v>
+        <v>7010175</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25665,10 +25665,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127311035</v>
+        <v>127311009</v>
       </c>
       <c r="B254" t="n">
-        <v>75075</v>
+        <v>80133</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -25676,21 +25676,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1460</v>
+        <v>2081</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -25700,10 +25700,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>444012</v>
+        <v>444133</v>
       </c>
       <c r="R254" t="n">
-        <v>7010079</v>
+        <v>7010104</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25762,7 +25762,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127311009</v>
+        <v>127311010</v>
       </c>
       <c r="B255" t="n">
         <v>80133</v>
@@ -25797,10 +25797,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>444133</v>
+        <v>443921</v>
       </c>
       <c r="R255" t="n">
-        <v>7010104</v>
+        <v>7010190</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -25859,10 +25859,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127311010</v>
+        <v>127311035</v>
       </c>
       <c r="B256" t="n">
-        <v>80133</v>
+        <v>75075</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -25870,21 +25870,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>2081</v>
+        <v>1460</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -25894,10 +25894,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>443921</v>
+        <v>444012</v>
       </c>
       <c r="R256" t="n">
-        <v>7010190</v>
+        <v>7010079</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26053,32 +26053,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127311043</v>
+        <v>127311001</v>
       </c>
       <c r="B258" t="n">
-        <v>80132</v>
+        <v>92052</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>443639</v>
+        <v>443716</v>
       </c>
       <c r="R258" t="n">
-        <v>7010011</v>
+        <v>7010053</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26150,32 +26150,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127311001</v>
+        <v>127310985</v>
       </c>
       <c r="B259" t="n">
-        <v>92052</v>
+        <v>91350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26185,10 +26185,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>443716</v>
+        <v>444090</v>
       </c>
       <c r="R259" t="n">
-        <v>7010053</v>
+        <v>7009966</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26247,7 +26247,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127310985</v>
+        <v>127310984</v>
       </c>
       <c r="B260" t="n">
         <v>91350</v>
@@ -26282,10 +26282,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>444090</v>
+        <v>444048</v>
       </c>
       <c r="R260" t="n">
-        <v>7009966</v>
+        <v>7009932</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26344,10 +26344,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127310984</v>
+        <v>127311043</v>
       </c>
       <c r="B261" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26355,21 +26355,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26379,10 +26379,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>444048</v>
+        <v>443639</v>
       </c>
       <c r="R261" t="n">
-        <v>7009932</v>
+        <v>7010011</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -11001,45 +11001,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127303918</v>
+        <v>127302675</v>
       </c>
       <c r="B108" t="n">
-        <v>97494</v>
+        <v>91369</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222741</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443944</v>
+        <v>443823</v>
       </c>
       <c r="R108" t="n">
-        <v>7010169</v>
+        <v>7010119</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11069,19 +11069,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>18:28</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11096,12 +11086,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11221,7 +11211,7 @@
         <v>127302632</v>
       </c>
       <c r="B110" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11318,7 +11308,7 @@
         <v>127302649</v>
       </c>
       <c r="B111" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11412,45 +11402,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127302675</v>
+        <v>127303918</v>
       </c>
       <c r="B112" t="n">
-        <v>91368</v>
+        <v>97495</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>222741</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443823</v>
+        <v>443944</v>
       </c>
       <c r="R112" t="n">
-        <v>7010119</v>
+        <v>7010169</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11480,9 +11470,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11497,12 +11497,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -11512,7 +11512,7 @@
         <v>127302635</v>
       </c>
       <c r="B113" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>127303919</v>
       </c>
       <c r="B114" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>127299825</v>
       </c>
       <c r="B115" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127299820</v>
+        <v>127302625</v>
       </c>
       <c r="B116" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,34 +11836,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444007</v>
+        <v>444262</v>
       </c>
       <c r="R116" t="n">
-        <v>7010102</v>
+        <v>7010300</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11898,11 +11898,6 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>14 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11915,12 +11910,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -11930,7 +11925,7 @@
         <v>127303924</v>
       </c>
       <c r="B117" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12151,10 +12146,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127302625</v>
+        <v>127299820</v>
       </c>
       <c r="B119" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12162,34 +12157,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444262</v>
+        <v>444007</v>
       </c>
       <c r="R119" t="n">
-        <v>7010300</v>
+        <v>7010102</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12224,6 +12219,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>14 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12236,22 +12236,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127302637</v>
+        <v>127302657</v>
       </c>
       <c r="B120" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12259,21 +12259,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443618</v>
+        <v>443766</v>
       </c>
       <c r="R120" t="n">
-        <v>7009972</v>
+        <v>7010076</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12345,10 +12345,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127302657</v>
+        <v>127302637</v>
       </c>
       <c r="B121" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12356,21 +12356,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443766</v>
+        <v>443618</v>
       </c>
       <c r="R121" t="n">
-        <v>7010076</v>
+        <v>7009972</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12445,7 +12445,7 @@
         <v>127302661</v>
       </c>
       <c r="B122" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>127302676</v>
       </c>
       <c r="B123" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>127299830</v>
       </c>
       <c r="B124" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>127299819</v>
       </c>
       <c r="B125" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>127302629</v>
       </c>
       <c r="B127" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13253,10 +13253,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127302634</v>
+        <v>127303913</v>
       </c>
       <c r="B130" t="n">
-        <v>91350</v>
+        <v>75075</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13264,34 +13264,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443749</v>
+        <v>443984</v>
       </c>
       <c r="R130" t="n">
-        <v>7010018</v>
+        <v>7010138</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13321,11 +13321,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -13334,26 +13344,41 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127303913</v>
+        <v>127302634</v>
       </c>
       <c r="B131" t="n">
-        <v>75075</v>
+        <v>91351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13361,34 +13386,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443984</v>
+        <v>443749</v>
       </c>
       <c r="R131" t="n">
-        <v>7010138</v>
+        <v>7010018</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13418,21 +13443,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -13441,31 +13456,16 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13475,7 +13475,7 @@
         <v>127302669</v>
       </c>
       <c r="B132" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>127302660</v>
       </c>
       <c r="B133" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13666,32 +13666,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127303916</v>
+        <v>127303906</v>
       </c>
       <c r="B134" t="n">
-        <v>75151</v>
+        <v>79115</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6486</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13701,10 +13701,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443956</v>
+        <v>444000</v>
       </c>
       <c r="R134" t="n">
-        <v>7010157</v>
+        <v>7010124</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13788,32 +13788,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127303906</v>
+        <v>127303916</v>
       </c>
       <c r="B135" t="n">
-        <v>79115</v>
+        <v>75151</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6450</v>
+        <v>6486</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13823,10 +13823,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444000</v>
+        <v>443956</v>
       </c>
       <c r="R135" t="n">
-        <v>7010124</v>
+        <v>7010157</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -13913,7 +13913,7 @@
         <v>127303920</v>
       </c>
       <c r="B136" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14022,10 +14022,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127299816</v>
+        <v>127302666</v>
       </c>
       <c r="B137" t="n">
-        <v>91350</v>
+        <v>91347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14033,34 +14033,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444022</v>
+        <v>443769</v>
       </c>
       <c r="R137" t="n">
-        <v>7010055</v>
+        <v>7010089</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14107,22 +14107,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127302666</v>
+        <v>127302668</v>
       </c>
       <c r="B138" t="n">
-        <v>91346</v>
+        <v>91365</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14130,21 +14130,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443769</v>
+        <v>443816</v>
       </c>
       <c r="R138" t="n">
-        <v>7010089</v>
+        <v>7009788</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14216,10 +14216,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127302668</v>
+        <v>127302670</v>
       </c>
       <c r="B139" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443816</v>
+        <v>444114</v>
       </c>
       <c r="R139" t="n">
-        <v>7009788</v>
+        <v>7010064</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127302670</v>
+        <v>127302658</v>
       </c>
       <c r="B140" t="n">
-        <v>91364</v>
+        <v>91647</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14324,21 +14324,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444114</v>
+        <v>443777</v>
       </c>
       <c r="R140" t="n">
-        <v>7010064</v>
+        <v>7010050</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14410,10 +14410,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127302658</v>
+        <v>127299816</v>
       </c>
       <c r="B141" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14421,34 +14421,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443777</v>
+        <v>444022</v>
       </c>
       <c r="R141" t="n">
-        <v>7010050</v>
+        <v>7010055</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14495,57 +14495,57 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127302646</v>
+        <v>127303910</v>
       </c>
       <c r="B142" t="n">
-        <v>91646</v>
+        <v>79285</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>658</v>
+        <v>6459</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443843</v>
+        <v>443992</v>
       </c>
       <c r="R142" t="n">
-        <v>7009837</v>
+        <v>7010143</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14575,11 +14575,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -14588,48 +14598,63 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127302679</v>
+        <v>127302646</v>
       </c>
       <c r="B143" t="n">
-        <v>92020</v>
+        <v>91647</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14639,10 +14664,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444009</v>
+        <v>443843</v>
       </c>
       <c r="R143" t="n">
-        <v>7010058</v>
+        <v>7009837</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14704,7 +14729,7 @@
         <v>127302671</v>
       </c>
       <c r="B144" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14798,45 +14823,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127303910</v>
+        <v>127302679</v>
       </c>
       <c r="B145" t="n">
-        <v>79285</v>
+        <v>92021</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6459</v>
+        <v>898</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443992</v>
+        <v>444009</v>
       </c>
       <c r="R145" t="n">
-        <v>7010143</v>
+        <v>7010058</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14866,21 +14891,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -14889,31 +14904,16 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
         <v>127302639</v>
       </c>
       <c r="B146" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15017,10 +15017,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127303898</v>
+        <v>127302650</v>
       </c>
       <c r="B147" t="n">
-        <v>80132</v>
+        <v>91647</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15028,34 +15028,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>444047</v>
+        <v>444093</v>
       </c>
       <c r="R147" t="n">
-        <v>7009927</v>
+        <v>7010086</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15085,19 +15085,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>21:26</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>21:26</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15112,22 +15102,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127302650</v>
+        <v>127303898</v>
       </c>
       <c r="B148" t="n">
-        <v>91646</v>
+        <v>80132</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15135,34 +15125,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>444093</v>
+        <v>444047</v>
       </c>
       <c r="R148" t="n">
-        <v>7010086</v>
+        <v>7009927</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15192,9 +15182,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15209,12 +15209,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -15224,7 +15224,7 @@
         <v>127303907</v>
       </c>
       <c r="B149" t="n">
-        <v>98801</v>
+        <v>98802</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>127299824</v>
       </c>
       <c r="B150" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15425,10 +15425,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127302643</v>
+        <v>127302648</v>
       </c>
       <c r="B151" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15436,42 +15436,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443735</v>
+        <v>444005</v>
       </c>
       <c r="R151" t="n">
-        <v>7009851</v>
+        <v>7009910</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15504,11 +15496,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15535,10 +15522,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127302648</v>
+        <v>127302643</v>
       </c>
       <c r="B152" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15546,34 +15533,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>444005</v>
+        <v>443735</v>
       </c>
       <c r="R152" t="n">
-        <v>7009910</v>
+        <v>7009851</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15606,6 +15601,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15632,10 +15632,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127302638</v>
+        <v>127299813</v>
       </c>
       <c r="B153" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15663,14 +15663,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443679</v>
+        <v>444303</v>
       </c>
       <c r="R153" t="n">
-        <v>7009870</v>
+        <v>7010251</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15717,44 +15717,44 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127302644</v>
+        <v>127302638</v>
       </c>
       <c r="B154" t="n">
-        <v>91804</v>
+        <v>91351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15764,10 +15764,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443970</v>
+        <v>443679</v>
       </c>
       <c r="R154" t="n">
-        <v>7009897</v>
+        <v>7009870</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15808,7 +15808,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -15830,7 +15829,7 @@
         <v>127303930</v>
       </c>
       <c r="B155" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15949,45 +15948,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127299813</v>
+        <v>127302644</v>
       </c>
       <c r="B156" t="n">
-        <v>91350</v>
+        <v>91805</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>444303</v>
+        <v>443970</v>
       </c>
       <c r="R156" t="n">
-        <v>7010251</v>
+        <v>7009897</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16028,28 +16027,29 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127303915</v>
+        <v>127299814</v>
       </c>
       <c r="B157" t="n">
-        <v>79110</v>
+        <v>91351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16057,34 +16057,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443965</v>
+        <v>444084</v>
       </c>
       <c r="R157" t="n">
-        <v>7010163</v>
+        <v>7010048</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16114,21 +16114,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -16137,41 +16127,26 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127299814</v>
+        <v>127299821</v>
       </c>
       <c r="B158" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16179,21 +16154,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16203,10 +16178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>444084</v>
+        <v>444255</v>
       </c>
       <c r="R158" t="n">
-        <v>7010048</v>
+        <v>7010318</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16265,10 +16240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127299821</v>
+        <v>127302652</v>
       </c>
       <c r="B159" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16296,14 +16271,14 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>444255</v>
+        <v>443999</v>
       </c>
       <c r="R159" t="n">
-        <v>7010318</v>
+        <v>7010076</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16350,12 +16325,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16365,7 +16340,7 @@
         <v>127303932</v>
       </c>
       <c r="B160" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16581,10 +16556,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127302652</v>
+        <v>127303915</v>
       </c>
       <c r="B162" t="n">
-        <v>91646</v>
+        <v>79110</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16592,34 +16567,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>658</v>
+        <v>283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443999</v>
+        <v>443965</v>
       </c>
       <c r="R162" t="n">
-        <v>7010076</v>
+        <v>7010163</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16649,11 +16624,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
@@ -16662,16 +16647,31 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -16681,7 +16681,7 @@
         <v>127302630</v>
       </c>
       <c r="B163" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16775,45 +16775,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127302645</v>
+        <v>127303914</v>
       </c>
       <c r="B164" t="n">
-        <v>91804</v>
+        <v>75075</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1209</v>
+        <v>1460</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>443997</v>
+        <v>443985</v>
       </c>
       <c r="R164" t="n">
-        <v>7010102</v>
+        <v>7010134</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16843,75 +16843,99 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127299827</v>
+        <v>127302645</v>
       </c>
       <c r="B165" t="n">
-        <v>91368</v>
+        <v>91805</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>444241</v>
+        <v>443997</v>
       </c>
       <c r="R165" t="n">
-        <v>7010317</v>
+        <v>7010102</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16952,28 +16976,29 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127303914</v>
+        <v>127299827</v>
       </c>
       <c r="B166" t="n">
-        <v>75075</v>
+        <v>91369</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16981,34 +17006,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1460</v>
+        <v>5432</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>443985</v>
+        <v>444241</v>
       </c>
       <c r="R166" t="n">
-        <v>7010134</v>
+        <v>7010317</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17038,21 +17063,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
@@ -17061,41 +17076,26 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127299823</v>
+        <v>127302628</v>
       </c>
       <c r="B167" t="n">
-        <v>80132</v>
+        <v>91351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17103,34 +17103,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>444412</v>
+        <v>443999</v>
       </c>
       <c r="R167" t="n">
-        <v>7010433</v>
+        <v>7010076</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17177,22 +17177,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127302628</v>
+        <v>127302665</v>
       </c>
       <c r="B168" t="n">
-        <v>91350</v>
+        <v>91758</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17200,21 +17200,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17224,10 +17219,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443999</v>
+        <v>444252</v>
       </c>
       <c r="R168" t="n">
-        <v>7010076</v>
+        <v>7010193</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17268,6 +17263,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17286,10 +17282,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127302678</v>
+        <v>127299823</v>
       </c>
       <c r="B169" t="n">
-        <v>91368</v>
+        <v>80132</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17297,34 +17293,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443705</v>
+        <v>444412</v>
       </c>
       <c r="R169" t="n">
-        <v>7009844</v>
+        <v>7010433</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17371,57 +17367,57 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127303912</v>
+        <v>127302678</v>
       </c>
       <c r="B170" t="n">
-        <v>75151</v>
+        <v>91369</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>443984</v>
+        <v>443705</v>
       </c>
       <c r="R170" t="n">
-        <v>7010138</v>
+        <v>7009844</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17451,19 +17447,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>19:01</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>19:01</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17478,52 +17464,57 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127302665</v>
+        <v>127303912</v>
       </c>
       <c r="B171" t="n">
-        <v>91757</v>
+        <v>75151</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6040186</v>
+        <v>6486</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>444252</v>
+        <v>443984</v>
       </c>
       <c r="R171" t="n">
-        <v>7010193</v>
+        <v>7010138</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17553,40 +17544,49 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127299822</v>
+        <v>127302673</v>
       </c>
       <c r="B172" t="n">
-        <v>80132</v>
+        <v>91365</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17594,34 +17594,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>444113</v>
+        <v>443884</v>
       </c>
       <c r="R172" t="n">
-        <v>7010093</v>
+        <v>7010169</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17668,22 +17668,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127302673</v>
+        <v>127302633</v>
       </c>
       <c r="B173" t="n">
-        <v>91364</v>
+        <v>91351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17691,21 +17691,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17715,10 +17715,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443884</v>
+        <v>443747</v>
       </c>
       <c r="R173" t="n">
-        <v>7010169</v>
+        <v>7010019</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17777,10 +17777,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127302633</v>
+        <v>127302651</v>
       </c>
       <c r="B174" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17788,21 +17788,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443747</v>
+        <v>444007</v>
       </c>
       <c r="R174" t="n">
-        <v>7010019</v>
+        <v>7010058</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17874,10 +17874,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127302651</v>
+        <v>127299822</v>
       </c>
       <c r="B175" t="n">
-        <v>91646</v>
+        <v>80132</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17885,34 +17885,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>444007</v>
+        <v>444113</v>
       </c>
       <c r="R175" t="n">
-        <v>7010058</v>
+        <v>7010093</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17959,12 +17959,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -17974,7 +17974,7 @@
         <v>127299815</v>
       </c>
       <c r="B176" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>127302659</v>
       </c>
       <c r="B177" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>127302653</v>
       </c>
       <c r="B178" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>127302654</v>
       </c>
       <c r="B179" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>127303909</v>
       </c>
       <c r="B180" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127302640</v>
+        <v>127302636</v>
       </c>
       <c r="B182" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443738</v>
+        <v>443640</v>
       </c>
       <c r="R182" t="n">
-        <v>7009862</v>
+        <v>7010000</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18675,10 +18675,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127302636</v>
+        <v>127302627</v>
       </c>
       <c r="B183" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18710,10 +18710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443640</v>
+        <v>444031</v>
       </c>
       <c r="R183" t="n">
-        <v>7010000</v>
+        <v>7010049</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18772,10 +18772,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127302627</v>
+        <v>127302640</v>
       </c>
       <c r="B184" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18807,10 +18807,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>444031</v>
+        <v>443738</v>
       </c>
       <c r="R184" t="n">
-        <v>7010049</v>
+        <v>7009862</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18872,7 +18872,7 @@
         <v>127302655</v>
       </c>
       <c r="B185" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18966,10 +18966,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127303925</v>
+        <v>127303922</v>
       </c>
       <c r="B186" t="n">
-        <v>79188</v>
+        <v>91711</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18977,21 +18977,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1249</v>
+        <v>2063</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19001,10 +19001,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443627</v>
+        <v>443745</v>
       </c>
       <c r="R186" t="n">
-        <v>7009957</v>
+        <v>7010077</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19058,19 +19058,9 @@
       <c r="AG186" t="b">
         <v>0</v>
       </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>På/intill död granticka på grov granlåga.</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -19088,45 +19078,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127302624</v>
+        <v>127303925</v>
       </c>
       <c r="B187" t="n">
-        <v>91350</v>
+        <v>79188</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Ågårdarna, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>444005</v>
+        <v>443627</v>
       </c>
       <c r="R187" t="n">
-        <v>7009910</v>
+        <v>7009957</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19156,11 +19146,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -19169,26 +19169,41 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127303928</v>
+        <v>127302624</v>
       </c>
       <c r="B188" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19216,14 +19231,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>443698</v>
+        <v>444005</v>
       </c>
       <c r="R188" t="n">
-        <v>7009874</v>
+        <v>7009910</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19253,21 +19268,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
@@ -19276,63 +19281,48 @@
       </c>
       <c r="AG188" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127303922</v>
+        <v>127303928</v>
       </c>
       <c r="B189" t="n">
-        <v>91710</v>
+        <v>91351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19342,10 +19332,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>443745</v>
+        <v>443698</v>
       </c>
       <c r="R189" t="n">
-        <v>7010077</v>
+        <v>7009874</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19377,7 +19367,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -19387,7 +19377,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19399,9 +19389,19 @@
       <c r="AG189" t="b">
         <v>0</v>
       </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>På/intill död granticka på grov granlåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>
@@ -19422,7 +19422,7 @@
         <v>127302663</v>
       </c>
       <c r="B190" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>127302672</v>
       </c>
       <c r="B191" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>127302647</v>
       </c>
       <c r="B192" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19710,10 +19710,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127303927</v>
+        <v>127299817</v>
       </c>
       <c r="B193" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19721,34 +19721,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Haratjärnen NÖ, Jmt</t>
+          <t>Haratjärnsskogen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443629</v>
+        <v>444242</v>
       </c>
       <c r="R193" t="n">
-        <v>7009887</v>
+        <v>7010316</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19778,21 +19778,11 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -19801,41 +19791,26 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127299817</v>
+        <v>127303927</v>
       </c>
       <c r="B194" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19843,34 +19818,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Haratjärnsskogen, Jmt</t>
+          <t>Haratjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>444242</v>
+        <v>443629</v>
       </c>
       <c r="R194" t="n">
-        <v>7010316</v>
+        <v>7009887</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19900,11 +19875,21 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -19913,61 +19898,76 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127311483</v>
+        <v>127311003</v>
       </c>
       <c r="B195" t="n">
-        <v>92052</v>
+        <v>57514</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>67</v>
+        <v>102621</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Haratjärnen, Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443711</v>
+        <v>443820</v>
       </c>
       <c r="R195" t="n">
-        <v>7010048</v>
+        <v>7009812</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20026,32 +20026,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127311006</v>
+        <v>127311026</v>
       </c>
       <c r="B196" t="n">
-        <v>75151</v>
+        <v>91647</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20061,10 +20061,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>444031</v>
+        <v>443721</v>
       </c>
       <c r="R196" t="n">
-        <v>7010078</v>
+        <v>7009852</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20123,10 +20123,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127311026</v>
+        <v>127311016</v>
       </c>
       <c r="B197" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443721</v>
+        <v>443914</v>
       </c>
       <c r="R197" t="n">
-        <v>7009852</v>
+        <v>7009959</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20220,10 +20220,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127311016</v>
+        <v>127311021</v>
       </c>
       <c r="B198" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20255,10 +20255,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>443914</v>
+        <v>444283</v>
       </c>
       <c r="R198" t="n">
-        <v>7009959</v>
+        <v>7010242</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20317,45 +20317,45 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127311021</v>
+        <v>127311483</v>
       </c>
       <c r="B199" t="n">
-        <v>91646</v>
+        <v>92053</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Haratjärnen, Jmt</t>
+          <t>Haratjärnen, Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>444283</v>
+        <v>443711</v>
       </c>
       <c r="R199" t="n">
-        <v>7010242</v>
+        <v>7010048</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20414,32 +20414,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127311003</v>
+        <v>127311006</v>
       </c>
       <c r="B200" t="n">
-        <v>57514</v>
+        <v>75151</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>102621</v>
+        <v>6486</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20449,10 +20449,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>443820</v>
+        <v>444031</v>
       </c>
       <c r="R200" t="n">
-        <v>7009812</v>
+        <v>7010078</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20514,7 +20514,7 @@
         <v>127310993</v>
       </c>
       <c r="B201" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20608,32 +20608,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127311011</v>
+        <v>127311031</v>
       </c>
       <c r="B202" t="n">
-        <v>91804</v>
+        <v>75075</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1209</v>
+        <v>1460</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>444037</v>
+        <v>444124</v>
       </c>
       <c r="R202" t="n">
-        <v>7010055</v>
+        <v>7010021</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20708,7 +20708,7 @@
         <v>127311020</v>
       </c>
       <c r="B203" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20802,32 +20802,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127311031</v>
+        <v>127311011</v>
       </c>
       <c r="B204" t="n">
-        <v>75075</v>
+        <v>91805</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1460</v>
+        <v>1209</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20837,10 +20837,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>444124</v>
+        <v>444037</v>
       </c>
       <c r="R204" t="n">
-        <v>7010021</v>
+        <v>7010055</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20996,10 +20996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127311018</v>
+        <v>127310997</v>
       </c>
       <c r="B206" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21007,34 +21007,42 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>444250</v>
+        <v>443735</v>
       </c>
       <c r="R206" t="n">
-        <v>7010307</v>
+        <v>7009858</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21067,6 +21075,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21093,10 +21106,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127310997</v>
+        <v>127311018</v>
       </c>
       <c r="B207" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21104,42 +21117,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Haratjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443735</v>
+        <v>444250</v>
       </c>
       <c r="R207" t="n">
-        <v>7009858</v>
+        <v>7010307</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21172,11 +21177,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21206,7 +21206,7 @@
         <v>127310987</v>
       </c>
       <c r="B208" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>127311017</v>
       </c>
       <c r="B209" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21397,32 +21397,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127311052</v>
+        <v>127311039</v>
       </c>
       <c r="B210" t="n">
-        <v>79029</v>
+        <v>79188</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21432,10 +21432,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443874</v>
+        <v>443626</v>
       </c>
       <c r="R210" t="n">
-        <v>7009953</v>
+        <v>7009924</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21591,32 +21591,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127311039</v>
+        <v>127311052</v>
       </c>
       <c r="B212" t="n">
-        <v>79188</v>
+        <v>79029</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21626,10 +21626,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>443626</v>
+        <v>443874</v>
       </c>
       <c r="R212" t="n">
-        <v>7009924</v>
+        <v>7009953</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21691,7 +21691,7 @@
         <v>127310989</v>
       </c>
       <c r="B213" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>127311036</v>
       </c>
       <c r="B215" t="n">
-        <v>91719</v>
+        <v>91720</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>127310996</v>
       </c>
       <c r="B217" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>127311060</v>
       </c>
       <c r="B218" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>127311012</v>
       </c>
       <c r="B219" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22464,32 +22464,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127310998</v>
+        <v>127311047</v>
       </c>
       <c r="B221" t="n">
-        <v>100557</v>
+        <v>91365</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>222771</v>
+        <v>1204</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22499,10 +22499,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443946</v>
+        <v>444088</v>
       </c>
       <c r="R221" t="n">
-        <v>7010139</v>
+        <v>7010038</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22561,32 +22561,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127311047</v>
+        <v>127310999</v>
       </c>
       <c r="B222" t="n">
-        <v>91364</v>
+        <v>80161</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22596,10 +22596,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>444088</v>
+        <v>444089</v>
       </c>
       <c r="R222" t="n">
-        <v>7010038</v>
+        <v>7010006</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22658,10 +22658,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127310999</v>
+        <v>127310998</v>
       </c>
       <c r="B223" t="n">
-        <v>80161</v>
+        <v>100558</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22669,21 +22669,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6462</v>
+        <v>222771</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22693,10 +22693,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>444089</v>
+        <v>443946</v>
       </c>
       <c r="R223" t="n">
-        <v>7010006</v>
+        <v>7010139</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22755,10 +22755,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127311059</v>
+        <v>127310995</v>
       </c>
       <c r="B224" t="n">
-        <v>88753</v>
+        <v>91351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22766,21 +22766,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22790,10 +22790,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>444272</v>
+        <v>443689</v>
       </c>
       <c r="R224" t="n">
-        <v>7010237</v>
+        <v>7009728</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22852,10 +22852,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127310995</v>
+        <v>127310990</v>
       </c>
       <c r="B225" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>443689</v>
+        <v>443745</v>
       </c>
       <c r="R225" t="n">
-        <v>7009728</v>
+        <v>7010081</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22949,10 +22949,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127310990</v>
+        <v>127311059</v>
       </c>
       <c r="B226" t="n">
-        <v>91350</v>
+        <v>88754</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22960,21 +22960,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22984,10 +22984,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443745</v>
+        <v>444272</v>
       </c>
       <c r="R226" t="n">
-        <v>7010081</v>
+        <v>7010237</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23046,10 +23046,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127310986</v>
+        <v>127311030</v>
       </c>
       <c r="B227" t="n">
-        <v>91350</v>
+        <v>75075</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23057,21 +23057,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23081,10 +23081,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>444046</v>
+        <v>444131</v>
       </c>
       <c r="R227" t="n">
-        <v>7010063</v>
+        <v>7010038</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23143,7 +23143,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127311030</v>
+        <v>127311034</v>
       </c>
       <c r="B228" t="n">
         <v>75075</v>
@@ -23178,10 +23178,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>444131</v>
+        <v>444026</v>
       </c>
       <c r="R228" t="n">
-        <v>7010038</v>
+        <v>7010076</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23240,10 +23240,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127311034</v>
+        <v>127310986</v>
       </c>
       <c r="B229" t="n">
-        <v>75075</v>
+        <v>91351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23251,21 +23251,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>444026</v>
+        <v>444046</v>
       </c>
       <c r="R229" t="n">
-        <v>7010076</v>
+        <v>7010063</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127311041</v>
+        <v>127311022</v>
       </c>
       <c r="B230" t="n">
-        <v>80132</v>
+        <v>91647</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23348,21 +23348,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23372,10 +23372,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>444094</v>
+        <v>444108</v>
       </c>
       <c r="R230" t="n">
-        <v>7010004</v>
+        <v>7010040</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23434,10 +23434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127311022</v>
+        <v>127311041</v>
       </c>
       <c r="B231" t="n">
-        <v>91646</v>
+        <v>80132</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23445,21 +23445,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444108</v>
+        <v>444094</v>
       </c>
       <c r="R231" t="n">
-        <v>7010040</v>
+        <v>7010004</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23531,10 +23531,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127310988</v>
+        <v>127311027</v>
       </c>
       <c r="B232" t="n">
-        <v>91350</v>
+        <v>75075</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23542,21 +23542,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23566,10 +23566,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>443937</v>
+        <v>444316</v>
       </c>
       <c r="R232" t="n">
-        <v>7010167</v>
+        <v>7010269</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23631,7 +23631,7 @@
         <v>127311024</v>
       </c>
       <c r="B233" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23725,10 +23725,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127311025</v>
+        <v>127310988</v>
       </c>
       <c r="B234" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23736,21 +23736,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23760,10 +23760,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>443634</v>
+        <v>443937</v>
       </c>
       <c r="R234" t="n">
-        <v>7009878</v>
+        <v>7010167</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23822,10 +23822,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127311027</v>
+        <v>127311025</v>
       </c>
       <c r="B235" t="n">
-        <v>75075</v>
+        <v>91647</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23833,21 +23833,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1460</v>
+        <v>658</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23857,10 +23857,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>444316</v>
+        <v>443634</v>
       </c>
       <c r="R235" t="n">
-        <v>7010269</v>
+        <v>7009878</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23922,7 +23922,7 @@
         <v>127311050</v>
       </c>
       <c r="B236" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>127311051</v>
       </c>
       <c r="B237" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>127310994</v>
       </c>
       <c r="B238" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24404,10 +24404,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127310991</v>
+        <v>127311023</v>
       </c>
       <c r="B241" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24415,21 +24415,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24439,10 +24439,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>443609</v>
+        <v>444039</v>
       </c>
       <c r="R241" t="n">
-        <v>7009974</v>
+        <v>7010073</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24501,10 +24501,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127311023</v>
+        <v>127310991</v>
       </c>
       <c r="B242" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24512,21 +24512,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24536,10 +24536,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>444039</v>
+        <v>443609</v>
       </c>
       <c r="R242" t="n">
-        <v>7010073</v>
+        <v>7009974</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24598,10 +24598,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127311048</v>
+        <v>127311053</v>
       </c>
       <c r="B243" t="n">
-        <v>91368</v>
+        <v>79029</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24609,21 +24609,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24633,10 +24633,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>444000</v>
+        <v>443960</v>
       </c>
       <c r="R243" t="n">
-        <v>7009885</v>
+        <v>7010126</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24695,10 +24695,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127311053</v>
+        <v>127311048</v>
       </c>
       <c r="B244" t="n">
-        <v>79029</v>
+        <v>91369</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24706,21 +24706,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -24730,10 +24730,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>443960</v>
+        <v>444000</v>
       </c>
       <c r="R244" t="n">
-        <v>7010126</v>
+        <v>7009885</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25086,7 +25086,7 @@
         <v>127311013</v>
       </c>
       <c r="B248" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>127311044</v>
       </c>
       <c r="B249" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>127311061</v>
       </c>
       <c r="B250" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>127311049</v>
       </c>
       <c r="B251" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25471,32 +25471,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127311014</v>
+        <v>127311009</v>
       </c>
       <c r="B252" t="n">
-        <v>91804</v>
+        <v>80133</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25506,10 +25506,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>443719</v>
+        <v>444133</v>
       </c>
       <c r="R252" t="n">
-        <v>7009858</v>
+        <v>7010104</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25568,10 +25568,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127310992</v>
+        <v>127311010</v>
       </c>
       <c r="B253" t="n">
-        <v>91350</v>
+        <v>80133</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25579,21 +25579,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>443635</v>
+        <v>443921</v>
       </c>
       <c r="R253" t="n">
-        <v>7009927</v>
+        <v>7010190</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25665,32 +25665,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127311009</v>
+        <v>127311014</v>
       </c>
       <c r="B254" t="n">
-        <v>80133</v>
+        <v>91805</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -25700,10 +25700,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>444133</v>
+        <v>443719</v>
       </c>
       <c r="R254" t="n">
-        <v>7010104</v>
+        <v>7009858</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25762,10 +25762,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127311010</v>
+        <v>127310992</v>
       </c>
       <c r="B255" t="n">
-        <v>80133</v>
+        <v>91351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -25773,21 +25773,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -25797,10 +25797,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>443921</v>
+        <v>443635</v>
       </c>
       <c r="R255" t="n">
-        <v>7010190</v>
+        <v>7009927</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26053,32 +26053,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127311001</v>
+        <v>127310985</v>
       </c>
       <c r="B258" t="n">
-        <v>92052</v>
+        <v>91351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>443716</v>
+        <v>444090</v>
       </c>
       <c r="R258" t="n">
-        <v>7010053</v>
+        <v>7009966</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26150,10 +26150,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127310985</v>
+        <v>127310984</v>
       </c>
       <c r="B259" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26185,10 +26185,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>444090</v>
+        <v>444048</v>
       </c>
       <c r="R259" t="n">
-        <v>7009966</v>
+        <v>7009932</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26247,32 +26247,32 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127310984</v>
+        <v>127311001</v>
       </c>
       <c r="B260" t="n">
-        <v>91350</v>
+        <v>92053</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26282,10 +26282,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>444048</v>
+        <v>443716</v>
       </c>
       <c r="R260" t="n">
-        <v>7009932</v>
+        <v>7010053</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -19932,7 +19932,7 @@
         <v>127311003</v>
       </c>
       <c r="B195" t="n">
-        <v>57514</v>
+        <v>57526</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -19932,7 +19932,7 @@
         <v>127311003</v>
       </c>
       <c r="B195" t="n">
-        <v>57526</v>
+        <v>57530</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -19932,7 +19932,7 @@
         <v>127311003</v>
       </c>
       <c r="B195" t="n">
-        <v>57530</v>
+        <v>57557</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -19932,7 +19932,7 @@
         <v>127311003</v>
       </c>
       <c r="B195" t="n">
-        <v>57557</v>
+        <v>57561</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -19932,7 +19932,7 @@
         <v>127311003</v>
       </c>
       <c r="B195" t="n">
-        <v>57561</v>
+        <v>57564</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -18969,7 +18969,7 @@
         <v>127303922</v>
       </c>
       <c r="B186" t="n">
-        <v>92182</v>
+        <v>92183</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>127303917</v>
       </c>
       <c r="B270" t="n">
-        <v>92180</v>
+        <v>92181</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -18969,7 +18969,7 @@
         <v>127303922</v>
       </c>
       <c r="B186" t="n">
-        <v>92183</v>
+        <v>92186</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>127303917</v>
       </c>
       <c r="B270" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -18969,7 +18969,7 @@
         <v>127303922</v>
       </c>
       <c r="B186" t="n">
-        <v>92186</v>
+        <v>92187</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>127303917</v>
       </c>
       <c r="B270" t="n">
-        <v>92184</v>
+        <v>92185</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -18969,7 +18969,7 @@
         <v>127303922</v>
       </c>
       <c r="B186" t="n">
-        <v>92187</v>
+        <v>92189</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>127303917</v>
       </c>
       <c r="B270" t="n">
-        <v>92185</v>
+        <v>92187</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -18969,7 +18969,7 @@
         <v>127303922</v>
       </c>
       <c r="B186" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>127303917</v>
       </c>
       <c r="B270" t="n">
-        <v>92187</v>
+        <v>92188</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -18969,7 +18969,7 @@
         <v>127303922</v>
       </c>
       <c r="B186" t="n">
-        <v>92190</v>
+        <v>92191</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>127303917</v>
       </c>
       <c r="B270" t="n">
-        <v>92188</v>
+        <v>92189</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 34547-2025 artfynd.xlsx
+++ b/artfynd/A 34547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY256"/>
+  <dimension ref="A1:AZ256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311483</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054773</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303915</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171801</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311059</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054774</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054775</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054776</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054777</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054778</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054779</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054780</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063419</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171758</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171759</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171760</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171761</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171762</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171763</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171764</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171765</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171766</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171767</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3132,6 +3257,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171768</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3229,6 +3359,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171769</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3326,6 +3461,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171770</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3423,6 +3563,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171771</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3520,6 +3665,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171772</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3617,6 +3767,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299819</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3719,6 +3874,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299820</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3816,6 +3976,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299821</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3913,6 +4078,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302646</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4010,6 +4180,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302647</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4107,6 +4282,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302648</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4204,6 +4384,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302649</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4301,6 +4486,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302650</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4398,6 +4588,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302651</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4495,6 +4690,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302652</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4592,6 +4792,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302653</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4689,6 +4894,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302654</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4786,6 +4996,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302655</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4883,6 +5098,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302657</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4980,6 +5200,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302658</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5077,6 +5302,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302659</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5174,6 +5404,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302660</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5271,6 +5506,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302661</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5368,6 +5608,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302663</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5490,6 +5735,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303909</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5612,6 +5862,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303924</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5734,6 +5989,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303930</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5831,6 +6091,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311016</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5928,6 +6193,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311017</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6025,6 +6295,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311018</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6122,6 +6397,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311020</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6219,6 +6499,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311021</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6316,6 +6601,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311022</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6413,6 +6703,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311023</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6510,6 +6805,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311024</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6607,6 +6907,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6704,6 +7009,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311026</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6801,6 +7111,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054796</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6898,6 +7213,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299830</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6995,6 +7315,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302679</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7092,6 +7417,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311060</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7189,6 +7519,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311061</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7286,6 +7621,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302666</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7383,6 +7723,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311044</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7480,6 +7825,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054764</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7577,6 +7927,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054765</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7674,6 +8029,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054766</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7771,6 +8131,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063407</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7868,6 +8233,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171727</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7965,6 +8335,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171728</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8062,6 +8437,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171729</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8159,6 +8539,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171730</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8256,6 +8641,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171731</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8353,6 +8743,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171732</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8450,6 +8845,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171733</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8547,6 +8947,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171734</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8644,6 +9049,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171735</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8741,6 +9151,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299813</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8838,6 +9253,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299814</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8935,6 +9355,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299815</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9032,6 +9457,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299816</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9129,6 +9559,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299817</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9226,6 +9661,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302624</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9323,6 +9763,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302625</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9420,6 +9865,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302627</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9517,6 +9967,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302628</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9614,6 +10069,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302629</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9711,6 +10171,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302630</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9808,6 +10273,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302632</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9905,6 +10375,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302633</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10002,6 +10477,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302634</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10099,6 +10579,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302635</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10196,6 +10681,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302636</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10293,6 +10783,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302637</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10390,6 +10885,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302638</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10487,6 +10987,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302639</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10584,6 +11089,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302640</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10706,6 +11216,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303928</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10828,6 +11343,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303932</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10925,6 +11445,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310984</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11022,6 +11547,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310985</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11119,6 +11649,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310986</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11216,6 +11751,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310987</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11313,6 +11853,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310988</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11410,6 +11955,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310989</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11507,6 +12057,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310990</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11604,6 +12159,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310991</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11701,6 +12261,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310992</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11798,6 +12363,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310993</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11895,6 +12465,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310994</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11992,6 +12567,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310995</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12089,6 +12669,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054783</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12186,6 +12771,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054784</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12283,6 +12873,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054785</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12380,6 +12975,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054786</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12477,6 +13077,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171788</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12574,6 +13179,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171789</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12671,6 +13281,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171790</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12768,6 +13383,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171791</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12865,6 +13485,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171792</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12962,6 +13587,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171793</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13059,6 +13689,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299824</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13156,6 +13791,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299825</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13253,6 +13893,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302668</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13350,6 +13995,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302669</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13447,6 +14097,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302670</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13544,6 +14199,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302671</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13641,6 +14301,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302672</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13738,6 +14403,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302673</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13860,6 +14530,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303919</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13957,6 +14632,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311047</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14055,6 +14735,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063416</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14153,6 +14838,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063417</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14250,6 +14940,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171756</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14347,6 +15042,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171757</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14445,6 +15145,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302644</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14543,6 +15248,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302645</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14640,6 +15350,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311011</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14737,6 +15452,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311012</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14834,6 +15554,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311013</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14931,6 +15656,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311014</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15028,6 +15758,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171774</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15125,6 +15860,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171775</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15222,6 +15962,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171776</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15319,6 +16064,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171777</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15416,6 +16166,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171778</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15513,6 +16268,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171779</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15610,6 +16370,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302664</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15732,6 +16497,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303925</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15829,6 +16599,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311037</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15926,6 +16701,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311038</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16023,6 +16803,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311039</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16120,6 +16905,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054795</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16217,6 +17007,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171799</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16339,6 +17134,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303905</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16461,6 +17261,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303913</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16583,6 +17388,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303914</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16680,6 +17490,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311027</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16777,6 +17592,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311029</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16874,6 +17694,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311030</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16971,6 +17796,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311031</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17068,6 +17898,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311032</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17165,6 +18000,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311033</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17262,6 +18102,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311034</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17359,6 +18204,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311035</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17456,6 +18306,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054781</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17553,6 +18408,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171773</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17650,6 +18510,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311036</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17747,6 +18612,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311040</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17882,6 +18752,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303917</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18002,6 +18877,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303922</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18099,6 +18979,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171754</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18196,6 +19081,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171755</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18293,6 +19183,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311009</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18390,6 +19285,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311010</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18487,6 +19387,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054768</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18584,6 +19489,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054770</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18681,6 +19591,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171737</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18778,6 +19693,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171738</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18875,6 +19795,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171739</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18972,6 +19897,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171740</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19069,6 +19999,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171741</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19166,6 +20101,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310996</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19263,6 +20203,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054763</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19360,6 +20305,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171726</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19462,6 +20412,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054790</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19564,6 +20519,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054791</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19661,6 +20621,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054792</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19763,6 +20728,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054793</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19865,6 +20835,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054794</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19962,6 +20937,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171798</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20059,6 +21039,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299829</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20166,6 +21151,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303899</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20288,6 +21278,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303927</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20385,6 +21380,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311052</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20482,6 +21482,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311053</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20579,6 +21584,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311054</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20676,6 +21686,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054762</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20773,6 +21788,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171725</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20895,6 +21915,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303906</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20992,6 +22017,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054782</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21089,6 +22119,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171780</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21186,6 +22221,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171781</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21283,6 +22323,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171782</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21380,6 +22425,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171783</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21477,6 +22527,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299822</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21574,6 +22629,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299823</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21681,6 +22741,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303898</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21778,6 +22843,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311041</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21875,6 +22945,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311042</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21972,6 +23047,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311043</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22094,6 +23174,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303910</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22191,6 +23276,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054771</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22288,6 +23378,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054772</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22385,6 +23480,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171744</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22482,6 +23582,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171745</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22579,6 +23684,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310999</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22676,6 +23786,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171802</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22773,6 +23888,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171747</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22870,6 +23990,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171748</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22967,6 +24092,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171749</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23064,6 +24194,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171750</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23161,6 +24296,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171751</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23258,6 +24398,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171752</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23355,6 +24500,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171753</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23452,6 +24602,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299818</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23559,6 +24714,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303912</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23681,6 +24841,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303916</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23778,6 +24943,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311004</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23875,6 +25045,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311006</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23972,6 +25147,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311007</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24069,6 +25249,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311008</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24178,6 +25363,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171746</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24280,6 +25470,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063408</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24382,6 +25577,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063409</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24484,6 +25684,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063410</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24586,6 +25791,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063411</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24688,6 +25898,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063412</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24790,6 +26005,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063413</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24892,6 +26112,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063414</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24994,6 +26219,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127063415</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25096,6 +26326,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302641</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25206,6 +26441,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302642</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25316,6 +26556,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302643</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25426,6 +26671,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310997</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25523,6 +26773,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311003</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25630,6 +26885,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303907</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25737,6 +26997,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303918</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25849,6 +27114,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303920</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25946,6 +27216,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310998</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26044,8 +27319,270 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302665</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>